--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,42 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>English National League</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>01:05:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
+    <t>Tamworth FC</t>
+  </si>
+  <si>
+    <t>Eastleigh</t>
+  </si>
+  <si>
+    <t>Millonarios</t>
+  </si>
+  <si>
+    <t>Sutton Utd</t>
+  </si>
+  <si>
+    <t>Southend</t>
+  </si>
+  <si>
+    <t>2026-09-28 01:19:23</t>
   </si>
 </sst>
 </file>
@@ -585,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +864,732 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2">
+        <v>2.36</v>
+      </c>
+      <c r="G2">
+        <v>2.54</v>
+      </c>
+      <c r="H2">
+        <v>3.15</v>
+      </c>
+      <c r="I2">
+        <v>3.45</v>
+      </c>
+      <c r="J2">
+        <v>3.4</v>
+      </c>
+      <c r="K2">
+        <v>3.65</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
+        <v>3.7</v>
+      </c>
+      <c r="O2">
+        <v>1.33</v>
+      </c>
+      <c r="P2">
+        <v>1.91</v>
+      </c>
+      <c r="Q2">
+        <v>1.96</v>
+      </c>
+      <c r="R2">
+        <v>1.35</v>
+      </c>
+      <c r="S2">
+        <v>3.45</v>
+      </c>
+      <c r="T2">
+        <v>1.76</v>
+      </c>
+      <c r="U2">
+        <v>2.18</v>
+      </c>
+      <c r="V2">
+        <v>1.42</v>
+      </c>
+      <c r="W2">
+        <v>1.64</v>
+      </c>
+      <c r="X2">
+        <v>17</v>
+      </c>
+      <c r="Y2">
+        <v>13</v>
+      </c>
+      <c r="Z2">
+        <v>23</v>
+      </c>
+      <c r="AA2">
+        <v>65</v>
+      </c>
+      <c r="AB2">
+        <v>11</v>
+      </c>
+      <c r="AC2">
+        <v>8</v>
+      </c>
+      <c r="AD2">
+        <v>14</v>
+      </c>
+      <c r="AE2">
+        <v>48</v>
+      </c>
+      <c r="AF2">
+        <v>16</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>17.5</v>
+      </c>
+      <c r="AI2">
+        <v>55</v>
+      </c>
+      <c r="AJ2">
+        <v>34</v>
+      </c>
+      <c r="AK2">
+        <v>27</v>
+      </c>
+      <c r="AL2">
+        <v>50</v>
+      </c>
+      <c r="AM2">
+        <v>110</v>
+      </c>
+      <c r="AN2">
+        <v>21</v>
+      </c>
+      <c r="AO2">
+        <v>36</v>
+      </c>
+      <c r="AP2">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2">
+        <v>11</v>
+      </c>
+      <c r="AR2">
+        <v>19.5</v>
+      </c>
+      <c r="AS2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU2">
+        <v>6.8</v>
+      </c>
+      <c r="AV2">
+        <v>12</v>
+      </c>
+      <c r="AW2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX2">
+        <v>13.5</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>14.5</v>
+      </c>
+      <c r="BA2">
+        <v>9</v>
+      </c>
+      <c r="BB2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE2">
+        <v>9.6</v>
+      </c>
+      <c r="BF2">
+        <v>17.5</v>
+      </c>
+      <c r="BG2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3">
+        <v>2.3</v>
+      </c>
+      <c r="G3">
+        <v>2.86</v>
+      </c>
+      <c r="H3">
+        <v>2.84</v>
+      </c>
+      <c r="I3">
+        <v>3.75</v>
+      </c>
+      <c r="J3">
+        <v>3.35</v>
+      </c>
+      <c r="K3">
+        <v>4.4</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1.12</v>
+      </c>
+      <c r="Q3">
+        <v>1.53</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4">
+        <v>4.1</v>
+      </c>
+      <c r="G4">
+        <v>5.5</v>
+      </c>
+      <c r="H4">
+        <v>1.77</v>
+      </c>
+      <c r="I4">
+        <v>1.96</v>
+      </c>
+      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4">
+        <v>4.3</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>2.22</v>
+      </c>
+      <c r="Q4">
+        <v>1.65</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -289,7 +289,7 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>2026-09-28 01:19:23</t>
+    <t>2026-09-28 03:29:40</t>
   </si>
 </sst>
 </file>
@@ -883,7 +883,7 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
         <v>2.54</v>
@@ -895,13 +895,13 @@
         <v>3.45</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -913,7 +913,7 @@
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q2">
         <v>1.96</v>
@@ -925,16 +925,16 @@
         <v>3.45</v>
       </c>
       <c r="T2">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
         <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X2">
         <v>17</v>
@@ -985,7 +985,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO2">
         <v>36</v>
@@ -1036,7 +1036,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF2">
         <v>17.5</v>
@@ -1125,40 +1125,40 @@
         <v>89</v>
       </c>
       <c r="F3">
+        <v>2.28</v>
+      </c>
+      <c r="G3">
+        <v>2.56</v>
+      </c>
+      <c r="H3">
+        <v>2.82</v>
+      </c>
+      <c r="I3">
+        <v>3.2</v>
+      </c>
+      <c r="J3">
+        <v>3.65</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>2.3</v>
       </c>
-      <c r="G3">
-        <v>2.86</v>
-      </c>
-      <c r="H3">
-        <v>2.84</v>
-      </c>
-      <c r="I3">
-        <v>3.75</v>
-      </c>
-      <c r="J3">
-        <v>3.35</v>
-      </c>
-      <c r="K3">
-        <v>4.4</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>1.12</v>
-      </c>
       <c r="Q3">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="R3">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -289,7 +289,7 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>2026-09-28 03:29:40</t>
+    <t>2026-09-28 05:41:51</t>
   </si>
 </sst>
 </file>
@@ -883,7 +883,7 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
         <v>2.54</v>
@@ -895,7 +895,7 @@
         <v>3.45</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
         <v>3.65</v>
@@ -907,7 +907,7 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
         <v>1.33</v>
@@ -922,10 +922,10 @@
         <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U2">
         <v>2.14</v>
@@ -1000,7 +1000,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1024,7 +1024,7 @@
         <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>9.199999999999999</v>
@@ -1131,7 +1131,7 @@
         <v>2.56</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I3">
         <v>3.2</v>
@@ -1140,7 +1140,7 @@
         <v>3.65</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>2.3</v>
       </c>
       <c r="Q3">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1376,13 +1376,13 @@
         <v>1.77</v>
       </c>
       <c r="I4">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -289,7 +289,7 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>2026-09-28 05:41:51</t>
+    <t>2026-09-28 07:53:38</t>
   </si>
 </sst>
 </file>
@@ -910,7 +910,7 @@
         <v>3.65</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
         <v>1.92</v>
@@ -922,13 +922,13 @@
         <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T2">
         <v>1.76</v>
       </c>
       <c r="U2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
         <v>1.42</v>
@@ -1125,22 +1125,22 @@
         <v>89</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H3">
         <v>2.8</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
         <v>3.65</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -289,7 +289,7 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>2026-09-28 07:53:38</t>
+    <t>2026-09-28 10:05:42</t>
   </si>
 </sst>
 </file>
@@ -907,31 +907,31 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q2">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
         <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
         <v>1.65</v>
@@ -973,7 +973,7 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK2">
         <v>27</v>
@@ -1000,7 +1000,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1015,16 +1015,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AX2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB2">
         <v>9.199999999999999</v>
@@ -1039,7 +1039,7 @@
         <v>9.4</v>
       </c>
       <c r="BF2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG2">
         <v>9.199999999999999</v>
@@ -1125,19 +1125,19 @@
         <v>89</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="H3">
         <v>2.8</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
         <v>4</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q3">
         <v>1.71</v>
@@ -1382,7 +1382,7 @@
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -289,7 +289,7 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>2026-09-28 10:05:42</t>
+    <t>2026-09-28 12:18:17</t>
   </si>
 </sst>
 </file>
@@ -883,7 +883,7 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
         <v>2.54</v>
@@ -892,13 +892,13 @@
         <v>3.15</v>
       </c>
       <c r="I2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.36</v>
@@ -919,19 +919,19 @@
         <v>1.9</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U2">
         <v>2.22</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
         <v>1.65</v>
@@ -952,7 +952,7 @@
         <v>11</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
         <v>14</v>
@@ -973,7 +973,7 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK2">
         <v>27</v>
@@ -985,7 +985,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO2">
         <v>36</v>
@@ -997,16 +997,16 @@
         <v>11</v>
       </c>
       <c r="AR2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2">
         <v>12</v>
@@ -1024,7 +1024,7 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2">
         <v>9.199999999999999</v>
@@ -1036,7 +1036,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>18</v>
@@ -1128,16 +1128,16 @@
         <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="H3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K3">
         <v>4</v>
@@ -1370,19 +1370,19 @@
         <v>4.1</v>
       </c>
       <c r="G4">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H4">
         <v>1.77</v>
       </c>
       <c r="I4">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -289,7 +289,7 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>2026-09-28 12:18:17</t>
+    <t>2026-09-28 14:30:34</t>
   </si>
 </sst>
 </file>
@@ -883,22 +883,22 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I2">
         <v>3.4</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.36</v>
@@ -910,22 +910,22 @@
         <v>3.7</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
         <v>1.94</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U2">
         <v>2.22</v>
@@ -934,10 +934,10 @@
         <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
         <v>13</v>
@@ -1000,7 +1000,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1024,7 +1024,7 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2">
         <v>9.199999999999999</v>
@@ -1036,7 +1036,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>18</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q3">
         <v>1.71</v>
@@ -1370,19 +1370,19 @@
         <v>4.1</v>
       </c>
       <c r="G4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="H4">
         <v>1.77</v>
       </c>
       <c r="I4">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>2.22</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -289,7 +289,7 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>2026-09-28 14:30:34</t>
+    <t>2026-09-28 16:40:20</t>
   </si>
 </sst>
 </file>
@@ -892,13 +892,13 @@
         <v>3.2</v>
       </c>
       <c r="I2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J2">
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.36</v>
@@ -913,13 +913,13 @@
         <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q2">
         <v>1.93</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
         <v>3.5</v>
@@ -934,10 +934,10 @@
         <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y2">
         <v>13</v>
@@ -973,7 +973,7 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK2">
         <v>27</v>
@@ -1000,7 +1000,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1024,7 +1024,7 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2">
         <v>9.199999999999999</v>
@@ -1036,7 +1036,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>18</v>
@@ -1125,226 +1125,226 @@
         <v>89</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H3">
         <v>2.82</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
         <v>3.7</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BO3">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>91</v>
@@ -1367,226 +1367,226 @@
         <v>90</v>
       </c>
       <c r="F4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G4">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I4">
         <v>1.92</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P4">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q4">
         <v>1.66</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>91</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>English National League</t>
   </si>
   <si>
+    <t>Peruvian Primera Division</t>
+  </si>
+  <si>
     <t>2026-09-30</t>
   </si>
   <si>
@@ -271,6 +274,9 @@
     <t>18:45:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
@@ -280,6 +286,9 @@
     <t>Eastleigh</t>
   </si>
   <si>
+    <t>Cienciano</t>
+  </si>
+  <si>
     <t>Millonarios</t>
   </si>
   <si>
@@ -289,7 +298,10 @@
     <t>Southend</t>
   </si>
   <si>
-    <t>2026-09-28 16:40:20</t>
+    <t>CD Los Chankas</t>
+  </si>
+  <si>
+    <t>2026-09-28 18:51:05</t>
   </si>
 </sst>
 </file>
@@ -621,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -871,16 +883,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F2">
         <v>2.36</v>
@@ -892,7 +904,7 @@
         <v>3.2</v>
       </c>
       <c r="I2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2">
         <v>3.4</v>
@@ -916,13 +928,13 @@
         <v>1.91</v>
       </c>
       <c r="Q2">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R2">
         <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T2">
         <v>1.76</v>
@@ -934,10 +946,10 @@
         <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
         <v>13</v>
@@ -958,7 +970,7 @@
         <v>14</v>
       </c>
       <c r="AE2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF2">
         <v>16</v>
@@ -979,7 +991,7 @@
         <v>27</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM2">
         <v>110</v>
@@ -1000,7 +1012,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT2">
         <v>9.199999999999999</v>
@@ -1012,7 +1024,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1024,25 +1036,25 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BB2">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BC2">
-        <v>9.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>18</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1105,7 +1117,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1113,31 +1125,31 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3">
         <v>2.3</v>
       </c>
       <c r="G3">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
         <v>4.1</v>
@@ -1146,37 +1158,37 @@
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
         <v>4.8</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q3">
         <v>1.62</v>
       </c>
       <c r="R3">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S3">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V3">
         <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X3">
         <v>25</v>
@@ -1194,10 +1206,10 @@
         <v>15</v>
       </c>
       <c r="AC3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
         <v>32</v>
@@ -1227,7 +1239,7 @@
         <v>70</v>
       </c>
       <c r="AN3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AO3">
         <v>21</v>
@@ -1245,7 +1257,7 @@
         <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU3">
         <v>8</v>
@@ -1302,7 +1314,7 @@
         <v>100</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN3">
         <v>7.6</v>
@@ -1347,7 +1359,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1355,16 +1367,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F4">
         <v>4.2</v>
@@ -1373,16 +1385,16 @@
         <v>4.8</v>
       </c>
       <c r="H4">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="I4">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1391,7 +1403,7 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
         <v>1.23</v>
@@ -1403,7 +1415,7 @@
         <v>1.66</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S4">
         <v>2.66</v>
@@ -1415,7 +1427,7 @@
         <v>2.26</v>
       </c>
       <c r="V4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W4">
         <v>1.26</v>
@@ -1424,7 +1436,7 @@
         <v>25</v>
       </c>
       <c r="Y4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
         <v>15.5</v>
@@ -1436,7 +1448,7 @@
         <v>21</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD4">
         <v>11</v>
@@ -1448,7 +1460,7 @@
         <v>38</v>
       </c>
       <c r="AG4">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AH4">
         <v>18</v>
@@ -1475,7 +1487,7 @@
         <v>11.5</v>
       </c>
       <c r="AP4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ4">
         <v>9.6</v>
@@ -1556,19 +1568,19 @@
         <v>48</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT4">
         <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
         <v>17.5</v>
@@ -1589,7 +1601,249 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5">
+        <v>1.4</v>
+      </c>
+      <c r="G5">
+        <v>1.49</v>
+      </c>
+      <c r="H5">
+        <v>7.4</v>
+      </c>
+      <c r="I5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J5">
+        <v>4.7</v>
+      </c>
+      <c r="K5">
+        <v>5.9</v>
+      </c>
+      <c r="L5">
+        <v>1.18</v>
+      </c>
+      <c r="M5">
+        <v>1.03</v>
+      </c>
+      <c r="N5">
+        <v>6</v>
+      </c>
+      <c r="O5">
+        <v>1.16</v>
+      </c>
+      <c r="P5">
+        <v>2.72</v>
+      </c>
+      <c r="Q5">
+        <v>1.4</v>
+      </c>
+      <c r="R5">
+        <v>1.68</v>
+      </c>
+      <c r="S5">
+        <v>2.2</v>
+      </c>
+      <c r="T5">
+        <v>1.6</v>
+      </c>
+      <c r="U5">
+        <v>2.18</v>
+      </c>
+      <c r="V5">
+        <v>1.11</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>38</v>
+      </c>
+      <c r="Y5">
+        <v>36</v>
+      </c>
+      <c r="Z5">
+        <v>90</v>
+      </c>
+      <c r="AA5">
+        <v>250</v>
+      </c>
+      <c r="AB5">
+        <v>13</v>
+      </c>
+      <c r="AC5">
+        <v>13.5</v>
+      </c>
+      <c r="AD5">
+        <v>30</v>
+      </c>
+      <c r="AE5">
+        <v>110</v>
+      </c>
+      <c r="AF5">
+        <v>11.5</v>
+      </c>
+      <c r="AG5">
+        <v>11</v>
+      </c>
+      <c r="AH5">
+        <v>22</v>
+      </c>
+      <c r="AI5">
+        <v>90</v>
+      </c>
+      <c r="AJ5">
+        <v>14</v>
+      </c>
+      <c r="AK5">
+        <v>15</v>
+      </c>
+      <c r="AL5">
+        <v>29</v>
+      </c>
+      <c r="AM5">
+        <v>110</v>
+      </c>
+      <c r="AN5">
+        <v>5.1</v>
+      </c>
+      <c r="AO5">
+        <v>100</v>
+      </c>
+      <c r="AP5">
+        <v>21</v>
+      </c>
+      <c r="AQ5">
+        <v>1.01</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>10.5</v>
+      </c>
+      <c r="AU5">
+        <v>11</v>
+      </c>
+      <c r="AV5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>9.4</v>
+      </c>
+      <c r="AY5">
+        <v>9</v>
+      </c>
+      <c r="AZ5">
+        <v>1.01</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>11</v>
+      </c>
+      <c r="BC5">
+        <v>12</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>4.2</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>15</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>6</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>12</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>29</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>16</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>75</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>70</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>15.5</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -301,7 +301,7 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-09-28 18:51:05</t>
+    <t>2026-09-28 21:01:45</t>
   </si>
 </sst>
 </file>
@@ -895,7 +895,7 @@
         <v>91</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
         <v>2.52</v>
@@ -904,16 +904,16 @@
         <v>3.2</v>
       </c>
       <c r="I2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2">
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -928,13 +928,13 @@
         <v>1.91</v>
       </c>
       <c r="Q2">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R2">
         <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
         <v>1.76</v>
@@ -1137,7 +1137,7 @@
         <v>92</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G3">
         <v>2.54</v>
@@ -1155,7 +1155,7 @@
         <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M3">
         <v>1.04</v>
@@ -1239,7 +1239,7 @@
         <v>70</v>
       </c>
       <c r="AN3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO3">
         <v>21</v>
@@ -1305,25 +1305,25 @@
         <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
         <v>1.02</v>
       </c>
       <c r="BN3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO3">
         <v>3.85</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
@@ -1347,13 +1347,13 @@
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1382,7 +1382,7 @@
         <v>4.2</v>
       </c>
       <c r="G4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H4">
         <v>1.8</v>
@@ -1397,7 +1397,7 @@
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
         <v>1.04</v>
@@ -1415,7 +1415,7 @@
         <v>1.66</v>
       </c>
       <c r="R4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
         <v>2.66</v>
@@ -1448,7 +1448,7 @@
         <v>21</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
         <v>11</v>
@@ -1466,7 +1466,7 @@
         <v>18</v>
       </c>
       <c r="AI4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ4">
         <v>110</v>
@@ -1484,7 +1484,7 @@
         <v>55</v>
       </c>
       <c r="AO4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AP4">
         <v>17.5</v>
@@ -1580,7 +1580,7 @@
         <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV4">
         <v>17.5</v>
@@ -1666,7 +1666,7 @@
         <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
         <v>1.11</v>
@@ -1732,7 +1732,7 @@
         <v>21</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR5">
         <v>1.01</v>
@@ -1747,7 +1747,7 @@
         <v>11</v>
       </c>
       <c r="AV5">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AW5">
         <v>1.01</v>
@@ -1771,7 +1771,7 @@
         <v>12</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BE5">
         <v>1.01</v>
@@ -1804,7 +1804,7 @@
         <v>6</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BP5">
         <v>12</v>
@@ -1816,7 +1816,7 @@
         <v>29</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT5">
         <v>16</v>
@@ -1828,13 +1828,13 @@
         <v>75</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX5">
         <v>70</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ5">
         <v>15.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -301,7 +301,7 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-09-28 21:01:45</t>
+    <t>2026-09-28 23:11:31</t>
   </si>
 </sst>
 </file>
@@ -895,64 +895,64 @@
         <v>91</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
         <v>3.2</v>
       </c>
       <c r="I2">
+        <v>3.45</v>
+      </c>
+      <c r="J2">
         <v>3.35</v>
       </c>
-      <c r="J2">
-        <v>3.4</v>
-      </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
         <v>1.66</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
         <v>23</v>
@@ -961,7 +961,7 @@
         <v>65</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -970,7 +970,7 @@
         <v>14</v>
       </c>
       <c r="AE2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>16</v>
@@ -985,7 +985,7 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK2">
         <v>27</v>
@@ -997,13 +997,13 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
         <v>11</v>
@@ -1012,13 +1012,13 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>12</v>
@@ -1048,7 +1048,7 @@
         <v>28</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>18</v>
@@ -1167,7 +1167,7 @@
         <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q3">
         <v>1.62</v>
@@ -1311,7 +1311,7 @@
         <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM3">
         <v>1.02</v>
@@ -1323,7 +1323,7 @@
         <v>3.85</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
@@ -1382,7 +1382,7 @@
         <v>4.2</v>
       </c>
       <c r="G4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
         <v>1.8</v>
@@ -1565,7 +1565,7 @@
         <v>5.1</v>
       </c>
       <c r="BP4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BQ4">
         <v>1.02</v>
@@ -1621,13 +1621,13 @@
         <v>94</v>
       </c>
       <c r="F5">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="G5">
         <v>1.49</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>9.800000000000001</v>
@@ -1660,7 +1660,7 @@
         <v>1.68</v>
       </c>
       <c r="S5">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T5">
         <v>1.6</v>
@@ -1729,7 +1729,7 @@
         <v>100</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
         <v>1.02</v>
@@ -1741,22 +1741,22 @@
         <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
         <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
         <v>1.01</v>
@@ -1765,19 +1765,19 @@
         <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
         <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BG5">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,15 @@
     <t>Peruvian Primera Division</t>
   </si>
   <si>
+    <t>Canadian Premier League</t>
+  </si>
+  <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
     <t>2026-09-30</t>
   </si>
   <si>
@@ -277,6 +286,12 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
@@ -289,6 +304,15 @@
     <t>Cienciano</t>
   </si>
   <si>
+    <t>Atletico Ottawa</t>
+  </si>
+  <si>
+    <t>Torque</t>
+  </si>
+  <si>
+    <t>New York Red Bulls</t>
+  </si>
+  <si>
     <t>Millonarios</t>
   </si>
   <si>
@@ -301,7 +325,16 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-09-28 23:11:31</t>
+    <t>Cavalry</t>
+  </si>
+  <si>
+    <t>Penarol</t>
+  </si>
+  <si>
+    <t>St Louis City SC</t>
+  </si>
+  <si>
+    <t>2026-09-29 01:21:48</t>
   </si>
 </sst>
 </file>
@@ -633,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -883,28 +916,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2">
         <v>3.35</v>
@@ -913,34 +946,34 @@
         <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
         <v>1.9</v>
       </c>
       <c r="Q2">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="R2">
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
         <v>1.41</v>
@@ -949,7 +982,7 @@
         <v>1.66</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
@@ -964,7 +997,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
         <v>14</v>
@@ -985,10 +1018,10 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL2">
         <v>46</v>
@@ -997,25 +1030,25 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO2">
         <v>44</v>
       </c>
       <c r="AP2">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1024,7 +1057,7 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -1036,25 +1069,25 @@
         <v>15</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB2">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2">
         <v>18</v>
       </c>
       <c r="BG2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1117,7 +1150,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1125,37 +1158,37 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H3">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.04</v>
@@ -1167,25 +1200,25 @@
         <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
         <v>1.62</v>
       </c>
       <c r="R3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T3">
         <v>1.56</v>
       </c>
       <c r="U3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
         <v>1.65</v>
@@ -1239,7 +1272,7 @@
         <v>70</v>
       </c>
       <c r="AN3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AO3">
         <v>21</v>
@@ -1251,7 +1284,7 @@
         <v>13.5</v>
       </c>
       <c r="AR3">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS3">
         <v>1.01</v>
@@ -1269,7 +1302,7 @@
         <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY3">
         <v>10</v>
@@ -1284,7 +1317,7 @@
         <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BD3">
         <v>1.01</v>
@@ -1296,7 +1329,7 @@
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1320,7 +1353,7 @@
         <v>7.8</v>
       </c>
       <c r="BO3">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
         <v>23</v>
@@ -1359,7 +1392,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1367,58 +1400,58 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H4">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="I4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
         <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="T4">
         <v>1.65</v>
@@ -1430,7 +1463,7 @@
         <v>2.06</v>
       </c>
       <c r="W4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X4">
         <v>25</v>
@@ -1439,7 +1472,7 @@
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA4">
         <v>22</v>
@@ -1460,7 +1493,7 @@
         <v>38</v>
       </c>
       <c r="AG4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH4">
         <v>18</v>
@@ -1520,7 +1553,7 @@
         <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BB4">
         <v>1.01</v>
@@ -1544,7 +1577,7 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
         <v>13</v>
@@ -1565,7 +1598,7 @@
         <v>5.1</v>
       </c>
       <c r="BP4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BQ4">
         <v>1.02</v>
@@ -1580,7 +1613,7 @@
         <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BV4">
         <v>17.5</v>
@@ -1601,7 +1634,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1609,40 +1642,40 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F5">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G5">
         <v>1.49</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="K5">
         <v>5.9</v>
       </c>
       <c r="L5">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
         <v>6</v>
@@ -1657,10 +1690,10 @@
         <v>1.4</v>
       </c>
       <c r="R5">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="S5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T5">
         <v>1.6</v>
@@ -1669,7 +1702,7 @@
         <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -1714,7 +1747,7 @@
         <v>14</v>
       </c>
       <c r="AK5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL5">
         <v>29</v>
@@ -1732,31 +1765,31 @@
         <v>1.01</v>
       </c>
       <c r="AQ5">
+        <v>21</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>10.5</v>
+      </c>
+      <c r="AU5">
+        <v>11</v>
+      </c>
+      <c r="AV5">
         <v>1.02</v>
       </c>
-      <c r="AR5">
-        <v>1.01</v>
-      </c>
-      <c r="AS5">
-        <v>1.01</v>
-      </c>
-      <c r="AT5">
-        <v>1.01</v>
-      </c>
-      <c r="AU5">
-        <v>1.01</v>
-      </c>
-      <c r="AV5">
-        <v>1.01</v>
-      </c>
       <c r="AW5">
         <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
         <v>1.01</v>
@@ -1765,7 +1798,7 @@
         <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC5">
         <v>1.01</v>
@@ -1777,7 +1810,7 @@
         <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BG5">
         <v>1.01</v>
@@ -1789,7 +1822,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
@@ -1804,13 +1837,13 @@
         <v>6</v>
       </c>
       <c r="BO5">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BP5">
         <v>12</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
         <v>29</v>
@@ -1843,7 +1876,733 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>95</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6">
+        <v>3.8</v>
+      </c>
+      <c r="G6">
+        <v>5.7</v>
+      </c>
+      <c r="H6">
+        <v>1.75</v>
+      </c>
+      <c r="I6">
+        <v>1.96</v>
+      </c>
+      <c r="J6">
+        <v>3.2</v>
+      </c>
+      <c r="K6">
+        <v>5.1</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.05</v>
+      </c>
+      <c r="N6">
+        <v>1.01</v>
+      </c>
+      <c r="O6">
+        <v>1.23</v>
+      </c>
+      <c r="P6">
+        <v>2.06</v>
+      </c>
+      <c r="Q6">
+        <v>1.61</v>
+      </c>
+      <c r="R6">
+        <v>1.44</v>
+      </c>
+      <c r="S6">
+        <v>2.6</v>
+      </c>
+      <c r="T6">
+        <v>1.58</v>
+      </c>
+      <c r="U6">
+        <v>2.16</v>
+      </c>
+      <c r="V6">
+        <v>2.04</v>
+      </c>
+      <c r="W6">
+        <v>1.21</v>
+      </c>
+      <c r="X6">
+        <v>24</v>
+      </c>
+      <c r="Y6">
+        <v>13</v>
+      </c>
+      <c r="Z6">
+        <v>15</v>
+      </c>
+      <c r="AA6">
+        <v>25</v>
+      </c>
+      <c r="AB6">
+        <v>23</v>
+      </c>
+      <c r="AC6">
+        <v>11.5</v>
+      </c>
+      <c r="AD6">
+        <v>12.5</v>
+      </c>
+      <c r="AE6">
+        <v>22</v>
+      </c>
+      <c r="AF6">
+        <v>44</v>
+      </c>
+      <c r="AG6">
+        <v>23</v>
+      </c>
+      <c r="AH6">
+        <v>22</v>
+      </c>
+      <c r="AI6">
+        <v>38</v>
+      </c>
+      <c r="AJ6">
+        <v>120</v>
+      </c>
+      <c r="AK6">
+        <v>65</v>
+      </c>
+      <c r="AL6">
+        <v>65</v>
+      </c>
+      <c r="AM6">
+        <v>100</v>
+      </c>
+      <c r="AN6">
+        <v>60</v>
+      </c>
+      <c r="AO6">
+        <v>12</v>
+      </c>
+      <c r="AP6">
+        <v>14</v>
+      </c>
+      <c r="AQ6">
+        <v>7.8</v>
+      </c>
+      <c r="AR6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS6">
+        <v>14.5</v>
+      </c>
+      <c r="AT6">
+        <v>13.5</v>
+      </c>
+      <c r="AU6">
+        <v>7</v>
+      </c>
+      <c r="AV6">
+        <v>7.6</v>
+      </c>
+      <c r="AW6">
+        <v>13</v>
+      </c>
+      <c r="AX6">
+        <v>26</v>
+      </c>
+      <c r="AY6">
+        <v>13</v>
+      </c>
+      <c r="AZ6">
+        <v>12.5</v>
+      </c>
+      <c r="BA6">
+        <v>22</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>7.4</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7">
+        <v>3.1</v>
+      </c>
+      <c r="G7">
+        <v>3.4</v>
+      </c>
+      <c r="H7">
+        <v>2.44</v>
+      </c>
+      <c r="I7">
+        <v>2.6</v>
+      </c>
+      <c r="J7">
+        <v>3.3</v>
+      </c>
+      <c r="K7">
+        <v>3.6</v>
+      </c>
+      <c r="L7">
+        <v>1.43</v>
+      </c>
+      <c r="M7">
+        <v>1.08</v>
+      </c>
+      <c r="N7">
+        <v>3.35</v>
+      </c>
+      <c r="O7">
+        <v>1.38</v>
+      </c>
+      <c r="P7">
+        <v>1.8</v>
+      </c>
+      <c r="Q7">
+        <v>2.1</v>
+      </c>
+      <c r="R7">
+        <v>1.3</v>
+      </c>
+      <c r="S7">
+        <v>3.85</v>
+      </c>
+      <c r="T7">
+        <v>1.83</v>
+      </c>
+      <c r="U7">
+        <v>2.02</v>
+      </c>
+      <c r="V7">
+        <v>1.62</v>
+      </c>
+      <c r="W7">
+        <v>1.41</v>
+      </c>
+      <c r="X7">
+        <v>15</v>
+      </c>
+      <c r="Y7">
+        <v>10.5</v>
+      </c>
+      <c r="Z7">
+        <v>16</v>
+      </c>
+      <c r="AA7">
+        <v>38</v>
+      </c>
+      <c r="AB7">
+        <v>12</v>
+      </c>
+      <c r="AC7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>12.5</v>
+      </c>
+      <c r="AE7">
+        <v>30</v>
+      </c>
+      <c r="AF7">
+        <v>23</v>
+      </c>
+      <c r="AG7">
+        <v>15</v>
+      </c>
+      <c r="AH7">
+        <v>19.5</v>
+      </c>
+      <c r="AI7">
+        <v>55</v>
+      </c>
+      <c r="AJ7">
+        <v>70</v>
+      </c>
+      <c r="AK7">
+        <v>48</v>
+      </c>
+      <c r="AL7">
+        <v>65</v>
+      </c>
+      <c r="AM7">
+        <v>140</v>
+      </c>
+      <c r="AN7">
+        <v>50</v>
+      </c>
+      <c r="AO7">
+        <v>26</v>
+      </c>
+      <c r="AP7">
+        <v>11</v>
+      </c>
+      <c r="AQ7">
+        <v>8.6</v>
+      </c>
+      <c r="AR7">
+        <v>13.5</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>10</v>
+      </c>
+      <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>10.5</v>
+      </c>
+      <c r="AW7">
+        <v>1.01</v>
+      </c>
+      <c r="AX7">
+        <v>18</v>
+      </c>
+      <c r="AY7">
+        <v>12</v>
+      </c>
+      <c r="AZ7">
+        <v>16</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>32</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>21</v>
+      </c>
+      <c r="BH7">
+        <v>3.7</v>
+      </c>
+      <c r="BI7">
+        <v>2.56</v>
+      </c>
+      <c r="BJ7">
+        <v>12</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>160</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>6.6</v>
+      </c>
+      <c r="BO7">
+        <v>4.7</v>
+      </c>
+      <c r="BP7">
+        <v>32</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>48</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>6.4</v>
+      </c>
+      <c r="BU7">
+        <v>4.2</v>
+      </c>
+      <c r="BV7">
+        <v>21</v>
+      </c>
+      <c r="BW7">
+        <v>14</v>
+      </c>
+      <c r="BX7">
+        <v>42</v>
+      </c>
+      <c r="BY7">
+        <v>1.02</v>
+      </c>
+      <c r="BZ7">
+        <v>40</v>
+      </c>
+      <c r="CA7">
+        <v>1.02</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8">
+        <v>3.5</v>
+      </c>
+      <c r="G8">
+        <v>3.6</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>2.04</v>
+      </c>
+      <c r="J8">
+        <v>4.3</v>
+      </c>
+      <c r="K8">
+        <v>4.6</v>
+      </c>
+      <c r="L8">
+        <v>1.23</v>
+      </c>
+      <c r="M8">
+        <v>1.02</v>
+      </c>
+      <c r="N8">
+        <v>7.2</v>
+      </c>
+      <c r="O8">
+        <v>1.14</v>
+      </c>
+      <c r="P8">
+        <v>3.05</v>
+      </c>
+      <c r="Q8">
+        <v>1.43</v>
+      </c>
+      <c r="R8">
+        <v>1.83</v>
+      </c>
+      <c r="S8">
+        <v>2.08</v>
+      </c>
+      <c r="T8">
+        <v>1.47</v>
+      </c>
+      <c r="U8">
+        <v>2.94</v>
+      </c>
+      <c r="V8">
+        <v>1.96</v>
+      </c>
+      <c r="W8">
+        <v>1.38</v>
+      </c>
+      <c r="X8">
+        <v>36</v>
+      </c>
+      <c r="Y8">
+        <v>19</v>
+      </c>
+      <c r="Z8">
+        <v>19</v>
+      </c>
+      <c r="AA8">
+        <v>26</v>
+      </c>
+      <c r="AB8">
+        <v>26</v>
+      </c>
+      <c r="AC8">
+        <v>11.5</v>
+      </c>
+      <c r="AD8">
+        <v>12.5</v>
+      </c>
+      <c r="AE8">
+        <v>18</v>
+      </c>
+      <c r="AF8">
+        <v>34</v>
+      </c>
+      <c r="AG8">
+        <v>16</v>
+      </c>
+      <c r="AH8">
+        <v>15</v>
+      </c>
+      <c r="AI8">
+        <v>25</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>34</v>
+      </c>
+      <c r="AL8">
+        <v>32</v>
+      </c>
+      <c r="AM8">
+        <v>46</v>
+      </c>
+      <c r="AN8">
+        <v>18</v>
+      </c>
+      <c r="AO8">
+        <v>7.6</v>
+      </c>
+      <c r="AP8">
+        <v>23</v>
+      </c>
+      <c r="AQ8">
+        <v>14</v>
+      </c>
+      <c r="AR8">
+        <v>15.5</v>
+      </c>
+      <c r="AS8">
+        <v>21</v>
+      </c>
+      <c r="AT8">
+        <v>16.5</v>
+      </c>
+      <c r="AU8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV8">
+        <v>10.5</v>
+      </c>
+      <c r="AW8">
+        <v>13</v>
+      </c>
+      <c r="AX8">
+        <v>21</v>
+      </c>
+      <c r="AY8">
+        <v>13.5</v>
+      </c>
+      <c r="AZ8">
+        <v>13</v>
+      </c>
+      <c r="BA8">
+        <v>20</v>
+      </c>
+      <c r="BB8">
+        <v>32</v>
+      </c>
+      <c r="BC8">
+        <v>20</v>
+      </c>
+      <c r="BD8">
+        <v>20</v>
+      </c>
+      <c r="BE8">
+        <v>26</v>
+      </c>
+      <c r="BF8">
+        <v>16</v>
+      </c>
+      <c r="BG8">
+        <v>6.8</v>
+      </c>
+      <c r="BH8">
+        <v>5.4</v>
+      </c>
+      <c r="BI8">
+        <v>4</v>
+      </c>
+      <c r="BJ8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK8">
+        <v>6.2</v>
+      </c>
+      <c r="BL8">
+        <v>65</v>
+      </c>
+      <c r="BM8">
+        <v>42</v>
+      </c>
+      <c r="BN8">
+        <v>8</v>
+      </c>
+      <c r="BO8">
+        <v>5.8</v>
+      </c>
+      <c r="BP8">
+        <v>25</v>
+      </c>
+      <c r="BQ8">
+        <v>16.5</v>
+      </c>
+      <c r="BR8">
+        <v>27</v>
+      </c>
+      <c r="BS8">
+        <v>18.5</v>
+      </c>
+      <c r="BT8">
+        <v>5.8</v>
+      </c>
+      <c r="BU8">
+        <v>4.2</v>
+      </c>
+      <c r="BV8">
+        <v>13</v>
+      </c>
+      <c r="BW8">
+        <v>9</v>
+      </c>
+      <c r="BX8">
+        <v>19.5</v>
+      </c>
+      <c r="BY8">
+        <v>13.5</v>
+      </c>
+      <c r="BZ8">
+        <v>12.5</v>
+      </c>
+      <c r="CA8">
+        <v>8.6</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Peruvian Primera Division</t>
   </si>
   <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
     <t>Canadian Premier League</t>
   </si>
   <si>
@@ -286,6 +289,9 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -304,6 +310,9 @@
     <t>Cienciano</t>
   </si>
   <si>
+    <t>Union San Felipe</t>
+  </si>
+  <si>
     <t>Atletico Ottawa</t>
   </si>
   <si>
@@ -325,6 +334,9 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
+    <t>San Luis</t>
+  </si>
+  <si>
     <t>Cavalry</t>
   </si>
   <si>
@@ -334,7 +346,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 01:21:48</t>
+    <t>2026-09-29 03:32:40</t>
   </si>
 </sst>
 </file>
@@ -666,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -916,31 +928,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I2">
         <v>3.4</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.55</v>
@@ -952,13 +964,13 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
@@ -982,16 +994,16 @@
         <v>1.66</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB2">
         <v>10.5</v>
@@ -1000,10 +1012,10 @@
         <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF2">
         <v>16</v>
@@ -1012,40 +1024,40 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK2">
         <v>28</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN2">
         <v>23</v>
       </c>
       <c r="AO2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP2">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AT2">
         <v>8.800000000000001</v>
@@ -1057,100 +1069,100 @@
         <v>12</v>
       </c>
       <c r="AW2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BB2">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BC2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BE2">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1158,37 +1170,37 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H3">
         <v>2.82</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M3">
         <v>1.04</v>
@@ -1200,16 +1212,16 @@
         <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q3">
         <v>1.62</v>
       </c>
       <c r="R3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S3">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T3">
         <v>1.56</v>
@@ -1218,10 +1230,10 @@
         <v>2.46</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
         <v>25</v>
@@ -1248,10 +1260,10 @@
         <v>32</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
         <v>16</v>
@@ -1353,7 +1365,7 @@
         <v>7.8</v>
       </c>
       <c r="BO3">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
         <v>23</v>
@@ -1392,7 +1404,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1400,31 +1412,31 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="I4">
         <v>1.94</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>4.3</v>
@@ -1436,22 +1448,22 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q4">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="T4">
         <v>1.65</v>
@@ -1463,7 +1475,7 @@
         <v>2.06</v>
       </c>
       <c r="W4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X4">
         <v>25</v>
@@ -1481,7 +1493,7 @@
         <v>21</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD4">
         <v>11</v>
@@ -1490,10 +1502,10 @@
         <v>19</v>
       </c>
       <c r="AF4">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AG4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH4">
         <v>18</v>
@@ -1508,16 +1520,16 @@
         <v>60</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP4">
         <v>17.5</v>
@@ -1532,10 +1544,10 @@
         <v>17</v>
       </c>
       <c r="AT4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
         <v>8.800000000000001</v>
@@ -1544,7 +1556,7 @@
         <v>15</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY4">
         <v>15</v>
@@ -1556,22 +1568,22 @@
         <v>21</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1580,7 +1592,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
@@ -1592,49 +1604,49 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1642,16 +1654,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F5">
         <v>1.4</v>
@@ -1663,7 +1675,7 @@
         <v>7.4</v>
       </c>
       <c r="I5">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
         <v>5.1</v>
@@ -1684,7 +1696,7 @@
         <v>1.16</v>
       </c>
       <c r="P5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q5">
         <v>1.4</v>
@@ -1693,16 +1705,16 @@
         <v>1.71</v>
       </c>
       <c r="S5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T5">
         <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -1756,7 +1768,7 @@
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO5">
         <v>100</v>
@@ -1765,7 +1777,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR5">
         <v>1.01</v>
@@ -1774,13 +1786,13 @@
         <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>10.5</v>
+        <v>1.02</v>
       </c>
       <c r="AU5">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.02</v>
+        <v>7.6</v>
       </c>
       <c r="AW5">
         <v>1.01</v>
@@ -1804,7 +1816,7 @@
         <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BE5">
         <v>1.01</v>
@@ -1837,19 +1849,19 @@
         <v>6</v>
       </c>
       <c r="BO5">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BP5">
         <v>12</v>
       </c>
       <c r="BQ5">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>29</v>
       </c>
       <c r="BS5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
         <v>16</v>
@@ -1876,7 +1888,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1884,160 +1896,160 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="G6">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="I6">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="K6">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
         <v>1.01</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q6">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="R6">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>1.02</v>
       </c>
       <c r="T6">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
         <v>1.01</v>
@@ -2055,7 +2067,7 @@
         <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2112,13 +2124,13 @@
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2126,166 +2138,166 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="G7">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="H7">
-        <v>2.44</v>
+        <v>1.76</v>
       </c>
       <c r="I7">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S7">
-        <v>3.85</v>
+        <v>2.74</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="V7">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="W7">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="X7">
+        <v>24</v>
+      </c>
+      <c r="Y7">
+        <v>13</v>
+      </c>
+      <c r="Z7">
         <v>15</v>
       </c>
-      <c r="Y7">
-        <v>10.5</v>
-      </c>
-      <c r="Z7">
-        <v>16</v>
-      </c>
       <c r="AA7">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AB7">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD7">
         <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AF7">
+        <v>44</v>
+      </c>
+      <c r="AG7">
         <v>23</v>
       </c>
-      <c r="AG7">
-        <v>15</v>
-      </c>
       <c r="AH7">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AK7">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AL7">
         <v>65</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AN7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AO7">
+        <v>12</v>
+      </c>
+      <c r="AP7">
+        <v>14</v>
+      </c>
+      <c r="AQ7">
+        <v>7.8</v>
+      </c>
+      <c r="AR7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS7">
+        <v>14.5</v>
+      </c>
+      <c r="AT7">
+        <v>13.5</v>
+      </c>
+      <c r="AU7">
+        <v>7</v>
+      </c>
+      <c r="AV7">
+        <v>7.6</v>
+      </c>
+      <c r="AW7">
+        <v>13</v>
+      </c>
+      <c r="AX7">
         <v>26</v>
       </c>
-      <c r="AP7">
-        <v>11</v>
-      </c>
-      <c r="AQ7">
-        <v>8.6</v>
-      </c>
-      <c r="AR7">
-        <v>13.5</v>
-      </c>
-      <c r="AS7">
-        <v>1.01</v>
-      </c>
-      <c r="AT7">
-        <v>10</v>
-      </c>
-      <c r="AU7">
-        <v>6.8</v>
-      </c>
-      <c r="AV7">
-        <v>10.5</v>
-      </c>
-      <c r="AW7">
-        <v>1.01</v>
-      </c>
-      <c r="AX7">
-        <v>18</v>
-      </c>
       <c r="AY7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BB7">
         <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
         <v>1.01</v>
@@ -2297,70 +2309,70 @@
         <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
         <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
         <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
         <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2368,241 +2380,483 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G8">
+        <v>3.4</v>
+      </c>
+      <c r="H8">
+        <v>2.42</v>
+      </c>
+      <c r="I8">
+        <v>2.6</v>
+      </c>
+      <c r="J8">
+        <v>3.3</v>
+      </c>
+      <c r="K8">
         <v>3.6</v>
       </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8">
+      <c r="L8">
+        <v>1.44</v>
+      </c>
+      <c r="M8">
+        <v>1.08</v>
+      </c>
+      <c r="N8">
+        <v>3.35</v>
+      </c>
+      <c r="O8">
+        <v>1.37</v>
+      </c>
+      <c r="P8">
+        <v>1.8</v>
+      </c>
+      <c r="Q8">
+        <v>2.1</v>
+      </c>
+      <c r="R8">
+        <v>1.31</v>
+      </c>
+      <c r="S8">
+        <v>3.85</v>
+      </c>
+      <c r="T8">
+        <v>1.84</v>
+      </c>
+      <c r="U8">
         <v>2.04</v>
       </c>
-      <c r="J8">
-        <v>4.3</v>
-      </c>
-      <c r="K8">
-        <v>4.6</v>
-      </c>
-      <c r="L8">
-        <v>1.23</v>
-      </c>
-      <c r="M8">
-        <v>1.02</v>
-      </c>
-      <c r="N8">
-        <v>7.2</v>
-      </c>
-      <c r="O8">
-        <v>1.14</v>
-      </c>
-      <c r="P8">
-        <v>3.05</v>
-      </c>
-      <c r="Q8">
-        <v>1.43</v>
-      </c>
-      <c r="R8">
-        <v>1.83</v>
-      </c>
-      <c r="S8">
-        <v>2.08</v>
-      </c>
-      <c r="T8">
-        <v>1.47</v>
-      </c>
-      <c r="U8">
-        <v>2.94</v>
-      </c>
       <c r="V8">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="W8">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X8">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="Y8">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA8">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AB8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AC8">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AF8">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AI8">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AL8">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AM8">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AN8">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="AO8">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="AP8">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AR8">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS8">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AT8">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AU8">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
         <v>10.5</v>
       </c>
       <c r="AW8">
+        <v>6</v>
+      </c>
+      <c r="AX8">
+        <v>18</v>
+      </c>
+      <c r="AY8">
+        <v>12</v>
+      </c>
+      <c r="AZ8">
+        <v>16</v>
+      </c>
+      <c r="BA8">
+        <v>6.6</v>
+      </c>
+      <c r="BB8">
+        <v>6.8</v>
+      </c>
+      <c r="BC8">
+        <v>32</v>
+      </c>
+      <c r="BD8">
+        <v>6.2</v>
+      </c>
+      <c r="BE8">
+        <v>6.6</v>
+      </c>
+      <c r="BF8">
+        <v>6.6</v>
+      </c>
+      <c r="BG8">
+        <v>21</v>
+      </c>
+      <c r="BH8">
+        <v>3.7</v>
+      </c>
+      <c r="BI8">
+        <v>2.56</v>
+      </c>
+      <c r="BJ8">
+        <v>12</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>160</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>7.4</v>
+      </c>
+      <c r="BO8">
+        <v>4.7</v>
+      </c>
+      <c r="BP8">
+        <v>32</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>48</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>6.4</v>
+      </c>
+      <c r="BU8">
+        <v>4.1</v>
+      </c>
+      <c r="BV8">
+        <v>24</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>42</v>
+      </c>
+      <c r="BY8">
+        <v>1.02</v>
+      </c>
+      <c r="BZ8">
+        <v>40</v>
+      </c>
+      <c r="CA8">
+        <v>1.02</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9">
+        <v>3.65</v>
+      </c>
+      <c r="G9">
+        <v>3.9</v>
+      </c>
+      <c r="H9">
+        <v>1.94</v>
+      </c>
+      <c r="I9">
+        <v>1.99</v>
+      </c>
+      <c r="J9">
+        <v>4.4</v>
+      </c>
+      <c r="K9">
+        <v>4.5</v>
+      </c>
+      <c r="L9">
+        <v>1.23</v>
+      </c>
+      <c r="M9">
+        <v>1.02</v>
+      </c>
+      <c r="N9">
+        <v>7.2</v>
+      </c>
+      <c r="O9">
+        <v>1.14</v>
+      </c>
+      <c r="P9">
+        <v>3.1</v>
+      </c>
+      <c r="Q9">
+        <v>1.43</v>
+      </c>
+      <c r="R9">
+        <v>1.84</v>
+      </c>
+      <c r="S9">
+        <v>2.08</v>
+      </c>
+      <c r="T9">
+        <v>1.46</v>
+      </c>
+      <c r="U9">
+        <v>2.94</v>
+      </c>
+      <c r="V9">
+        <v>2</v>
+      </c>
+      <c r="W9">
+        <v>1.34</v>
+      </c>
+      <c r="X9">
+        <v>34</v>
+      </c>
+      <c r="Y9">
+        <v>18</v>
+      </c>
+      <c r="Z9">
+        <v>18</v>
+      </c>
+      <c r="AA9">
+        <v>25</v>
+      </c>
+      <c r="AB9">
+        <v>26</v>
+      </c>
+      <c r="AC9">
+        <v>11</v>
+      </c>
+      <c r="AD9">
+        <v>11.5</v>
+      </c>
+      <c r="AE9">
+        <v>17.5</v>
+      </c>
+      <c r="AF9">
+        <v>36</v>
+      </c>
+      <c r="AG9">
+        <v>17</v>
+      </c>
+      <c r="AH9">
+        <v>14.5</v>
+      </c>
+      <c r="AI9">
+        <v>23</v>
+      </c>
+      <c r="AJ9">
+        <v>70</v>
+      </c>
+      <c r="AK9">
+        <v>36</v>
+      </c>
+      <c r="AL9">
+        <v>36</v>
+      </c>
+      <c r="AM9">
+        <v>46</v>
+      </c>
+      <c r="AN9">
+        <v>20</v>
+      </c>
+      <c r="AO9">
+        <v>7.4</v>
+      </c>
+      <c r="AP9">
+        <v>23</v>
+      </c>
+      <c r="AQ9">
+        <v>15</v>
+      </c>
+      <c r="AR9">
+        <v>15.5</v>
+      </c>
+      <c r="AS9">
+        <v>22</v>
+      </c>
+      <c r="AT9">
+        <v>24</v>
+      </c>
+      <c r="AU9">
+        <v>10</v>
+      </c>
+      <c r="AV9">
+        <v>10</v>
+      </c>
+      <c r="AW9">
+        <v>15</v>
+      </c>
+      <c r="AX9">
+        <v>29</v>
+      </c>
+      <c r="AY9">
+        <v>15</v>
+      </c>
+      <c r="AZ9">
         <v>13</v>
       </c>
-      <c r="AX8">
-        <v>21</v>
-      </c>
-      <c r="AY8">
+      <c r="BA9">
+        <v>20</v>
+      </c>
+      <c r="BB9">
+        <v>55</v>
+      </c>
+      <c r="BC9">
+        <v>28</v>
+      </c>
+      <c r="BD9">
+        <v>29</v>
+      </c>
+      <c r="BE9">
+        <v>38</v>
+      </c>
+      <c r="BF9">
+        <v>17.5</v>
+      </c>
+      <c r="BG9">
+        <v>6.6</v>
+      </c>
+      <c r="BH9">
+        <v>5.4</v>
+      </c>
+      <c r="BI9">
+        <v>4</v>
+      </c>
+      <c r="BJ9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK9">
+        <v>6.2</v>
+      </c>
+      <c r="BL9">
+        <v>65</v>
+      </c>
+      <c r="BM9">
+        <v>42</v>
+      </c>
+      <c r="BN9">
+        <v>8</v>
+      </c>
+      <c r="BO9">
+        <v>5.8</v>
+      </c>
+      <c r="BP9">
+        <v>25</v>
+      </c>
+      <c r="BQ9">
+        <v>16.5</v>
+      </c>
+      <c r="BR9">
+        <v>27</v>
+      </c>
+      <c r="BS9">
+        <v>18.5</v>
+      </c>
+      <c r="BT9">
+        <v>5.8</v>
+      </c>
+      <c r="BU9">
+        <v>4.2</v>
+      </c>
+      <c r="BV9">
+        <v>13</v>
+      </c>
+      <c r="BW9">
+        <v>9</v>
+      </c>
+      <c r="BX9">
+        <v>19.5</v>
+      </c>
+      <c r="BY9">
         <v>13.5</v>
       </c>
-      <c r="AZ8">
-        <v>13</v>
-      </c>
-      <c r="BA8">
-        <v>20</v>
-      </c>
-      <c r="BB8">
-        <v>32</v>
-      </c>
-      <c r="BC8">
-        <v>20</v>
-      </c>
-      <c r="BD8">
-        <v>20</v>
-      </c>
-      <c r="BE8">
-        <v>26</v>
-      </c>
-      <c r="BF8">
-        <v>16</v>
-      </c>
-      <c r="BG8">
-        <v>6.8</v>
-      </c>
-      <c r="BH8">
-        <v>5.4</v>
-      </c>
-      <c r="BI8">
-        <v>4</v>
-      </c>
-      <c r="BJ8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK8">
-        <v>6.2</v>
-      </c>
-      <c r="BL8">
-        <v>65</v>
-      </c>
-      <c r="BM8">
-        <v>42</v>
-      </c>
-      <c r="BN8">
-        <v>8</v>
-      </c>
-      <c r="BO8">
-        <v>5.8</v>
-      </c>
-      <c r="BP8">
-        <v>25</v>
-      </c>
-      <c r="BQ8">
-        <v>16.5</v>
-      </c>
-      <c r="BR8">
-        <v>27</v>
-      </c>
-      <c r="BS8">
-        <v>18.5</v>
-      </c>
-      <c r="BT8">
-        <v>5.8</v>
-      </c>
-      <c r="BU8">
-        <v>4.2</v>
-      </c>
-      <c r="BV8">
-        <v>13</v>
-      </c>
-      <c r="BW8">
-        <v>9</v>
-      </c>
-      <c r="BX8">
-        <v>19.5</v>
-      </c>
-      <c r="BY8">
-        <v>13.5</v>
-      </c>
-      <c r="BZ8">
+      <c r="BZ9">
         <v>12.5</v>
       </c>
-      <c r="CA8">
+      <c r="CA9">
         <v>8.6</v>
       </c>
-      <c r="CB8" t="s">
-        <v>106</v>
+      <c r="CB9" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -346,7 +346,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 03:32:40</t>
+    <t>2026-09-29 05:48:08</t>
   </si>
 </sst>
 </file>
@@ -940,16 +940,16 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J2">
         <v>3.3</v>
@@ -958,7 +958,7 @@
         <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -967,7 +967,7 @@
         <v>3.7</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
         <v>1.89</v>
@@ -982,181 +982,181 @@
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.66</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AE2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
+        <v>9</v>
+      </c>
+      <c r="AQ2">
+        <v>9.4</v>
+      </c>
+      <c r="AR2">
+        <v>2.82</v>
+      </c>
+      <c r="AS2">
+        <v>3.05</v>
+      </c>
+      <c r="AT2">
+        <v>8.4</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>3</v>
+      </c>
+      <c r="AX2">
         <v>11.5</v>
       </c>
-      <c r="AQ2">
-        <v>10.5</v>
-      </c>
-      <c r="AR2">
-        <v>20</v>
-      </c>
-      <c r="AS2">
-        <v>40</v>
-      </c>
-      <c r="AT2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU2">
-        <v>6.8</v>
-      </c>
-      <c r="AV2">
-        <v>12</v>
-      </c>
-      <c r="AW2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX2">
-        <v>13.5</v>
-      </c>
       <c r="AY2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>2.98</v>
       </c>
       <c r="BC2">
-        <v>7.6</v>
+        <v>2.88</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>3.15</v>
       </c>
       <c r="BF2">
-        <v>19</v>
+        <v>3.15</v>
       </c>
       <c r="BG2">
-        <v>23</v>
+        <v>3.15</v>
       </c>
       <c r="BH2">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1182,19 +1182,19 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K3">
         <v>4.1</v>
@@ -1215,7 +1215,7 @@
         <v>2.34</v>
       </c>
       <c r="Q3">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="R3">
         <v>1.54</v>
@@ -1224,103 +1224,103 @@
         <v>2.56</v>
       </c>
       <c r="T3">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="U3">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="V3">
         <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH3">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AO3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
         <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3">
+        <v>1.01</v>
+      </c>
+      <c r="AV3">
+        <v>1.01</v>
+      </c>
+      <c r="AW3">
+        <v>1.01</v>
+      </c>
+      <c r="AX3">
+        <v>1.01</v>
+      </c>
+      <c r="AY3">
         <v>8</v>
       </c>
-      <c r="AV3">
-        <v>11.5</v>
-      </c>
-      <c r="AW3">
-        <v>1.01</v>
-      </c>
-      <c r="AX3">
-        <v>15.5</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
       <c r="AZ3">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA3">
         <v>1.01</v>
@@ -1329,7 +1329,7 @@
         <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
         <v>1.01</v>
@@ -1338,10 +1338,10 @@
         <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1350,55 +1350,55 @@
         <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1424,166 +1424,166 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="G4">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="H4">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="I4">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
+        <v>1.22</v>
+      </c>
+      <c r="P4">
+        <v>2.26</v>
+      </c>
+      <c r="Q4">
+        <v>1.63</v>
+      </c>
+      <c r="R4">
+        <v>1.47</v>
+      </c>
+      <c r="S4">
+        <v>2.56</v>
+      </c>
+      <c r="T4">
+        <v>1.6</v>
+      </c>
+      <c r="U4">
+        <v>2.28</v>
+      </c>
+      <c r="V4">
+        <v>1.99</v>
+      </c>
+      <c r="W4">
         <v>1.23</v>
       </c>
-      <c r="P4">
-        <v>2.24</v>
-      </c>
-      <c r="Q4">
-        <v>1.66</v>
-      </c>
-      <c r="R4">
-        <v>1.5</v>
-      </c>
-      <c r="S4">
-        <v>2.66</v>
-      </c>
-      <c r="T4">
-        <v>1.65</v>
-      </c>
-      <c r="U4">
-        <v>2.26</v>
-      </c>
-      <c r="V4">
-        <v>2.06</v>
-      </c>
-      <c r="W4">
-        <v>1.26</v>
-      </c>
       <c r="X4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z4">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD4">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
+        <v>30</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
         <v>44</v>
       </c>
-      <c r="AG4">
-        <v>19</v>
-      </c>
-      <c r="AH4">
-        <v>18</v>
-      </c>
-      <c r="AI4">
-        <v>32</v>
-      </c>
-      <c r="AJ4">
-        <v>110</v>
-      </c>
-      <c r="AK4">
-        <v>60</v>
-      </c>
       <c r="AL4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AP4">
-        <v>17.5</v>
+        <v>1.49</v>
       </c>
       <c r="AQ4">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="AR4">
-        <v>11</v>
+        <v>1.41</v>
       </c>
       <c r="AS4">
-        <v>17</v>
+        <v>1.49</v>
       </c>
       <c r="AT4">
-        <v>17</v>
+        <v>1.49</v>
       </c>
       <c r="AU4">
-        <v>8.4</v>
+        <v>1.35</v>
       </c>
       <c r="AV4">
-        <v>8.800000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="AW4">
-        <v>15</v>
+        <v>1.49</v>
       </c>
       <c r="AX4">
-        <v>5.9</v>
+        <v>1.42</v>
       </c>
       <c r="AY4">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>14.5</v>
+        <v>1.49</v>
       </c>
       <c r="BA4">
-        <v>21</v>
+        <v>1.49</v>
       </c>
       <c r="BB4">
-        <v>6</v>
+        <v>1.49</v>
       </c>
       <c r="BC4">
-        <v>6.2</v>
+        <v>1.44</v>
       </c>
       <c r="BD4">
-        <v>6.4</v>
+        <v>1.49</v>
       </c>
       <c r="BE4">
-        <v>6.2</v>
+        <v>1.49</v>
       </c>
       <c r="BF4">
-        <v>6.2</v>
+        <v>1.49</v>
       </c>
       <c r="BG4">
-        <v>8.199999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1666,22 +1666,22 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G5">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>1.36</v>
       </c>
       <c r="I5">
-        <v>8.6</v>
+        <v>15.5</v>
       </c>
       <c r="J5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="K5">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1690,22 +1690,22 @@
         <v>1.02</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>2.58</v>
       </c>
       <c r="O5">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="P5">
-        <v>2.74</v>
+        <v>2.22</v>
       </c>
       <c r="Q5">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="R5">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="T5">
         <v>1.6</v>
@@ -1714,115 +1714,115 @@
         <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="W5">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="X5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
         <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>22</v>
+        <v>2.16</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AT5">
+        <v>3.65</v>
+      </c>
+      <c r="AU5">
+        <v>3.7</v>
+      </c>
+      <c r="AV5">
         <v>1.02</v>
       </c>
-      <c r="AU5">
-        <v>1.01</v>
-      </c>
-      <c r="AV5">
-        <v>7.6</v>
-      </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX5">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BA5">
         <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>1.87</v>
       </c>
       <c r="BC5">
         <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
         <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
         <v>1.01</v>
@@ -1834,7 +1834,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
@@ -1846,43 +1846,43 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
         <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
         <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -1911,19 +1911,19 @@
         <v>1.1</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H6">
         <v>1.1</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="J6">
         <v>1.1</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1932,22 +1932,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
         <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2153,145 +2153,145 @@
         <v>3.95</v>
       </c>
       <c r="G7">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="H7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I7">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
         <v>1.01</v>
       </c>
       <c r="O7">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="T7">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="W7">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
         <v>1.01</v>
@@ -2309,7 +2309,7 @@
         <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2392,226 +2392,226 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H8">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="I8">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="J8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
         <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R8">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="U8">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="V8">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W8">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X8">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC8">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8">
-        <v>8.6</v>
+        <v>1.19</v>
       </c>
       <c r="AR8">
-        <v>13.5</v>
+        <v>1.28</v>
       </c>
       <c r="AS8">
-        <v>6.2</v>
+        <v>1.28</v>
       </c>
       <c r="AT8">
-        <v>10</v>
+        <v>1.23</v>
       </c>
       <c r="AU8">
-        <v>6.8</v>
+        <v>1.15</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>1.23</v>
       </c>
       <c r="AW8">
-        <v>6</v>
+        <v>1.28</v>
       </c>
       <c r="AX8">
-        <v>18</v>
+        <v>1.28</v>
       </c>
       <c r="AY8">
-        <v>12</v>
+        <v>1.28</v>
       </c>
       <c r="AZ8">
-        <v>16</v>
+        <v>1.28</v>
       </c>
       <c r="BA8">
-        <v>6.6</v>
+        <v>1.28</v>
       </c>
       <c r="BB8">
-        <v>6.8</v>
+        <v>1.28</v>
       </c>
       <c r="BC8">
-        <v>32</v>
+        <v>1.28</v>
       </c>
       <c r="BD8">
-        <v>6.2</v>
+        <v>1.28</v>
       </c>
       <c r="BE8">
-        <v>6.6</v>
+        <v>1.28</v>
       </c>
       <c r="BF8">
-        <v>6.6</v>
+        <v>1.28</v>
       </c>
       <c r="BG8">
-        <v>21</v>
+        <v>1.28</v>
       </c>
       <c r="BH8">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
         <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
         <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
         <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>110</v>
@@ -2640,16 +2640,16 @@
         <v>3.9</v>
       </c>
       <c r="H9">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I9">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J9">
         <v>4.4</v>
       </c>
       <c r="K9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
         <v>1.23</v>
@@ -2658,19 +2658,19 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P9">
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S9">
         <v>2.08</v>
@@ -2679,10 +2679,10 @@
         <v>1.46</v>
       </c>
       <c r="U9">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W9">
         <v>1.34</v>
@@ -2691,61 +2691,61 @@
         <v>34</v>
       </c>
       <c r="Y9">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Z9">
         <v>18</v>
       </c>
       <c r="AA9">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AB9">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AC9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD9">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF9">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AG9">
         <v>17</v>
       </c>
       <c r="AH9">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AI9">
         <v>23</v>
       </c>
       <c r="AJ9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
         <v>36</v>
       </c>
       <c r="AL9">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AM9">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AN9">
         <v>20</v>
       </c>
       <c r="AO9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AP9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR9">
         <v>15.5</v>
@@ -2763,13 +2763,13 @@
         <v>10</v>
       </c>
       <c r="AW9">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AX9">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AY9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ9">
         <v>13</v>
@@ -2778,82 +2778,82 @@
         <v>20</v>
       </c>
       <c r="BB9">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BC9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BD9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE9">
         <v>38</v>
       </c>
       <c r="BF9">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG9">
         <v>6.6</v>
       </c>
       <c r="BH9">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>110</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
     <t>English National League</t>
   </si>
   <si>
@@ -283,6 +286,9 @@
     <t>01:05:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>18:45:00</t>
   </si>
   <si>
@@ -301,6 +307,9 @@
     <t>Ind Medellin</t>
   </si>
   <si>
+    <t>Belize</t>
+  </si>
+  <si>
     <t>Tamworth FC</t>
   </si>
   <si>
@@ -325,6 +334,9 @@
     <t>Millonarios</t>
   </si>
   <si>
+    <t>St Vincent &amp; Grenadines</t>
+  </si>
+  <si>
     <t>Sutton Utd</t>
   </si>
   <si>
@@ -346,7 +358,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 05:48:08</t>
+    <t>2026-09-29 07:59:09</t>
   </si>
 </sst>
 </file>
@@ -678,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -928,49 +940,49 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I2">
         <v>3.45</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
         <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
         <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
@@ -979,190 +991,190 @@
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="U2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
         <v>27</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB2">
+        <v>10.5</v>
+      </c>
+      <c r="AC2">
+        <v>7.8</v>
+      </c>
+      <c r="AD2">
+        <v>14.5</v>
+      </c>
+      <c r="AE2">
+        <v>48</v>
+      </c>
+      <c r="AF2">
+        <v>15.5</v>
+      </c>
+      <c r="AG2">
+        <v>11.5</v>
+      </c>
+      <c r="AH2">
+        <v>18</v>
+      </c>
+      <c r="AI2">
+        <v>60</v>
+      </c>
+      <c r="AJ2">
+        <v>36</v>
+      </c>
+      <c r="AK2">
+        <v>27</v>
+      </c>
+      <c r="AL2">
+        <v>48</v>
+      </c>
+      <c r="AM2">
+        <v>120</v>
+      </c>
+      <c r="AN2">
+        <v>22</v>
+      </c>
+      <c r="AO2">
+        <v>46</v>
+      </c>
+      <c r="AP2">
+        <v>12</v>
+      </c>
+      <c r="AQ2">
+        <v>11</v>
+      </c>
+      <c r="AR2">
+        <v>20</v>
+      </c>
+      <c r="AS2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT2">
+        <v>9</v>
+      </c>
+      <c r="AU2">
+        <v>7</v>
+      </c>
+      <c r="AV2">
         <v>12.5</v>
       </c>
-      <c r="AC2">
+      <c r="AW2">
         <v>9</v>
       </c>
-      <c r="AD2">
-        <v>17</v>
-      </c>
-      <c r="AE2">
-        <v>55</v>
-      </c>
-      <c r="AF2">
-        <v>19.5</v>
-      </c>
-      <c r="AG2">
+      <c r="AX2">
         <v>13.5</v>
       </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>65</v>
-      </c>
-      <c r="AJ2">
-        <v>48</v>
-      </c>
-      <c r="AK2">
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>15.5</v>
+      </c>
+      <c r="BA2">
+        <v>8.6</v>
+      </c>
+      <c r="BB2">
+        <v>22</v>
+      </c>
+      <c r="BC2">
+        <v>19</v>
+      </c>
+      <c r="BD2">
         <v>34</v>
       </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>1000</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>9</v>
-      </c>
-      <c r="AQ2">
+      <c r="BE2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF2">
+        <v>18.5</v>
+      </c>
+      <c r="BG2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH2">
+        <v>3.75</v>
+      </c>
+      <c r="BI2">
+        <v>2.78</v>
+      </c>
+      <c r="BJ2">
         <v>9.4</v>
       </c>
-      <c r="AR2">
-        <v>2.82</v>
-      </c>
-      <c r="AS2">
-        <v>3.05</v>
-      </c>
-      <c r="AT2">
-        <v>8.4</v>
-      </c>
-      <c r="AU2">
+      <c r="BK2">
+        <v>7.4</v>
+      </c>
+      <c r="BL2">
+        <v>140</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>5.3</v>
+      </c>
+      <c r="BO2">
+        <v>4.2</v>
+      </c>
+      <c r="BP2">
+        <v>17.5</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>36</v>
+      </c>
+      <c r="BS2">
+        <v>1.02</v>
+      </c>
+      <c r="BT2">
         <v>6.6</v>
       </c>
-      <c r="AV2">
-        <v>11</v>
-      </c>
-      <c r="AW2">
-        <v>3</v>
-      </c>
-      <c r="AX2">
-        <v>11.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>3</v>
-      </c>
-      <c r="BB2">
-        <v>2.98</v>
-      </c>
-      <c r="BC2">
-        <v>2.88</v>
-      </c>
-      <c r="BD2">
-        <v>3</v>
-      </c>
-      <c r="BE2">
-        <v>3.15</v>
-      </c>
-      <c r="BF2">
-        <v>3.15</v>
-      </c>
-      <c r="BG2">
-        <v>3.15</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.01</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>1.01</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.01</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>1.01</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>1.01</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.01</v>
-      </c>
-      <c r="BT2">
-        <v>1000</v>
-      </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1170,276 +1182,276 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.52</v>
+        <v>2.94</v>
       </c>
       <c r="H3">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="J3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="Q3">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="R3">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="S3">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="U3">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC3">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN3">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY3">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BF3">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM3">
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F4">
-        <v>3.95</v>
+        <v>2.28</v>
       </c>
       <c r="G4">
-        <v>5.2</v>
+        <v>2.56</v>
       </c>
       <c r="H4">
-        <v>1.77</v>
+        <v>2.84</v>
       </c>
       <c r="I4">
-        <v>2.02</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.28</v>
@@ -1448,205 +1460,205 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="S4">
         <v>2.56</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="V4">
-        <v>1.99</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y4">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z4">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC4">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF4">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK4">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO4">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AP4">
-        <v>1.49</v>
+        <v>18</v>
       </c>
       <c r="AQ4">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="AR4">
-        <v>1.41</v>
+        <v>17.5</v>
       </c>
       <c r="AS4">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.49</v>
+        <v>12</v>
       </c>
       <c r="AU4">
-        <v>1.35</v>
+        <v>8</v>
       </c>
       <c r="AV4">
-        <v>1.37</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.42</v>
+        <v>15.5</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>1.49</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.44</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>1.49</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>1.35</v>
+        <v>17</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1654,241 +1666,241 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="G5">
-        <v>1.53</v>
+        <v>4.6</v>
       </c>
       <c r="H5">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="I5">
+        <v>1.94</v>
+      </c>
+      <c r="J5">
+        <v>3.9</v>
+      </c>
+      <c r="K5">
+        <v>4.3</v>
+      </c>
+      <c r="L5">
+        <v>1.28</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>4.7</v>
+      </c>
+      <c r="O5">
+        <v>1.23</v>
+      </c>
+      <c r="P5">
+        <v>2.26</v>
+      </c>
+      <c r="Q5">
+        <v>1.66</v>
+      </c>
+      <c r="R5">
+        <v>1.5</v>
+      </c>
+      <c r="S5">
+        <v>2.68</v>
+      </c>
+      <c r="T5">
+        <v>1.65</v>
+      </c>
+      <c r="U5">
+        <v>2.28</v>
+      </c>
+      <c r="V5">
+        <v>2.06</v>
+      </c>
+      <c r="W5">
+        <v>1.27</v>
+      </c>
+      <c r="X5">
+        <v>25</v>
+      </c>
+      <c r="Y5">
+        <v>12</v>
+      </c>
+      <c r="Z5">
         <v>15.5</v>
       </c>
-      <c r="J5">
+      <c r="AA5">
+        <v>25</v>
+      </c>
+      <c r="AB5">
+        <v>21</v>
+      </c>
+      <c r="AC5">
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <v>11</v>
+      </c>
+      <c r="AE5">
+        <v>22</v>
+      </c>
+      <c r="AF5">
+        <v>38</v>
+      </c>
+      <c r="AG5">
+        <v>22</v>
+      </c>
+      <c r="AH5">
+        <v>18</v>
+      </c>
+      <c r="AI5">
+        <v>32</v>
+      </c>
+      <c r="AJ5">
+        <v>110</v>
+      </c>
+      <c r="AK5">
+        <v>60</v>
+      </c>
+      <c r="AL5">
+        <v>65</v>
+      </c>
+      <c r="AM5">
+        <v>95</v>
+      </c>
+      <c r="AN5">
+        <v>55</v>
+      </c>
+      <c r="AO5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP5">
+        <v>17.5</v>
+      </c>
+      <c r="AQ5">
+        <v>9.6</v>
+      </c>
+      <c r="AR5">
+        <v>11</v>
+      </c>
+      <c r="AS5">
+        <v>17.5</v>
+      </c>
+      <c r="AT5">
+        <v>16.5</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>9</v>
+      </c>
+      <c r="AW5">
+        <v>15</v>
+      </c>
+      <c r="AX5">
+        <v>6</v>
+      </c>
+      <c r="AY5">
+        <v>15</v>
+      </c>
+      <c r="AZ5">
+        <v>14.5</v>
+      </c>
+      <c r="BA5">
+        <v>5.9</v>
+      </c>
+      <c r="BB5">
+        <v>6.8</v>
+      </c>
+      <c r="BC5">
+        <v>6.2</v>
+      </c>
+      <c r="BD5">
+        <v>6.4</v>
+      </c>
+      <c r="BE5">
+        <v>6.6</v>
+      </c>
+      <c r="BF5">
+        <v>6.4</v>
+      </c>
+      <c r="BG5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH5">
         <v>4.7</v>
       </c>
-      <c r="K5">
-        <v>950</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
+      <c r="BI5">
+        <v>3.15</v>
+      </c>
+      <c r="BJ5">
+        <v>11</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>120</v>
+      </c>
+      <c r="BM5">
         <v>1.02</v>
       </c>
-      <c r="N5">
-        <v>2.58</v>
-      </c>
-      <c r="O5">
-        <v>1.13</v>
-      </c>
-      <c r="P5">
-        <v>2.22</v>
-      </c>
-      <c r="Q5">
-        <v>1.45</v>
-      </c>
-      <c r="R5">
-        <v>1.52</v>
-      </c>
-      <c r="S5">
-        <v>2.14</v>
-      </c>
-      <c r="T5">
-        <v>1.6</v>
-      </c>
-      <c r="U5">
-        <v>2.18</v>
-      </c>
-      <c r="V5">
-        <v>1.07</v>
-      </c>
-      <c r="W5">
-        <v>2.84</v>
-      </c>
-      <c r="X5">
-        <v>1000</v>
-      </c>
-      <c r="Y5">
-        <v>1000</v>
-      </c>
-      <c r="Z5">
-        <v>1000</v>
-      </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
-        <v>1000</v>
-      </c>
-      <c r="AC5">
-        <v>1000</v>
-      </c>
-      <c r="AD5">
-        <v>1000</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>1000</v>
-      </c>
-      <c r="AG5">
-        <v>1000</v>
-      </c>
-      <c r="AH5">
-        <v>1000</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>1000</v>
-      </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>1.01</v>
-      </c>
-      <c r="AQ5">
-        <v>2.16</v>
-      </c>
-      <c r="AR5">
-        <v>1.56</v>
-      </c>
-      <c r="AS5">
-        <v>1.65</v>
-      </c>
-      <c r="AT5">
-        <v>3.65</v>
-      </c>
-      <c r="AU5">
+      <c r="BN5">
+        <v>9.6</v>
+      </c>
+      <c r="BO5">
+        <v>6</v>
+      </c>
+      <c r="BP5">
+        <v>40</v>
+      </c>
+      <c r="BQ5">
+        <v>1.02</v>
+      </c>
+      <c r="BR5">
+        <v>46</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>5.6</v>
+      </c>
+      <c r="BU5">
         <v>3.7</v>
       </c>
-      <c r="AV5">
-        <v>1.02</v>
-      </c>
-      <c r="AW5">
-        <v>1.02</v>
-      </c>
-      <c r="AX5">
-        <v>1.01</v>
-      </c>
-      <c r="AY5">
-        <v>1.01</v>
-      </c>
-      <c r="AZ5">
-        <v>2.92</v>
-      </c>
-      <c r="BA5">
-        <v>1.01</v>
-      </c>
-      <c r="BB5">
-        <v>1.87</v>
-      </c>
-      <c r="BC5">
-        <v>1.01</v>
-      </c>
-      <c r="BD5">
-        <v>1.01</v>
-      </c>
-      <c r="BE5">
-        <v>1.01</v>
-      </c>
-      <c r="BF5">
-        <v>1.01</v>
-      </c>
-      <c r="BG5">
-        <v>1.01</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.01</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.01</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.01</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.01</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.01</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.01</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.01</v>
-      </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1896,178 +1908,178 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G6">
+        <v>1.48</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
+      </c>
+      <c r="I6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5.9</v>
+      </c>
+      <c r="L6">
+        <v>1.21</v>
+      </c>
+      <c r="M6">
+        <v>1.02</v>
+      </c>
+      <c r="N6">
+        <v>6.2</v>
+      </c>
+      <c r="O6">
+        <v>1.16</v>
+      </c>
+      <c r="P6">
+        <v>2.76</v>
+      </c>
+      <c r="Q6">
+        <v>1.46</v>
+      </c>
+      <c r="R6">
+        <v>1.7</v>
+      </c>
+      <c r="S6">
+        <v>2.16</v>
+      </c>
+      <c r="T6">
+        <v>1.6</v>
+      </c>
+      <c r="U6">
+        <v>2.2</v>
+      </c>
+      <c r="V6">
+        <v>1.13</v>
+      </c>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <v>38</v>
+      </c>
+      <c r="Y6">
+        <v>38</v>
+      </c>
+      <c r="Z6">
+        <v>90</v>
+      </c>
+      <c r="AA6">
+        <v>250</v>
+      </c>
+      <c r="AB6">
+        <v>13</v>
+      </c>
+      <c r="AC6">
+        <v>14</v>
+      </c>
+      <c r="AD6">
+        <v>32</v>
+      </c>
+      <c r="AE6">
         <v>110</v>
       </c>
-      <c r="H6">
-        <v>1.1</v>
-      </c>
-      <c r="I6">
-        <v>140</v>
-      </c>
-      <c r="J6">
-        <v>1.1</v>
-      </c>
-      <c r="K6">
-        <v>900</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>1.26</v>
-      </c>
-      <c r="O6">
-        <v>1.01</v>
-      </c>
-      <c r="P6">
-        <v>1.26</v>
-      </c>
-      <c r="Q6">
-        <v>1.89</v>
-      </c>
-      <c r="R6">
-        <v>1.18</v>
-      </c>
-      <c r="S6">
-        <v>2.46</v>
-      </c>
-      <c r="T6">
-        <v>1.01</v>
-      </c>
-      <c r="U6">
-        <v>1.01</v>
-      </c>
-      <c r="V6">
-        <v>1.01</v>
-      </c>
-      <c r="W6">
-        <v>1.01</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>1000</v>
-      </c>
-      <c r="Z6">
-        <v>1000</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>1000</v>
-      </c>
-      <c r="AC6">
-        <v>1000</v>
-      </c>
-      <c r="AD6">
-        <v>1000</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2076,7 +2088,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
@@ -2088,49 +2100,49 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2138,241 +2150,241 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
         <v>3.95</v>
       </c>
-      <c r="G7">
-        <v>6.4</v>
-      </c>
       <c r="H7">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>2.82</v>
       </c>
       <c r="J7">
+        <v>3.15</v>
+      </c>
+      <c r="K7">
         <v>3.6</v>
       </c>
-      <c r="K7">
-        <v>5.8</v>
-      </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="O7">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q7">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S7">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="W7">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2380,241 +2392,241 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F8">
-        <v>2.86</v>
+        <v>3.95</v>
       </c>
       <c r="G8">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="H8">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="I8">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="J8">
         <v>3.25</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
+        <v>1.01</v>
+      </c>
+      <c r="O8">
+        <v>1.21</v>
+      </c>
+      <c r="P8">
+        <v>2.08</v>
+      </c>
+      <c r="Q8">
+        <v>1.68</v>
+      </c>
+      <c r="R8">
+        <v>1.45</v>
+      </c>
+      <c r="S8">
+        <v>2.62</v>
+      </c>
+      <c r="T8">
+        <v>1.58</v>
+      </c>
+      <c r="U8">
+        <v>2.16</v>
+      </c>
+      <c r="V8">
+        <v>1.99</v>
+      </c>
+      <c r="W8">
+        <v>1.21</v>
+      </c>
+      <c r="X8">
+        <v>24</v>
+      </c>
+      <c r="Y8">
+        <v>13</v>
+      </c>
+      <c r="Z8">
+        <v>15</v>
+      </c>
+      <c r="AA8">
+        <v>25</v>
+      </c>
+      <c r="AB8">
+        <v>23</v>
+      </c>
+      <c r="AC8">
+        <v>10</v>
+      </c>
+      <c r="AD8">
+        <v>12.5</v>
+      </c>
+      <c r="AE8">
+        <v>22</v>
+      </c>
+      <c r="AF8">
+        <v>44</v>
+      </c>
+      <c r="AG8">
+        <v>23</v>
+      </c>
+      <c r="AH8">
+        <v>22</v>
+      </c>
+      <c r="AI8">
+        <v>38</v>
+      </c>
+      <c r="AJ8">
+        <v>120</v>
+      </c>
+      <c r="AK8">
+        <v>65</v>
+      </c>
+      <c r="AL8">
+        <v>65</v>
+      </c>
+      <c r="AM8">
+        <v>100</v>
+      </c>
+      <c r="AN8">
+        <v>60</v>
+      </c>
+      <c r="AO8">
+        <v>12</v>
+      </c>
+      <c r="AP8">
+        <v>14</v>
+      </c>
+      <c r="AQ8">
+        <v>7.8</v>
+      </c>
+      <c r="AR8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS8">
+        <v>14.5</v>
+      </c>
+      <c r="AT8">
+        <v>13.5</v>
+      </c>
+      <c r="AU8">
+        <v>7</v>
+      </c>
+      <c r="AV8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW8">
+        <v>13</v>
+      </c>
+      <c r="AX8">
+        <v>26</v>
+      </c>
+      <c r="AY8">
+        <v>13</v>
+      </c>
+      <c r="AZ8">
+        <v>12.5</v>
+      </c>
+      <c r="BA8">
+        <v>22</v>
+      </c>
+      <c r="BB8">
+        <v>1.01</v>
+      </c>
+      <c r="BC8">
+        <v>1.01</v>
+      </c>
+      <c r="BD8">
+        <v>1.01</v>
+      </c>
+      <c r="BE8">
+        <v>1.01</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>8.4</v>
+      </c>
+      <c r="BH8">
+        <v>4.6</v>
+      </c>
+      <c r="BI8">
         <v>3.05</v>
       </c>
-      <c r="O8">
-        <v>1.37</v>
-      </c>
-      <c r="P8">
-        <v>1.73</v>
-      </c>
-      <c r="Q8">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <v>1.26</v>
-      </c>
-      <c r="S8">
-        <v>3.6</v>
-      </c>
-      <c r="T8">
-        <v>1.75</v>
-      </c>
-      <c r="U8">
-        <v>1.96</v>
-      </c>
-      <c r="V8">
-        <v>1.55</v>
-      </c>
-      <c r="W8">
-        <v>1.38</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>970</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>970</v>
-      </c>
-      <c r="AC8">
-        <v>970</v>
-      </c>
-      <c r="AD8">
-        <v>970</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>1000</v>
-      </c>
-      <c r="AG8">
-        <v>1000</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.28</v>
-      </c>
-      <c r="AQ8">
-        <v>1.19</v>
-      </c>
-      <c r="AR8">
-        <v>1.28</v>
-      </c>
-      <c r="AS8">
-        <v>1.28</v>
-      </c>
-      <c r="AT8">
-        <v>1.23</v>
-      </c>
-      <c r="AU8">
-        <v>1.15</v>
-      </c>
-      <c r="AV8">
-        <v>1.23</v>
-      </c>
-      <c r="AW8">
-        <v>1.28</v>
-      </c>
-      <c r="AX8">
-        <v>1.28</v>
-      </c>
-      <c r="AY8">
-        <v>1.28</v>
-      </c>
-      <c r="AZ8">
-        <v>1.28</v>
-      </c>
-      <c r="BA8">
-        <v>1.28</v>
-      </c>
-      <c r="BB8">
-        <v>1.28</v>
-      </c>
-      <c r="BC8">
-        <v>1.28</v>
-      </c>
-      <c r="BD8">
-        <v>1.28</v>
-      </c>
-      <c r="BE8">
-        <v>1.28</v>
-      </c>
-      <c r="BF8">
-        <v>1.28</v>
-      </c>
-      <c r="BG8">
-        <v>1.28</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.01</v>
-      </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM8">
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8">
         <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2622,241 +2634,483 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9">
+        <v>3.1</v>
+      </c>
+      <c r="G9">
+        <v>3.25</v>
+      </c>
+      <c r="H9">
+        <v>2.44</v>
+      </c>
+      <c r="I9">
+        <v>2.6</v>
+      </c>
+      <c r="J9">
+        <v>3.25</v>
+      </c>
+      <c r="K9">
+        <v>3.55</v>
+      </c>
+      <c r="L9">
+        <v>1.38</v>
+      </c>
+      <c r="M9">
+        <v>1.08</v>
+      </c>
+      <c r="N9">
+        <v>3.3</v>
+      </c>
+      <c r="O9">
+        <v>1.37</v>
+      </c>
+      <c r="P9">
+        <v>1.8</v>
+      </c>
+      <c r="Q9">
+        <v>2.1</v>
+      </c>
+      <c r="R9">
+        <v>1.31</v>
+      </c>
+      <c r="S9">
+        <v>3.85</v>
+      </c>
+      <c r="T9">
+        <v>1.87</v>
+      </c>
+      <c r="U9">
+        <v>2.02</v>
+      </c>
+      <c r="V9">
+        <v>1.62</v>
+      </c>
+      <c r="W9">
+        <v>1.44</v>
+      </c>
+      <c r="X9">
+        <v>15</v>
+      </c>
+      <c r="Y9">
+        <v>10.5</v>
+      </c>
+      <c r="Z9">
+        <v>16</v>
+      </c>
+      <c r="AA9">
+        <v>50</v>
+      </c>
+      <c r="AB9">
+        <v>14</v>
+      </c>
+      <c r="AC9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD9">
+        <v>12.5</v>
+      </c>
+      <c r="AE9">
+        <v>42</v>
+      </c>
+      <c r="AF9">
+        <v>23</v>
+      </c>
+      <c r="AG9">
+        <v>15</v>
+      </c>
+      <c r="AH9">
+        <v>19.5</v>
+      </c>
+      <c r="AI9">
+        <v>55</v>
+      </c>
+      <c r="AJ9">
+        <v>70</v>
+      </c>
+      <c r="AK9">
+        <v>50</v>
+      </c>
+      <c r="AL9">
+        <v>65</v>
+      </c>
+      <c r="AM9">
+        <v>140</v>
+      </c>
+      <c r="AN9">
+        <v>50</v>
+      </c>
+      <c r="AO9">
+        <v>27</v>
+      </c>
+      <c r="AP9">
+        <v>10.5</v>
+      </c>
+      <c r="AQ9">
+        <v>8.4</v>
+      </c>
+      <c r="AR9">
+        <v>13</v>
+      </c>
+      <c r="AS9">
+        <v>27</v>
+      </c>
+      <c r="AT9">
+        <v>10</v>
+      </c>
+      <c r="AU9">
+        <v>6.8</v>
+      </c>
+      <c r="AV9">
+        <v>10.5</v>
+      </c>
+      <c r="AW9">
+        <v>5.3</v>
+      </c>
+      <c r="AX9">
+        <v>18</v>
+      </c>
+      <c r="AY9">
+        <v>12</v>
+      </c>
+      <c r="AZ9">
+        <v>16</v>
+      </c>
+      <c r="BA9">
+        <v>34</v>
+      </c>
+      <c r="BB9">
+        <v>40</v>
+      </c>
+      <c r="BC9">
+        <v>24</v>
+      </c>
+      <c r="BD9">
+        <v>36</v>
+      </c>
+      <c r="BE9">
+        <v>5.8</v>
+      </c>
+      <c r="BF9">
+        <v>32</v>
+      </c>
+      <c r="BG9">
+        <v>21</v>
+      </c>
+      <c r="BH9">
+        <v>3.65</v>
+      </c>
+      <c r="BI9">
+        <v>2.56</v>
+      </c>
+      <c r="BJ9">
+        <v>12</v>
+      </c>
+      <c r="BK9">
+        <v>7.4</v>
+      </c>
+      <c r="BL9">
+        <v>170</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>6.6</v>
+      </c>
+      <c r="BO9">
+        <v>5.3</v>
+      </c>
+      <c r="BP9">
+        <v>32</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>50</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>6.4</v>
+      </c>
+      <c r="BU9">
+        <v>4.1</v>
+      </c>
+      <c r="BV9">
+        <v>24</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>42</v>
+      </c>
+      <c r="BY9">
+        <v>1.02</v>
+      </c>
+      <c r="BZ9">
+        <v>40</v>
+      </c>
+      <c r="CA9">
+        <v>1.02</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
         <v>87</v>
       </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9">
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10">
         <v>3.65</v>
       </c>
-      <c r="G9">
-        <v>3.9</v>
-      </c>
-      <c r="H9">
-        <v>1.93</v>
-      </c>
-      <c r="I9">
+      <c r="G10">
+        <v>3.8</v>
+      </c>
+      <c r="H10">
+        <v>1.94</v>
+      </c>
+      <c r="I10">
         <v>1.98</v>
       </c>
-      <c r="J9">
+      <c r="J10">
         <v>4.4</v>
       </c>
-      <c r="K9">
+      <c r="K10">
         <v>4.6</v>
       </c>
-      <c r="L9">
-        <v>1.23</v>
-      </c>
-      <c r="M9">
+      <c r="L10">
+        <v>1.24</v>
+      </c>
+      <c r="M10">
         <v>1.02</v>
       </c>
-      <c r="N9">
-        <v>7.4</v>
-      </c>
-      <c r="O9">
-        <v>1.13</v>
-      </c>
-      <c r="P9">
-        <v>3.1</v>
-      </c>
-      <c r="Q9">
-        <v>1.44</v>
-      </c>
-      <c r="R9">
-        <v>1.85</v>
-      </c>
-      <c r="S9">
-        <v>2.08</v>
-      </c>
-      <c r="T9">
-        <v>1.46</v>
-      </c>
-      <c r="U9">
-        <v>2.9</v>
-      </c>
-      <c r="V9">
+      <c r="N10">
+        <v>7.2</v>
+      </c>
+      <c r="O10">
+        <v>1.14</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>1.47</v>
+      </c>
+      <c r="R10">
+        <v>1.84</v>
+      </c>
+      <c r="S10">
+        <v>2.12</v>
+      </c>
+      <c r="T10">
+        <v>1.47</v>
+      </c>
+      <c r="U10">
+        <v>2.98</v>
+      </c>
+      <c r="V10">
         <v>2.02</v>
       </c>
-      <c r="W9">
-        <v>1.34</v>
-      </c>
-      <c r="X9">
+      <c r="W10">
+        <v>1.35</v>
+      </c>
+      <c r="X10">
         <v>34</v>
       </c>
-      <c r="Y9">
+      <c r="Y10">
+        <v>17.5</v>
+      </c>
+      <c r="Z10">
+        <v>17.5</v>
+      </c>
+      <c r="AA10">
+        <v>25</v>
+      </c>
+      <c r="AB10">
+        <v>26</v>
+      </c>
+      <c r="AC10">
+        <v>11</v>
+      </c>
+      <c r="AD10">
+        <v>11</v>
+      </c>
+      <c r="AE10">
+        <v>17</v>
+      </c>
+      <c r="AF10">
+        <v>36</v>
+      </c>
+      <c r="AG10">
+        <v>17</v>
+      </c>
+      <c r="AH10">
+        <v>14.5</v>
+      </c>
+      <c r="AI10">
         <v>23</v>
       </c>
-      <c r="Z9">
-        <v>18</v>
-      </c>
-      <c r="AA9">
+      <c r="AJ10">
+        <v>75</v>
+      </c>
+      <c r="AK10">
+        <v>36</v>
+      </c>
+      <c r="AL10">
         <v>34</v>
       </c>
-      <c r="AB9">
+      <c r="AM10">
+        <v>46</v>
+      </c>
+      <c r="AN10">
+        <v>21</v>
+      </c>
+      <c r="AO10">
+        <v>7.2</v>
+      </c>
+      <c r="AP10">
+        <v>29</v>
+      </c>
+      <c r="AQ10">
+        <v>15.5</v>
+      </c>
+      <c r="AR10">
+        <v>15.5</v>
+      </c>
+      <c r="AS10">
+        <v>22</v>
+      </c>
+      <c r="AT10">
+        <v>23</v>
+      </c>
+      <c r="AU10">
+        <v>10</v>
+      </c>
+      <c r="AV10">
+        <v>10.5</v>
+      </c>
+      <c r="AW10">
+        <v>15.5</v>
+      </c>
+      <c r="AX10">
+        <v>32</v>
+      </c>
+      <c r="AY10">
+        <v>15</v>
+      </c>
+      <c r="AZ10">
+        <v>13</v>
+      </c>
+      <c r="BA10">
+        <v>20</v>
+      </c>
+      <c r="BB10">
+        <v>55</v>
+      </c>
+      <c r="BC10">
+        <v>30</v>
+      </c>
+      <c r="BD10">
+        <v>30</v>
+      </c>
+      <c r="BE10">
+        <v>40</v>
+      </c>
+      <c r="BF10">
+        <v>17</v>
+      </c>
+      <c r="BG10">
+        <v>6.6</v>
+      </c>
+      <c r="BH10">
+        <v>5.4</v>
+      </c>
+      <c r="BI10">
+        <v>4</v>
+      </c>
+      <c r="BJ10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK10">
+        <v>6.2</v>
+      </c>
+      <c r="BL10">
+        <v>65</v>
+      </c>
+      <c r="BM10">
         <v>42</v>
       </c>
-      <c r="AC9">
-        <v>12.5</v>
-      </c>
-      <c r="AD9">
+      <c r="BN10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO10">
+        <v>5.9</v>
+      </c>
+      <c r="BP10">
+        <v>25</v>
+      </c>
+      <c r="BQ10">
+        <v>17.5</v>
+      </c>
+      <c r="BR10">
+        <v>27</v>
+      </c>
+      <c r="BS10">
+        <v>19</v>
+      </c>
+      <c r="BT10">
+        <v>5.7</v>
+      </c>
+      <c r="BU10">
+        <v>4.7</v>
+      </c>
+      <c r="BV10">
         <v>13</v>
       </c>
-      <c r="AE9">
-        <v>17</v>
-      </c>
-      <c r="AF9">
-        <v>65</v>
-      </c>
-      <c r="AG9">
-        <v>17</v>
-      </c>
-      <c r="AH9">
-        <v>18</v>
-      </c>
-      <c r="AI9">
-        <v>23</v>
-      </c>
-      <c r="AJ9">
-        <v>1000</v>
-      </c>
-      <c r="AK9">
-        <v>36</v>
-      </c>
-      <c r="AL9">
-        <v>70</v>
-      </c>
-      <c r="AM9">
-        <v>150</v>
-      </c>
-      <c r="AN9">
-        <v>20</v>
-      </c>
-      <c r="AO9">
-        <v>7.8</v>
-      </c>
-      <c r="AP9">
-        <v>22</v>
-      </c>
-      <c r="AQ9">
-        <v>16</v>
-      </c>
-      <c r="AR9">
-        <v>15.5</v>
-      </c>
-      <c r="AS9">
-        <v>22</v>
-      </c>
-      <c r="AT9">
-        <v>24</v>
-      </c>
-      <c r="AU9">
-        <v>10</v>
-      </c>
-      <c r="AV9">
-        <v>10</v>
-      </c>
-      <c r="AW9">
-        <v>12.5</v>
-      </c>
-      <c r="AX9">
-        <v>32</v>
-      </c>
-      <c r="AY9">
-        <v>13</v>
-      </c>
-      <c r="AZ9">
-        <v>13</v>
-      </c>
-      <c r="BA9">
-        <v>20</v>
-      </c>
-      <c r="BB9">
-        <v>32</v>
-      </c>
-      <c r="BC9">
-        <v>30</v>
-      </c>
-      <c r="BD9">
-        <v>30</v>
-      </c>
-      <c r="BE9">
-        <v>38</v>
-      </c>
-      <c r="BF9">
-        <v>14.5</v>
-      </c>
-      <c r="BG9">
-        <v>6.6</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.01</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>1.01</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>1.01</v>
-      </c>
-      <c r="BN9">
-        <v>1000</v>
-      </c>
-      <c r="BO9">
-        <v>1.01</v>
-      </c>
-      <c r="BP9">
-        <v>1000</v>
-      </c>
-      <c r="BQ9">
-        <v>1.01</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>1.01</v>
-      </c>
-      <c r="BT9">
-        <v>1000</v>
-      </c>
-      <c r="BU9">
-        <v>1.01</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>1.01</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>1.01</v>
-      </c>
-      <c r="BZ9">
-        <v>1000</v>
-      </c>
-      <c r="CA9">
-        <v>1.01</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>110</v>
+      <c r="BW10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX10">
+        <v>19.5</v>
+      </c>
+      <c r="BY10">
+        <v>14</v>
+      </c>
+      <c r="BZ10">
+        <v>12</v>
+      </c>
+      <c r="CA10">
+        <v>8.6</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -358,7 +358,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 07:59:09</t>
+    <t>2026-09-29 10:10:53</t>
   </si>
 </sst>
 </file>
@@ -955,25 +955,25 @@
         <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H2">
         <v>3.3</v>
       </c>
       <c r="I2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
         <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
         <v>3.75</v>
@@ -988,37 +988,37 @@
         <v>2.04</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
         <v>1.79</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
         <v>13</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA2">
         <v>70</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -1027,49 +1027,49 @@
         <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
         <v>60</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP2">
         <v>12</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT2">
         <v>9</v>
@@ -1081,7 +1081,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1093,7 +1093,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB2">
         <v>22</v>
@@ -1102,22 +1102,22 @@
         <v>19</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
         <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
         <v>9.4</v>
@@ -1132,10 +1132,10 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP2">
         <v>17.5</v>
@@ -1144,7 +1144,7 @@
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS2">
         <v>1.02</v>
@@ -1156,19 +1156,19 @@
         <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BW2">
         <v>1.02</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA2">
         <v>1.02</v>
@@ -1194,100 +1194,100 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G3">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H3">
         <v>2.64</v>
       </c>
       <c r="I3">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J3">
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
         <v>1.08</v>
       </c>
       <c r="N3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O3">
         <v>1.33</v>
       </c>
       <c r="P3">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q3">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R3">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U3">
         <v>2.08</v>
       </c>
       <c r="V3">
+        <v>1.54</v>
+      </c>
+      <c r="W3">
         <v>1.53</v>
-      </c>
-      <c r="W3">
-        <v>1.52</v>
       </c>
       <c r="X3">
         <v>15.5</v>
       </c>
       <c r="Y3">
+        <v>12</v>
+      </c>
+      <c r="Z3">
+        <v>19.5</v>
+      </c>
+      <c r="AA3">
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>12.5</v>
+      </c>
+      <c r="AC3">
+        <v>8.4</v>
+      </c>
+      <c r="AD3">
         <v>13</v>
       </c>
-      <c r="Z3">
-        <v>20</v>
-      </c>
-      <c r="AA3">
-        <v>55</v>
-      </c>
-      <c r="AB3">
-        <v>13</v>
-      </c>
-      <c r="AC3">
-        <v>9</v>
-      </c>
-      <c r="AD3">
-        <v>15</v>
-      </c>
       <c r="AE3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF3">
         <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ3">
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1302,31 +1302,31 @@
         <v>34</v>
       </c>
       <c r="AP3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
         <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT3">
         <v>9.4</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AX3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1335,25 +1335,25 @@
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC3">
         <v>26</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="BE3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BH3">
         <v>3.7</v>
@@ -1436,19 +1436,19 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H4">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I4">
         <v>3.25</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>4.1</v>
@@ -1472,10 +1472,10 @@
         <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S4">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="T4">
         <v>1.56</v>
@@ -1487,7 +1487,7 @@
         <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X4">
         <v>25</v>
@@ -1496,7 +1496,7 @@
         <v>19</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA4">
         <v>55</v>
@@ -1505,19 +1505,19 @@
         <v>15</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
         <v>32</v>
       </c>
       <c r="AF4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
         <v>16</v>
@@ -1538,10 +1538,10 @@
         <v>70</v>
       </c>
       <c r="AN4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP4">
         <v>18</v>
@@ -1550,22 +1550,22 @@
         <v>14</v>
       </c>
       <c r="AR4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT4">
         <v>12</v>
       </c>
       <c r="AU4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX4">
         <v>15.5</v>
@@ -1577,19 +1577,19 @@
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC4">
         <v>19</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
@@ -1711,7 +1711,7 @@
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
         <v>1.5</v>
@@ -1720,13 +1720,13 @@
         <v>2.68</v>
       </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W5">
         <v>1.27</v>
@@ -1735,7 +1735,7 @@
         <v>25</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z5">
         <v>15.5</v>
@@ -1744,7 +1744,7 @@
         <v>25</v>
       </c>
       <c r="AB5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1810,7 +1810,7 @@
         <v>15</v>
       </c>
       <c r="AX5">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AY5">
         <v>15</v>
@@ -1819,22 +1819,22 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
+        <v>5.6</v>
+      </c>
+      <c r="BB5">
+        <v>6.4</v>
+      </c>
+      <c r="BC5">
         <v>5.9</v>
       </c>
-      <c r="BB5">
-        <v>6.8</v>
-      </c>
-      <c r="BC5">
+      <c r="BD5">
+        <v>6</v>
+      </c>
+      <c r="BE5">
         <v>6.2</v>
       </c>
-      <c r="BD5">
-        <v>6.4</v>
-      </c>
-      <c r="BE5">
-        <v>6.6</v>
-      </c>
       <c r="BF5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG5">
         <v>8.199999999999999</v>
@@ -1879,7 +1879,7 @@
         <v>5.6</v>
       </c>
       <c r="BU5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV5">
         <v>14.5</v>
@@ -1923,7 +1923,7 @@
         <v>1.4</v>
       </c>
       <c r="G6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H6">
         <v>7.4</v>
@@ -1959,7 +1959,7 @@
         <v>1.7</v>
       </c>
       <c r="S6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T6">
         <v>1.6</v>
@@ -1968,10 +1968,10 @@
         <v>2.2</v>
       </c>
       <c r="V6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X6">
         <v>38</v>
@@ -2016,13 +2016,13 @@
         <v>14.5</v>
       </c>
       <c r="AL6">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM6">
         <v>110</v>
       </c>
       <c r="AN6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
         <v>100</v>
@@ -2031,13 +2031,13 @@
         <v>22</v>
       </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="AR6">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AS6">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2046,7 +2046,7 @@
         <v>11</v>
       </c>
       <c r="AV6">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AW6">
         <v>7.4</v>
@@ -2058,19 +2058,19 @@
         <v>9</v>
       </c>
       <c r="AZ6">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BA6">
         <v>7.4</v>
       </c>
       <c r="BB6">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC6">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BD6">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="BE6">
         <v>7.4</v>
@@ -2162,73 +2162,73 @@
         <v>110</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G7">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="H7">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="I7">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>2.54</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O7">
         <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
         <v>1.24</v>
       </c>
       <c r="S7">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="T7">
         <v>1.7</v>
       </c>
       <c r="U7">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="W7">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X7">
         <v>14.5</v>
       </c>
       <c r="Y7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
         <v>9.199999999999999</v>
@@ -2237,13 +2237,13 @@
         <v>14</v>
       </c>
       <c r="AE7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AG7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH7">
         <v>23</v>
@@ -2252,7 +2252,7 @@
         <v>55</v>
       </c>
       <c r="AJ7">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK7">
         <v>55</v>
@@ -2264,109 +2264,109 @@
         <v>140</v>
       </c>
       <c r="AN7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP7">
-        <v>8.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AQ7">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="AR7">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="AT7">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="AU7">
-        <v>5.7</v>
+        <v>2.96</v>
       </c>
       <c r="AV7">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="AW7">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="AX7">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="BA7">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="BB7">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BC7">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="BD7">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BE7">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BF7">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="BG7">
-        <v>19</v>
+        <v>3.8</v>
       </c>
       <c r="BH7">
         <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7">
         <v>12</v>
       </c>
       <c r="BK7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BL7">
         <v>170</v>
       </c>
       <c r="BM7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BP7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU7">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BV7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW7">
         <v>4</v>
@@ -2375,7 +2375,7 @@
         <v>42</v>
       </c>
       <c r="BY7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2407,13 +2407,13 @@
         <v>3.95</v>
       </c>
       <c r="G8">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H8">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="I8">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="J8">
         <v>3.25</v>
@@ -2431,31 +2431,31 @@
         <v>1.01</v>
       </c>
       <c r="O8">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q8">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="R8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S8">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="T8">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="U8">
         <v>2.16</v>
       </c>
       <c r="V8">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="W8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -2473,7 +2473,7 @@
         <v>23</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
@@ -2530,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AW8">
         <v>13</v>
@@ -2563,7 +2563,7 @@
         <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH8">
         <v>4.6</v>
@@ -2646,106 +2646,106 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G9">
         <v>3.25</v>
       </c>
       <c r="H9">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I9">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J9">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
         <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M9">
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q9">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R9">
         <v>1.31</v>
       </c>
       <c r="S9">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T9">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U9">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9">
         <v>16</v>
       </c>
       <c r="AA9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB9">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AC9">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD9">
         <v>12.5</v>
       </c>
       <c r="AE9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
         <v>19.5</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK9">
         <v>50</v>
       </c>
       <c r="AL9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM9">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
         <v>50</v>
@@ -2754,28 +2754,28 @@
         <v>27</v>
       </c>
       <c r="AP9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9">
         <v>13</v>
       </c>
       <c r="AS9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT9">
         <v>10</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV9">
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="AX9">
         <v>18</v>
@@ -2784,22 +2784,22 @@
         <v>12</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB9">
         <v>40</v>
       </c>
       <c r="BC9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE9">
-        <v>5.8</v>
+        <v>40</v>
       </c>
       <c r="BF9">
         <v>32</v>
@@ -2811,7 +2811,7 @@
         <v>3.65</v>
       </c>
       <c r="BI9">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9">
         <v>12</v>
@@ -2823,10 +2823,10 @@
         <v>170</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN9">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO9">
         <v>5.3</v>
@@ -2835,37 +2835,37 @@
         <v>32</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR9">
         <v>50</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT9">
         <v>6.4</v>
       </c>
       <c r="BU9">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
         <v>24</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BX9">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BY9">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="BZ9">
         <v>40</v>
       </c>
       <c r="CA9">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="CB9" t="s">
         <v>114</v>
@@ -2894,16 +2894,16 @@
         <v>3.8</v>
       </c>
       <c r="H10">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J10">
         <v>4.4</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>1.24</v>
@@ -2912,7 +2912,7 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>1.14</v>
@@ -2933,10 +2933,10 @@
         <v>1.47</v>
       </c>
       <c r="U10">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="V10">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W10">
         <v>1.35</v>
@@ -2963,7 +2963,7 @@
         <v>11</v>
       </c>
       <c r="AE10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF10">
         <v>36</v>
@@ -2993,10 +2993,10 @@
         <v>21</v>
       </c>
       <c r="AO10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AP10">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AQ10">
         <v>15.5</v>
@@ -3020,7 +3020,7 @@
         <v>15.5</v>
       </c>
       <c r="AX10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AY10">
         <v>15</v>
@@ -3107,7 +3107,7 @@
         <v>12</v>
       </c>
       <c r="CA10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB10" t="s">
         <v>114</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -358,7 +358,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 10:10:53</t>
+    <t>2026-09-29 12:22:20</t>
   </si>
 </sst>
 </file>
@@ -967,22 +967,22 @@
         <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>1.41</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O2">
         <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
@@ -991,13 +991,13 @@
         <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -1006,7 +1006,7 @@
         <v>1.69</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
         <v>13</v>
@@ -1018,7 +1018,7 @@
         <v>70</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -1063,13 +1063,13 @@
         <v>12</v>
       </c>
       <c r="AQ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR2">
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2">
         <v>9</v>
@@ -1081,7 +1081,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="AX2">
         <v>13.5</v>
@@ -1093,43 +1093,43 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2">
         <v>22</v>
       </c>
       <c r="BC2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BD2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2">
         <v>9.4</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>140</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BN2">
         <v>5.2</v>
@@ -1153,25 +1153,25 @@
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
         <v>27</v>
       </c>
       <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>38</v>
+      </c>
+      <c r="BY2">
         <v>1.02</v>
       </c>
-      <c r="BX2">
-        <v>44</v>
-      </c>
-      <c r="BY2">
+      <c r="BZ2">
+        <v>32</v>
+      </c>
+      <c r="CA2">
         <v>1.01</v>
-      </c>
-      <c r="BZ2">
-        <v>28</v>
-      </c>
-      <c r="CA2">
-        <v>1.02</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1197,49 +1197,49 @@
         <v>2.72</v>
       </c>
       <c r="G3">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="I3">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J3">
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
         <v>1.42</v>
       </c>
       <c r="M3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
         <v>3.7</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R3">
         <v>1.35</v>
       </c>
       <c r="S3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U3">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V3">
         <v>1.54</v>
@@ -1248,25 +1248,25 @@
         <v>1.53</v>
       </c>
       <c r="X3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z3">
         <v>19.5</v>
       </c>
       <c r="AA3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
         <v>34</v>
@@ -1275,46 +1275,46 @@
         <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
         <v>18</v>
       </c>
       <c r="AI3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ3">
+        <v>46</v>
+      </c>
+      <c r="AK3">
+        <v>32</v>
+      </c>
+      <c r="AL3">
         <v>50</v>
-      </c>
-      <c r="AK3">
-        <v>34</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
       </c>
       <c r="AM3">
         <v>110</v>
       </c>
       <c r="AN3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3">
         <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS3">
-        <v>36</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU3">
         <v>6.8</v>
@@ -1323,10 +1323,10 @@
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AX3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1335,37 +1335,37 @@
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>36</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>75</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="BH3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>140</v>
@@ -1377,19 +1377,19 @@
         <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3">
         <v>25</v>
       </c>
       <c r="BQ3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BR3">
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1398,16 +1398,16 @@
         <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BX3">
         <v>40</v>
       </c>
       <c r="BY3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BZ3">
         <v>34</v>
@@ -1436,7 +1436,7 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
         <v>2.54</v>
@@ -1445,10 +1445,10 @@
         <v>2.86</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>4.1</v>
@@ -1466,16 +1466,16 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q4">
         <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S4">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="T4">
         <v>1.56</v>
@@ -1484,7 +1484,7 @@
         <v>2.46</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
         <v>1.65</v>
@@ -1496,7 +1496,7 @@
         <v>19</v>
       </c>
       <c r="Z4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA4">
         <v>55</v>
@@ -1541,7 +1541,7 @@
         <v>14.5</v>
       </c>
       <c r="AO4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP4">
         <v>18</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV4">
         <v>11.5</v>
@@ -1714,7 +1714,7 @@
         <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S5">
         <v>2.68</v>
@@ -1726,19 +1726,19 @@
         <v>2.26</v>
       </c>
       <c r="V5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W5">
         <v>1.27</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y5">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA5">
         <v>25</v>
@@ -1777,7 +1777,7 @@
         <v>65</v>
       </c>
       <c r="AM5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN5">
         <v>55</v>
@@ -1789,7 +1789,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
         <v>11</v>
@@ -1801,7 +1801,7 @@
         <v>16.5</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
         <v>9</v>
@@ -1810,7 +1810,7 @@
         <v>15</v>
       </c>
       <c r="AX5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY5">
         <v>15</v>
@@ -1819,25 +1819,25 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB5">
+        <v>6.6</v>
+      </c>
+      <c r="BC5">
+        <v>6</v>
+      </c>
+      <c r="BD5">
+        <v>6.2</v>
+      </c>
+      <c r="BE5">
         <v>6.4</v>
       </c>
-      <c r="BC5">
-        <v>5.9</v>
-      </c>
-      <c r="BD5">
-        <v>6</v>
-      </c>
-      <c r="BE5">
+      <c r="BF5">
         <v>6.2</v>
       </c>
-      <c r="BF5">
-        <v>6</v>
-      </c>
       <c r="BG5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
@@ -1852,7 +1852,7 @@
         <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM5">
         <v>1.02</v>
@@ -1879,7 +1879,7 @@
         <v>5.6</v>
       </c>
       <c r="BU5">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BV5">
         <v>14.5</v>
@@ -1923,16 +1923,16 @@
         <v>1.4</v>
       </c>
       <c r="G6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K6">
         <v>5.9</v>
@@ -1965,10 +1965,10 @@
         <v>1.6</v>
       </c>
       <c r="U6">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W6">
         <v>3.05</v>
@@ -2028,118 +2028,118 @@
         <v>100</v>
       </c>
       <c r="AP6">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6">
-        <v>26</v>
+        <v>7.8</v>
       </c>
       <c r="AR6">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AS6">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="AT6">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AU6">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="AV6">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AW6">
         <v>7.4</v>
       </c>
       <c r="AX6">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY6">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AZ6">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="BA6">
         <v>7.4</v>
       </c>
       <c r="BB6">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BC6">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="BD6">
-        <v>19.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE6">
         <v>7.4</v>
       </c>
       <c r="BF6">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="BG6">
         <v>7.4</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ6">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM6">
+        <v>1.02</v>
+      </c>
+      <c r="BN6">
+        <v>5.1</v>
+      </c>
+      <c r="BO6">
+        <v>3.35</v>
+      </c>
+      <c r="BP6">
+        <v>10</v>
+      </c>
+      <c r="BQ6">
         <v>1.01</v>
       </c>
-      <c r="BN6">
-        <v>6</v>
-      </c>
-      <c r="BO6">
-        <v>3.15</v>
-      </c>
-      <c r="BP6">
-        <v>12</v>
-      </c>
-      <c r="BQ6">
-        <v>5.3</v>
-      </c>
       <c r="BR6">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BU6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BW6">
         <v>1.02</v>
       </c>
       <c r="BX6">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BY6">
         <v>1.02</v>
       </c>
       <c r="BZ6">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="s">
         <v>114</v>
@@ -2162,19 +2162,19 @@
         <v>110</v>
       </c>
       <c r="F7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G7">
         <v>4.2</v>
       </c>
       <c r="H7">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="I7">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="J7">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="K7">
         <v>4.2</v>
@@ -2186,22 +2186,22 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
         <v>1.24</v>
       </c>
       <c r="S7">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
         <v>1.7</v>
@@ -2210,7 +2210,7 @@
         <v>2</v>
       </c>
       <c r="V7">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W7">
         <v>1.31</v>
@@ -2264,7 +2264,7 @@
         <v>140</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO7">
         <v>29</v>
@@ -2279,13 +2279,13 @@
         <v>3.5</v>
       </c>
       <c r="AS7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AT7">
         <v>3.35</v>
       </c>
       <c r="AU7">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="AV7">
         <v>3.3</v>
@@ -2321,13 +2321,13 @@
         <v>4</v>
       </c>
       <c r="BG7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BH7">
         <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7">
         <v>12</v>
@@ -2404,10 +2404,10 @@
         <v>111</v>
       </c>
       <c r="F8">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G8">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H8">
         <v>1.76</v>
@@ -2416,7 +2416,7 @@
         <v>1.96</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
         <v>5.1</v>
@@ -2431,22 +2431,22 @@
         <v>1.01</v>
       </c>
       <c r="O8">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="R8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
         <v>2.74</v>
       </c>
       <c r="T8">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="U8">
         <v>2.16</v>
@@ -2455,7 +2455,7 @@
         <v>2.04</v>
       </c>
       <c r="W8">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -2530,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8">
         <v>13</v>
@@ -2658,7 +2658,7 @@
         <v>2.58</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
         <v>3.55</v>
@@ -2670,19 +2670,19 @@
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
         <v>1.38</v>
       </c>
       <c r="P9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q9">
         <v>2.14</v>
       </c>
       <c r="R9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S9">
         <v>3.95</v>
@@ -2736,7 +2736,7 @@
         <v>60</v>
       </c>
       <c r="AJ9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK9">
         <v>50</v>
@@ -2790,7 +2790,7 @@
         <v>36</v>
       </c>
       <c r="BB9">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="BC9">
         <v>25</v>
@@ -2823,7 +2823,7 @@
         <v>170</v>
       </c>
       <c r="BM9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN9">
         <v>7.4</v>
@@ -2835,13 +2835,13 @@
         <v>32</v>
       </c>
       <c r="BQ9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR9">
         <v>50</v>
       </c>
       <c r="BS9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT9">
         <v>6.4</v>
@@ -2853,10 +2853,10 @@
         <v>24</v>
       </c>
       <c r="BW9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BX9">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BY9">
         <v>4.3</v>
@@ -2865,7 +2865,7 @@
         <v>40</v>
       </c>
       <c r="CA9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB9" t="s">
         <v>114</v>
@@ -2888,19 +2888,19 @@
         <v>113</v>
       </c>
       <c r="F10">
+        <v>3.55</v>
+      </c>
+      <c r="G10">
         <v>3.65</v>
       </c>
-      <c r="G10">
-        <v>3.8</v>
-      </c>
       <c r="H10">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="I10">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="J10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K10">
         <v>4.5</v>
@@ -2912,10 +2912,10 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P10">
         <v>3</v>
@@ -2924,22 +2924,22 @@
         <v>1.47</v>
       </c>
       <c r="R10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T10">
         <v>1.47</v>
       </c>
       <c r="U10">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V10">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="W10">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X10">
         <v>34</v>
@@ -2948,40 +2948,40 @@
         <v>17.5</v>
       </c>
       <c r="Z10">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA10">
+        <v>27</v>
+      </c>
+      <c r="AB10">
         <v>25</v>
-      </c>
-      <c r="AB10">
-        <v>26</v>
       </c>
       <c r="AC10">
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE10">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH10">
         <v>14.5</v>
       </c>
       <c r="AI10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL10">
         <v>34</v>
@@ -2990,13 +2990,13 @@
         <v>46</v>
       </c>
       <c r="AN10">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO10">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AQ10">
         <v>15.5</v>
@@ -3005,25 +3005,25 @@
         <v>15.5</v>
       </c>
       <c r="AS10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT10">
         <v>23</v>
       </c>
       <c r="AU10">
+        <v>9.6</v>
+      </c>
+      <c r="AV10">
         <v>10</v>
       </c>
-      <c r="AV10">
-        <v>10.5</v>
-      </c>
       <c r="AW10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX10">
         <v>30</v>
       </c>
       <c r="AY10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ10">
         <v>13</v>
@@ -3032,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="BB10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC10">
         <v>30</v>
@@ -3044,16 +3044,16 @@
         <v>40</v>
       </c>
       <c r="BF10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG10">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BJ10">
         <v>8.800000000000001</v>
@@ -3068,22 +3068,22 @@
         <v>42</v>
       </c>
       <c r="BN10">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO10">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ10">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BR10">
         <v>27</v>
       </c>
       <c r="BS10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BT10">
         <v>5.7</v>
@@ -3092,22 +3092,22 @@
         <v>4.7</v>
       </c>
       <c r="BV10">
+        <v>13.5</v>
+      </c>
+      <c r="BW10">
+        <v>9.6</v>
+      </c>
+      <c r="BX10">
+        <v>20</v>
+      </c>
+      <c r="BY10">
+        <v>14.5</v>
+      </c>
+      <c r="BZ10">
         <v>13</v>
       </c>
-      <c r="BW10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX10">
-        <v>19.5</v>
-      </c>
-      <c r="BY10">
-        <v>14</v>
-      </c>
-      <c r="BZ10">
-        <v>12</v>
-      </c>
       <c r="CA10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB10" t="s">
         <v>114</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -358,7 +358,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 12:22:20</t>
+    <t>2026-09-29 14:34:15</t>
   </si>
 </sst>
 </file>
@@ -961,10 +961,10 @@
         <v>3.3</v>
       </c>
       <c r="I2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
         <v>3.5</v>
@@ -973,7 +973,7 @@
         <v>1.41</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
         <v>3.8</v>
@@ -991,13 +991,13 @@
         <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -1012,7 +1012,7 @@
         <v>13</v>
       </c>
       <c r="Z2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA2">
         <v>70</v>
@@ -1030,7 +1030,7 @@
         <v>46</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1042,7 +1042,7 @@
         <v>60</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK2">
         <v>26</v>
@@ -1054,7 +1054,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO2">
         <v>44</v>
@@ -1084,7 +1084,7 @@
         <v>27</v>
       </c>
       <c r="AX2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY2">
         <v>10</v>
@@ -1114,7 +1114,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BH2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI2">
         <v>2.82</v>
@@ -1129,16 +1129,16 @@
         <v>140</v>
       </c>
       <c r="BM2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO2">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
@@ -1153,13 +1153,13 @@
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX2">
         <v>38</v>
@@ -1168,10 +1168,10 @@
         <v>1.02</v>
       </c>
       <c r="BZ2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1194,22 +1194,22 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H3">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I3">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="J3">
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
         <v>1.42</v>
@@ -1242,10 +1242,10 @@
         <v>2.12</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X3">
         <v>16</v>
@@ -1254,7 +1254,7 @@
         <v>13</v>
       </c>
       <c r="Z3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA3">
         <v>46</v>
@@ -1263,19 +1263,19 @@
         <v>12</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
         <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH3">
         <v>18</v>
@@ -1284,10 +1284,10 @@
         <v>46</v>
       </c>
       <c r="AJ3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL3">
         <v>50</v>
@@ -1302,16 +1302,16 @@
         <v>30</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ3">
         <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT3">
         <v>9.6</v>
@@ -1323,7 +1323,7 @@
         <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AX3">
         <v>15.5</v>
@@ -1335,25 +1335,25 @@
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>5.9</v>
       </c>
       <c r="BB3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC3">
+        <v>5.6</v>
+      </c>
+      <c r="BD3">
+        <v>5.8</v>
+      </c>
+      <c r="BE3">
         <v>6.2</v>
-      </c>
-      <c r="BD3">
-        <v>6.4</v>
-      </c>
-      <c r="BE3">
-        <v>6.8</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
         <v>3.75</v>
@@ -1374,7 +1374,7 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO3">
         <v>4.6</v>
@@ -1389,16 +1389,16 @@
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW3">
         <v>16</v>
@@ -1410,7 +1410,7 @@
         <v>25</v>
       </c>
       <c r="BZ3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA3">
         <v>21</v>
@@ -1439,13 +1439,13 @@
         <v>2.32</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H4">
         <v>2.86</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
         <v>3.75</v>
@@ -1466,10 +1466,10 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R4">
         <v>1.53</v>
@@ -1481,10 +1481,10 @@
         <v>1.56</v>
       </c>
       <c r="U4">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
         <v>1.65</v>
@@ -1595,7 +1595,7 @@
         <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH4">
         <v>4.7</v>
@@ -1604,19 +1604,19 @@
         <v>3.35</v>
       </c>
       <c r="BJ4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM4">
         <v>1.02</v>
       </c>
       <c r="BN4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
         <v>4.5</v>
@@ -1646,13 +1646,13 @@
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY4">
         <v>1.02</v>
       </c>
       <c r="BZ4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1684,10 +1684,10 @@
         <v>4.6</v>
       </c>
       <c r="H5">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="I5">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J5">
         <v>3.9</v>
@@ -1711,10 +1711,10 @@
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
         <v>2.68</v>
@@ -1726,13 +1726,13 @@
         <v>2.26</v>
       </c>
       <c r="V5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W5">
         <v>1.27</v>
       </c>
       <c r="X5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y5">
         <v>12</v>
@@ -1774,10 +1774,10 @@
         <v>60</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN5">
         <v>55</v>
@@ -1819,7 +1819,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB5">
         <v>6.6</v>
@@ -1837,7 +1837,7 @@
         <v>6.2</v>
       </c>
       <c r="BG5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
@@ -1852,7 +1852,7 @@
         <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM5">
         <v>1.02</v>
@@ -1876,13 +1876,13 @@
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU5">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BV5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
@@ -1923,16 +1923,16 @@
         <v>1.4</v>
       </c>
       <c r="G6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>8.6</v>
       </c>
       <c r="J6">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
         <v>5.9</v>
@@ -1965,7 +1965,7 @@
         <v>1.6</v>
       </c>
       <c r="U6">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V6">
         <v>1.13</v>
@@ -2016,7 +2016,7 @@
         <v>14.5</v>
       </c>
       <c r="AL6">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM6">
         <v>110</v>
@@ -2028,58 +2028,58 @@
         <v>100</v>
       </c>
       <c r="AP6">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS6">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="AT6">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AV6">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="AX6">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="AY6">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BB6">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="BC6">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="BD6">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BF6">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH6">
         <v>5.6</v>
@@ -2094,7 +2094,7 @@
         <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM6">
         <v>1.02</v>
@@ -2103,7 +2103,7 @@
         <v>5.1</v>
       </c>
       <c r="BO6">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BP6">
         <v>10</v>
@@ -2124,7 +2124,7 @@
         <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW6">
         <v>1.02</v>
@@ -2168,13 +2168,13 @@
         <v>4.2</v>
       </c>
       <c r="H7">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="I7">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="J7">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="K7">
         <v>4.2</v>
@@ -2186,7 +2186,7 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
         <v>1.36</v>
@@ -2195,13 +2195,13 @@
         <v>1.64</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
         <v>1.24</v>
       </c>
       <c r="S7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T7">
         <v>1.7</v>
@@ -2210,13 +2210,13 @@
         <v>2</v>
       </c>
       <c r="V7">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W7">
         <v>1.31</v>
       </c>
       <c r="X7">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
         <v>11</v>
@@ -2273,61 +2273,61 @@
         <v>3.35</v>
       </c>
       <c r="AQ7">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AR7">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AS7">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AT7">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AU7">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AV7">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AW7">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AX7">
+        <v>3.95</v>
+      </c>
+      <c r="AY7">
+        <v>3.65</v>
+      </c>
+      <c r="AZ7">
         <v>3.8</v>
       </c>
-      <c r="AY7">
-        <v>3.5</v>
-      </c>
-      <c r="AZ7">
-        <v>3.65</v>
-      </c>
       <c r="BA7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE7">
+        <v>4.4</v>
+      </c>
+      <c r="BF7">
         <v>4.2</v>
       </c>
-      <c r="BF7">
-        <v>4</v>
-      </c>
       <c r="BG7">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BH7">
         <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7">
         <v>12</v>
@@ -2404,10 +2404,10 @@
         <v>111</v>
       </c>
       <c r="F8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G8">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="H8">
         <v>1.76</v>
@@ -2416,7 +2416,7 @@
         <v>1.96</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
         <v>5.1</v>
@@ -2431,16 +2431,16 @@
         <v>1.01</v>
       </c>
       <c r="O8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
         <v>1.67</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S8">
         <v>2.74</v>
@@ -2455,7 +2455,7 @@
         <v>2.04</v>
       </c>
       <c r="W8">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -2530,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AW8">
         <v>13</v>
@@ -2655,7 +2655,7 @@
         <v>2.46</v>
       </c>
       <c r="I9">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J9">
         <v>3.4</v>
@@ -2664,7 +2664,7 @@
         <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M9">
         <v>1.08</v>
@@ -2682,7 +2682,7 @@
         <v>2.14</v>
       </c>
       <c r="R9">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S9">
         <v>3.95</v>
@@ -2775,7 +2775,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX9">
         <v>18</v>
@@ -2888,19 +2888,19 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G10">
         <v>3.65</v>
       </c>
       <c r="H10">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>2.06</v>
       </c>
       <c r="J10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K10">
         <v>4.5</v>
@@ -2909,10 +2909,10 @@
         <v>1.24</v>
       </c>
       <c r="M10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>1.15</v>
@@ -2930,16 +2930,16 @@
         <v>2.14</v>
       </c>
       <c r="T10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U10">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="V10">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W10">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X10">
         <v>34</v>
@@ -2948,7 +2948,7 @@
         <v>17.5</v>
       </c>
       <c r="Z10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA10">
         <v>27</v>
@@ -2963,7 +2963,7 @@
         <v>12</v>
       </c>
       <c r="AE10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF10">
         <v>34</v>
@@ -2990,13 +2990,13 @@
         <v>46</v>
       </c>
       <c r="AN10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO10">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AP10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ10">
         <v>15.5</v>
@@ -3008,13 +3008,13 @@
         <v>24</v>
       </c>
       <c r="AT10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW10">
         <v>16</v>
@@ -3032,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="BB10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC10">
         <v>30</v>
@@ -3068,7 +3068,7 @@
         <v>42</v>
       </c>
       <c r="BN10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO10">
         <v>5.7</v>
@@ -3086,10 +3086,10 @@
         <v>18.5</v>
       </c>
       <c r="BT10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
         <v>13.5</v>
@@ -3104,7 +3104,7 @@
         <v>14.5</v>
       </c>
       <c r="BZ10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA10">
         <v>9</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -358,7 +358,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 14:34:15</t>
+    <t>2026-09-29 16:44:36</t>
   </si>
 </sst>
 </file>
@@ -952,31 +952,31 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J2">
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
         <v>1.34</v>
@@ -994,16 +994,16 @@
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
         <v>2.18</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W2">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
         <v>14</v>
@@ -1015,22 +1015,22 @@
         <v>27</v>
       </c>
       <c r="AA2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1039,10 +1039,10 @@
         <v>17.5</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK2">
         <v>26</v>
@@ -1054,7 +1054,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO2">
         <v>44</v>
@@ -1063,13 +1063,13 @@
         <v>12</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="AT2">
         <v>9</v>
@@ -1081,7 +1081,7 @@
         <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX2">
         <v>13</v>
@@ -1093,28 +1093,28 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BB2">
+        <v>27</v>
+      </c>
+      <c r="BC2">
         <v>22</v>
       </c>
-      <c r="BC2">
-        <v>23</v>
-      </c>
       <c r="BD2">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BH2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
         <v>2.82</v>
@@ -1129,25 +1129,25 @@
         <v>140</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>1.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
         <v>6.6</v>
@@ -1156,22 +1156,22 @@
         <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW2">
-        <v>1.02</v>
+        <v>7.8</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY2">
-        <v>1.02</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
         <v>28</v>
       </c>
       <c r="CA2">
-        <v>1.02</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1194,16 +1194,16 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="G3">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="H3">
+        <v>2.56</v>
+      </c>
+      <c r="I3">
         <v>2.66</v>
-      </c>
-      <c r="I3">
-        <v>2.74</v>
       </c>
       <c r="J3">
         <v>3.5</v>
@@ -1212,94 +1212,94 @@
         <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
         <v>1.94</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R3">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U3">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W3">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y3">
         <v>13</v>
       </c>
       <c r="Z3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF3">
         <v>22</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN3">
         <v>30</v>
       </c>
       <c r="AO3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AP3">
         <v>12</v>
@@ -1308,25 +1308,25 @@
         <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT3">
         <v>9.6</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1335,31 +1335,31 @@
         <v>15</v>
       </c>
       <c r="BA3">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
         <v>6.6</v>
       </c>
       <c r="BC3">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD3">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BH3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI3">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1368,7 +1368,7 @@
         <v>7.2</v>
       </c>
       <c r="BL3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM3">
         <v>1.01</v>
@@ -1377,13 +1377,13 @@
         <v>6.8</v>
       </c>
       <c r="BO3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BR3">
         <v>40</v>
@@ -1392,28 +1392,28 @@
         <v>26</v>
       </c>
       <c r="BT3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
+        <v>23</v>
+      </c>
+      <c r="BW3">
+        <v>15</v>
+      </c>
+      <c r="BX3">
+        <v>38</v>
+      </c>
+      <c r="BY3">
         <v>24</v>
-      </c>
-      <c r="BW3">
-        <v>16</v>
-      </c>
-      <c r="BX3">
-        <v>40</v>
-      </c>
-      <c r="BY3">
-        <v>25</v>
       </c>
       <c r="BZ3">
         <v>32</v>
       </c>
       <c r="CA3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1436,13 +1436,13 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H4">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I4">
         <v>3.25</v>
@@ -1451,52 +1451,52 @@
         <v>3.75</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M4">
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="R4">
         <v>1.53</v>
       </c>
       <c r="S4">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="T4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V4">
         <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X4">
         <v>25</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA4">
         <v>55</v>
@@ -1508,7 +1508,7 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE4">
         <v>32</v>
@@ -1526,10 +1526,10 @@
         <v>36</v>
       </c>
       <c r="AJ4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL4">
         <v>32</v>
@@ -1538,7 +1538,7 @@
         <v>70</v>
       </c>
       <c r="AN4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AO4">
         <v>23</v>
@@ -1550,10 +1550,10 @@
         <v>14</v>
       </c>
       <c r="AR4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS4">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="AT4">
         <v>12</v>
@@ -1565,7 +1565,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX4">
         <v>15.5</v>
@@ -1577,25 +1577,25 @@
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC4">
         <v>19</v>
       </c>
       <c r="BD4">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH4">
         <v>4.7</v>
@@ -1604,25 +1604,25 @@
         <v>3.35</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM4">
         <v>1.02</v>
       </c>
       <c r="BN4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
@@ -1637,7 +1637,7 @@
         <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV4">
         <v>24</v>
@@ -1646,7 +1646,7 @@
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY4">
         <v>1.02</v>
@@ -1681,19 +1681,19 @@
         <v>4.2</v>
       </c>
       <c r="G5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H5">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="I5">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.28</v>
@@ -1708,13 +1708,13 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S5">
         <v>2.68</v>
@@ -1723,28 +1723,28 @@
         <v>1.66</v>
       </c>
       <c r="U5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W5">
         <v>1.27</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y5">
         <v>12</v>
       </c>
       <c r="Z5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA5">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AB5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1759,7 +1759,7 @@
         <v>38</v>
       </c>
       <c r="AG5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5">
         <v>18</v>
@@ -1780,7 +1780,7 @@
         <v>95</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO5">
         <v>9.800000000000001</v>
@@ -1807,10 +1807,10 @@
         <v>9</v>
       </c>
       <c r="AW5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX5">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AY5">
         <v>15</v>
@@ -1819,22 +1819,22 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB5">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC5">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BD5">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG5">
         <v>8.199999999999999</v>
@@ -1861,7 +1861,7 @@
         <v>9.6</v>
       </c>
       <c r="BO5">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
         <v>40</v>
@@ -1876,13 +1876,13 @@
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU5">
         <v>3.7</v>
       </c>
       <c r="BV5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
@@ -1938,7 +1938,7 @@
         <v>5.9</v>
       </c>
       <c r="L6">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M6">
         <v>1.02</v>
@@ -1965,13 +1965,13 @@
         <v>1.6</v>
       </c>
       <c r="U6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
         <v>1.13</v>
       </c>
       <c r="W6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X6">
         <v>38</v>
@@ -2028,7 +2028,7 @@
         <v>100</v>
       </c>
       <c r="AP6">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6">
         <v>8.199999999999999</v>
@@ -2037,7 +2037,7 @@
         <v>12.5</v>
       </c>
       <c r="AS6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2046,10 +2046,10 @@
         <v>11</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AW6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AX6">
         <v>9.4</v>
@@ -2061,7 +2061,7 @@
         <v>17.5</v>
       </c>
       <c r="BA6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BB6">
         <v>11</v>
@@ -2070,10 +2070,10 @@
         <v>11.5</v>
       </c>
       <c r="BD6">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BE6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BF6">
         <v>3.75</v>
@@ -2109,7 +2109,7 @@
         <v>10</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
         <v>20</v>
@@ -2171,10 +2171,10 @@
         <v>2.04</v>
       </c>
       <c r="I7">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="J7">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="K7">
         <v>4.2</v>
@@ -2186,7 +2186,7 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="O7">
         <v>1.36</v>
@@ -2210,7 +2210,7 @@
         <v>2</v>
       </c>
       <c r="V7">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W7">
         <v>1.31</v>
@@ -2327,7 +2327,7 @@
         <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7">
         <v>12</v>
@@ -2655,7 +2655,7 @@
         <v>2.46</v>
       </c>
       <c r="I9">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J9">
         <v>3.4</v>
@@ -2664,7 +2664,7 @@
         <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M9">
         <v>1.08</v>
@@ -2888,16 +2888,16 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I10">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J10">
         <v>4.2</v>
@@ -2930,13 +2930,13 @@
         <v>2.14</v>
       </c>
       <c r="T10">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U10">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V10">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W10">
         <v>1.37</v>
@@ -2948,22 +2948,22 @@
         <v>17.5</v>
       </c>
       <c r="Z10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC10">
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF10">
         <v>34</v>
@@ -2981,22 +2981,22 @@
         <v>70</v>
       </c>
       <c r="AK10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL10">
         <v>34</v>
       </c>
       <c r="AM10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AN10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ10">
         <v>15.5</v>
@@ -3014,10 +3014,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX10">
         <v>30</v>
@@ -3047,13 +3047,13 @@
         <v>17.5</v>
       </c>
       <c r="BG10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH10">
         <v>5.3</v>
       </c>
       <c r="BI10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ10">
         <v>8.800000000000001</v>
@@ -3074,10 +3074,10 @@
         <v>5.7</v>
       </c>
       <c r="BP10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BR10">
         <v>27</v>
@@ -3092,7 +3092,7 @@
         <v>4.8</v>
       </c>
       <c r="BV10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BW10">
         <v>9.6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -358,7 +358,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 16:44:36</t>
+    <t>2026-09-29 18:55:09</t>
   </si>
 </sst>
 </file>
@@ -952,7 +952,7 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
         <v>2.4</v>
@@ -961,13 +961,13 @@
         <v>3.4</v>
       </c>
       <c r="I2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>1.42</v>
@@ -976,31 +976,31 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O2">
         <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.71</v>
@@ -1012,67 +1012,67 @@
         <v>13</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
         <v>32</v>
       </c>
       <c r="AK2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM2">
         <v>110</v>
       </c>
       <c r="AN2">
+        <v>21</v>
+      </c>
+      <c r="AO2">
+        <v>40</v>
+      </c>
+      <c r="AP2">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2">
+        <v>12</v>
+      </c>
+      <c r="AR2">
         <v>20</v>
       </c>
-      <c r="AO2">
-        <v>44</v>
-      </c>
-      <c r="AP2">
-        <v>12</v>
-      </c>
-      <c r="AQ2">
-        <v>11.5</v>
-      </c>
-      <c r="AR2">
-        <v>21</v>
-      </c>
       <c r="AS2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -1081,37 +1081,37 @@
         <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AX2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC2">
         <v>22</v>
       </c>
       <c r="BD2">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="BF2">
         <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="BH2">
         <v>3.75</v>
@@ -1135,7 +1135,7 @@
         <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP2">
         <v>17.5</v>
@@ -1162,7 +1162,7 @@
         <v>7.8</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY2">
         <v>8.6</v>
@@ -1171,7 +1171,7 @@
         <v>28</v>
       </c>
       <c r="CA2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1194,55 +1194,55 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>2.56</v>
       </c>
       <c r="I3">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
         <v>1.41</v>
       </c>
       <c r="M3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>3.85</v>
       </c>
       <c r="O3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
+        <v>1.98</v>
+      </c>
+      <c r="Q3">
         <v>1.94</v>
       </c>
-      <c r="Q3">
-        <v>1.96</v>
-      </c>
       <c r="R3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W3">
         <v>1.5</v>
@@ -1275,46 +1275,46 @@
         <v>22</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH3">
         <v>17.5</v>
       </c>
       <c r="AI3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ3">
         <v>55</v>
       </c>
       <c r="AK3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP3">
         <v>12</v>
       </c>
       <c r="AQ3">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3">
         <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="AT3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
         <v>7</v>
@@ -1323,7 +1323,7 @@
         <v>10</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AX3">
         <v>17</v>
@@ -1335,31 +1335,31 @@
         <v>15</v>
       </c>
       <c r="BA3">
+        <v>30</v>
+      </c>
+      <c r="BB3">
+        <v>6.8</v>
+      </c>
+      <c r="BC3">
+        <v>6.2</v>
+      </c>
+      <c r="BD3">
+        <v>34</v>
+      </c>
+      <c r="BE3">
         <v>6.6</v>
-      </c>
-      <c r="BB3">
-        <v>6.6</v>
-      </c>
-      <c r="BC3">
-        <v>6.4</v>
-      </c>
-      <c r="BD3">
-        <v>6.6</v>
-      </c>
-      <c r="BE3">
-        <v>6.8</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI3">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1368,13 +1368,13 @@
         <v>7.2</v>
       </c>
       <c r="BL3">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO3">
         <v>4.8</v>
@@ -1389,7 +1389,7 @@
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
@@ -1401,19 +1401,19 @@
         <v>23</v>
       </c>
       <c r="BW3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BX3">
         <v>38</v>
       </c>
       <c r="BY3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BZ3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1436,7 +1436,7 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="G4">
         <v>2.52</v>
@@ -1454,7 +1454,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M4">
         <v>1.04</v>
@@ -1466,25 +1466,25 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
         <v>1.64</v>
       </c>
       <c r="R4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S4">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="T4">
         <v>1.57</v>
       </c>
       <c r="U4">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
         <v>1.66</v>
@@ -1505,16 +1505,16 @@
         <v>15</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
         <v>32</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AG4">
         <v>13.5</v>
@@ -1523,7 +1523,7 @@
         <v>16</v>
       </c>
       <c r="AI4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ4">
         <v>34</v>
@@ -1532,16 +1532,16 @@
         <v>25</v>
       </c>
       <c r="AL4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM4">
         <v>70</v>
       </c>
       <c r="AN4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP4">
         <v>18</v>
@@ -1556,7 +1556,7 @@
         <v>34</v>
       </c>
       <c r="AT4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU4">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX4">
         <v>15.5</v>
@@ -1577,10 +1577,10 @@
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB4">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BC4">
         <v>19</v>
@@ -1589,7 +1589,7 @@
         <v>19.5</v>
       </c>
       <c r="BE4">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
@@ -1601,13 +1601,13 @@
         <v>4.7</v>
       </c>
       <c r="BI4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ4">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>90</v>
@@ -1622,13 +1622,13 @@
         <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
@@ -1652,7 +1652,7 @@
         <v>1.02</v>
       </c>
       <c r="BZ4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1681,28 +1681,28 @@
         <v>4.2</v>
       </c>
       <c r="G5">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H5">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="I5">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
         <v>1.23</v>
@@ -1729,16 +1729,16 @@
         <v>2.06</v>
       </c>
       <c r="W5">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y5">
         <v>12</v>
       </c>
       <c r="Z5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA5">
         <v>22</v>
@@ -1747,28 +1747,28 @@
         <v>21</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
         <v>11</v>
       </c>
       <c r="AE5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF5">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AG5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AH5">
         <v>18</v>
       </c>
       <c r="AI5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ5">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK5">
         <v>60</v>
@@ -1777,13 +1777,13 @@
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN5">
-        <v>46</v>
+        <v>260</v>
       </c>
       <c r="AO5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP5">
         <v>17.5</v>
@@ -1810,7 +1810,7 @@
         <v>15.5</v>
       </c>
       <c r="AX5">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AY5">
         <v>15</v>
@@ -1819,22 +1819,22 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BB5">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BC5">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BF5">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BG5">
         <v>8.199999999999999</v>
@@ -1867,7 +1867,7 @@
         <v>40</v>
       </c>
       <c r="BQ5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>46</v>
@@ -1879,7 +1879,7 @@
         <v>5.6</v>
       </c>
       <c r="BU5">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV5">
         <v>14.5</v>
@@ -1920,28 +1920,28 @@
         <v>109</v>
       </c>
       <c r="F6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H6">
         <v>7.4</v>
       </c>
       <c r="I6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L6">
         <v>1.25</v>
       </c>
       <c r="M6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
         <v>6.2</v>
@@ -1950,28 +1950,28 @@
         <v>1.16</v>
       </c>
       <c r="P6">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q6">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R6">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S6">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T6">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V6">
         <v>1.13</v>
       </c>
       <c r="W6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X6">
         <v>38</v>
@@ -1989,7 +1989,7 @@
         <v>13</v>
       </c>
       <c r="AC6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AD6">
         <v>32</v>
@@ -1998,7 +1998,7 @@
         <v>110</v>
       </c>
       <c r="AF6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG6">
         <v>11.5</v>
@@ -2010,34 +2010,34 @@
         <v>90</v>
       </c>
       <c r="AJ6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AK6">
         <v>14.5</v>
       </c>
       <c r="AL6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM6">
         <v>110</v>
       </c>
       <c r="AN6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO6">
         <v>100</v>
       </c>
       <c r="AP6">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2046,40 +2046,40 @@
         <v>11</v>
       </c>
       <c r="AV6">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="AW6">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX6">
+        <v>9.6</v>
+      </c>
+      <c r="AY6">
         <v>9.4</v>
-      </c>
-      <c r="AY6">
-        <v>9</v>
       </c>
       <c r="AZ6">
         <v>17.5</v>
       </c>
       <c r="BA6">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BB6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD6">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BF6">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BG6">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BH6">
         <v>5.6</v>
@@ -2121,7 +2121,7 @@
         <v>13.5</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BV6">
         <v>55</v>
@@ -2162,61 +2162,61 @@
         <v>110</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H7">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="I7">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="J7">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Y7">
         <v>11</v>
@@ -2231,10 +2231,10 @@
         <v>14.5</v>
       </c>
       <c r="AC7">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE7">
         <v>34</v>
@@ -2264,103 +2264,103 @@
         <v>140</v>
       </c>
       <c r="AN7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO7">
         <v>29</v>
       </c>
       <c r="AP7">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AR7">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT7">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="AU7">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX7">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AY7">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AZ7">
-        <v>3.8</v>
+        <v>16</v>
       </c>
       <c r="BA7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB7">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BC7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD7">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE7">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG7">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="BH7">
         <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7">
         <v>12</v>
       </c>
       <c r="BK7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BL7">
         <v>170</v>
       </c>
       <c r="BM7">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BN7">
         <v>7.8</v>
       </c>
       <c r="BO7">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BP7">
         <v>36</v>
       </c>
       <c r="BQ7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR7">
         <v>55</v>
       </c>
       <c r="BS7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU7">
         <v>2.7</v>
@@ -2369,13 +2369,13 @@
         <v>22</v>
       </c>
       <c r="BW7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BX7">
         <v>42</v>
       </c>
       <c r="BY7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2404,58 +2404,58 @@
         <v>111</v>
       </c>
       <c r="F8">
+        <v>3.9</v>
+      </c>
+      <c r="G8">
+        <v>5.5</v>
+      </c>
+      <c r="H8">
+        <v>1.75</v>
+      </c>
+      <c r="I8">
+        <v>1.95</v>
+      </c>
+      <c r="J8">
         <v>3.8</v>
-      </c>
-      <c r="G8">
-        <v>5.1</v>
-      </c>
-      <c r="H8">
-        <v>1.76</v>
-      </c>
-      <c r="I8">
-        <v>1.96</v>
-      </c>
-      <c r="J8">
-        <v>3.6</v>
       </c>
       <c r="K8">
         <v>5.1</v>
       </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="O8">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
         <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R8">
         <v>1.44</v>
       </c>
       <c r="S8">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="T8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
         <v>2.04</v>
       </c>
       <c r="W8">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -2464,13 +2464,13 @@
         <v>13</v>
       </c>
       <c r="Z8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA8">
         <v>25</v>
       </c>
       <c r="AB8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC8">
         <v>11.5</v>
@@ -2515,7 +2515,7 @@
         <v>14</v>
       </c>
       <c r="AQ8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR8">
         <v>9.199999999999999</v>
@@ -2524,7 +2524,7 @@
         <v>14.5</v>
       </c>
       <c r="AT8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU8">
         <v>7</v>
@@ -2545,37 +2545,37 @@
         <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH8">
         <v>4.6</v>
       </c>
       <c r="BI8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
         <v>120</v>
@@ -2584,7 +2584,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO8">
         <v>6</v>
@@ -2593,13 +2593,13 @@
         <v>42</v>
       </c>
       <c r="BQ8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BR8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BT8">
         <v>5.5</v>
@@ -2817,7 +2817,7 @@
         <v>12</v>
       </c>
       <c r="BK9">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL9">
         <v>170</v>
@@ -2897,10 +2897,10 @@
         <v>1.99</v>
       </c>
       <c r="I10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K10">
         <v>4.5</v>
@@ -2909,7 +2909,7 @@
         <v>1.24</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
         <v>7</v>
@@ -2936,7 +2936,7 @@
         <v>2.96</v>
       </c>
       <c r="V10">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="W10">
         <v>1.37</v>
@@ -2948,7 +2948,7 @@
         <v>17.5</v>
       </c>
       <c r="Z10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA10">
         <v>26</v>
@@ -2981,7 +2981,7 @@
         <v>70</v>
       </c>
       <c r="AK10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL10">
         <v>34</v>
@@ -2996,7 +2996,7 @@
         <v>7.6</v>
       </c>
       <c r="AP10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ10">
         <v>15.5</v>
@@ -3074,10 +3074,10 @@
         <v>5.7</v>
       </c>
       <c r="BP10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BR10">
         <v>27</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -358,7 +358,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 18:55:09</t>
+    <t>2026-09-29 21:05:23</t>
   </si>
 </sst>
 </file>
@@ -952,22 +952,22 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H2">
+        <v>3.25</v>
+      </c>
+      <c r="I2">
+        <v>3.35</v>
+      </c>
+      <c r="J2">
         <v>3.4</v>
       </c>
-      <c r="I2">
-        <v>3.5</v>
-      </c>
-      <c r="J2">
-        <v>3.45</v>
-      </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
         <v>1.42</v>
@@ -979,7 +979,7 @@
         <v>3.85</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
         <v>1.93</v>
@@ -991,19 +991,19 @@
         <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
         <v>1.79</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="X2">
         <v>14</v>
@@ -1012,10 +1012,10 @@
         <v>13</v>
       </c>
       <c r="Z2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB2">
         <v>10.5</v>
@@ -1027,7 +1027,7 @@
         <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF2">
         <v>15.5</v>
@@ -1036,7 +1036,7 @@
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
         <v>48</v>
@@ -1045,7 +1045,7 @@
         <v>32</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL2">
         <v>42</v>
@@ -1057,13 +1057,13 @@
         <v>21</v>
       </c>
       <c r="AO2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP2">
         <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
         <v>20</v>
@@ -1075,7 +1075,7 @@
         <v>9.4</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
         <v>12.5</v>
@@ -1090,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
         <v>42</v>
@@ -1099,25 +1099,25 @@
         <v>28</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD2">
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="BF2">
         <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
         <v>9.4</v>
@@ -1129,49 +1129,49 @@
         <v>140</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="BN2">
         <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP2">
         <v>17.5</v>
       </c>
       <c r="BQ2">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
         <v>27</v>
       </c>
       <c r="BW2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1194,22 +1194,22 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="H3">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="I3">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="J3">
         <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
         <v>1.41</v>
@@ -1218,55 +1218,55 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q3">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
         <v>1.38</v>
       </c>
       <c r="S3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U3">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V3">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="X3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE3">
         <v>30</v>
@@ -1275,22 +1275,22 @@
         <v>22</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH3">
         <v>17.5</v>
       </c>
       <c r="AI3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AJ3">
         <v>55</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM3">
         <v>110</v>
@@ -1299,22 +1299,22 @@
         <v>32</v>
       </c>
       <c r="AO3">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AP3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU3">
         <v>7</v>
@@ -1323,13 +1323,13 @@
         <v>10</v>
       </c>
       <c r="AW3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
         <v>15</v>
@@ -1338,82 +1338,82 @@
         <v>30</v>
       </c>
       <c r="BB3">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BC3">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BD3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>75</v>
       </c>
       <c r="BF3">
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BH3">
         <v>3.9</v>
       </c>
       <c r="BI3">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>7.2</v>
+        <v>3.85</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>90</v>
       </c>
       <c r="BN3">
         <v>7</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BP3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="BR3">
         <v>40</v>
       </c>
       <c r="BS3">
-        <v>25</v>
+        <v>5.3</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BW3">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="BX3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY3">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="BZ3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA3">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1436,58 +1436,58 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G4">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H4">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
         <v>1.54</v>
       </c>
       <c r="S4">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X4">
         <v>25</v>
@@ -1496,7 +1496,7 @@
         <v>17.5</v>
       </c>
       <c r="Z4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4">
         <v>55</v>
@@ -1514,13 +1514,13 @@
         <v>32</v>
       </c>
       <c r="AF4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI4">
         <v>40</v>
@@ -1529,7 +1529,7 @@
         <v>34</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL4">
         <v>36</v>
@@ -1538,7 +1538,7 @@
         <v>70</v>
       </c>
       <c r="AN4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO4">
         <v>21</v>
@@ -1553,7 +1553,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4">
         <v>12.5</v>
@@ -1562,22 +1562,22 @@
         <v>8</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX4">
         <v>15.5</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BB4">
         <v>16</v>
@@ -1586,10 +1586,10 @@
         <v>19</v>
       </c>
       <c r="BD4">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BE4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
@@ -1607,7 +1607,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>90</v>
@@ -1619,16 +1619,16 @@
         <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
@@ -1655,7 +1655,7 @@
         <v>20</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB4" t="s">
         <v>114</v>
@@ -1681,22 +1681,22 @@
         <v>4.2</v>
       </c>
       <c r="G5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H5">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="I5">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1717,7 +1717,7 @@
         <v>1.51</v>
       </c>
       <c r="S5">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="T5">
         <v>1.66</v>
@@ -1726,16 +1726,16 @@
         <v>2.28</v>
       </c>
       <c r="V5">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="W5">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
         <v>13.5</v>
@@ -1747,22 +1747,22 @@
         <v>21</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
         <v>11</v>
       </c>
       <c r="AE5">
+        <v>19</v>
+      </c>
+      <c r="AF5">
+        <v>85</v>
+      </c>
+      <c r="AG5">
+        <v>18.5</v>
+      </c>
+      <c r="AH5">
         <v>21</v>
-      </c>
-      <c r="AF5">
-        <v>100</v>
-      </c>
-      <c r="AG5">
-        <v>26</v>
-      </c>
-      <c r="AH5">
-        <v>18</v>
       </c>
       <c r="AI5">
         <v>36</v>
@@ -1774,7 +1774,7 @@
         <v>60</v>
       </c>
       <c r="AL5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM5">
         <v>200</v>
@@ -1786,10 +1786,10 @@
         <v>9.6</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR5">
         <v>11</v>
@@ -1798,13 +1798,13 @@
         <v>17.5</v>
       </c>
       <c r="AT5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU5">
         <v>8.4</v>
       </c>
       <c r="AV5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5">
         <v>15.5</v>
@@ -1822,7 +1822,7 @@
         <v>14.5</v>
       </c>
       <c r="BB5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5">
         <v>34</v>
@@ -1837,7 +1837,7 @@
         <v>30</v>
       </c>
       <c r="BG5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
@@ -1849,7 +1849,7 @@
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL5">
         <v>120</v>
@@ -1867,7 +1867,7 @@
         <v>40</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BR5">
         <v>46</v>
@@ -1879,13 +1879,13 @@
         <v>5.6</v>
       </c>
       <c r="BU5">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BV5">
         <v>14.5</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
         <v>28</v>
@@ -1926,7 +1926,7 @@
         <v>1.46</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>8.800000000000001</v>
@@ -1965,13 +1965,13 @@
         <v>1.73</v>
       </c>
       <c r="U6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X6">
         <v>38</v>
@@ -1989,7 +1989,7 @@
         <v>13</v>
       </c>
       <c r="AC6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD6">
         <v>32</v>
@@ -2010,7 +2010,7 @@
         <v>90</v>
       </c>
       <c r="AJ6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AK6">
         <v>14.5</v>
@@ -2022,7 +2022,7 @@
         <v>110</v>
       </c>
       <c r="AN6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO6">
         <v>100</v>
@@ -2031,25 +2031,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="AR6">
+        <v>30</v>
+      </c>
+      <c r="AS6">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AS6">
-        <v>22</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV6">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW6">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="AX6">
         <v>9.6</v>
@@ -2058,13 +2058,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA6">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BB6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC6">
         <v>12</v>
@@ -2073,13 +2073,13 @@
         <v>14.5</v>
       </c>
       <c r="BE6">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="BF6">
         <v>4.3</v>
       </c>
       <c r="BG6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH6">
         <v>5.6</v>
@@ -2165,19 +2165,19 @@
         <v>3.3</v>
       </c>
       <c r="G7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I7">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2186,16 +2186,16 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R7">
         <v>1.29</v>
@@ -2204,16 +2204,16 @@
         <v>3.5</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
         <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X7">
         <v>15</v>
@@ -2222,7 +2222,7 @@
         <v>11</v>
       </c>
       <c r="Z7">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AA7">
         <v>40</v>
@@ -2279,7 +2279,7 @@
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT7">
         <v>10.5</v>
@@ -2291,34 +2291,34 @@
         <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX7">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AZ7">
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE7">
+        <v>4.9</v>
+      </c>
+      <c r="BF7">
         <v>4.7</v>
-      </c>
-      <c r="BF7">
-        <v>4.5</v>
       </c>
       <c r="BG7">
         <v>5.7</v>
@@ -2407,7 +2407,7 @@
         <v>3.9</v>
       </c>
       <c r="G8">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H8">
         <v>1.75</v>
@@ -2416,52 +2416,52 @@
         <v>1.95</v>
       </c>
       <c r="J8">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>2.46</v>
+        <v>3.85</v>
       </c>
       <c r="O8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="Q8">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R8">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S8">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T8">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="U8">
         <v>2.18</v>
       </c>
       <c r="V8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X8">
         <v>24</v>
       </c>
       <c r="Y8">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z8">
         <v>15.5</v>
@@ -2476,7 +2476,7 @@
         <v>11.5</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
         <v>22</v>
@@ -2521,16 +2521,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS8">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU8">
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8">
         <v>13</v>
@@ -2548,19 +2548,19 @@
         <v>21</v>
       </c>
       <c r="BB8">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
         <v>7.2</v>
@@ -2649,10 +2649,10 @@
         <v>3.05</v>
       </c>
       <c r="G9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H9">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I9">
         <v>2.58</v>
@@ -2664,19 +2664,19 @@
         <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M9">
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O9">
         <v>1.38</v>
       </c>
       <c r="P9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q9">
         <v>2.14</v>
@@ -2694,7 +2694,7 @@
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W9">
         <v>1.45</v>
@@ -2727,31 +2727,31 @@
         <v>22</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH9">
         <v>19.5</v>
       </c>
       <c r="AI9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK9">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>310</v>
       </c>
       <c r="AM9">
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AO9">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP9">
         <v>11</v>
@@ -2760,7 +2760,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS9">
         <v>28</v>
@@ -2775,7 +2775,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX9">
         <v>18</v>
@@ -2790,19 +2790,19 @@
         <v>36</v>
       </c>
       <c r="BB9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC9">
         <v>25</v>
       </c>
       <c r="BD9">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BE9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BF9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BG9">
         <v>21</v>
@@ -2897,7 +2897,7 @@
         <v>1.99</v>
       </c>
       <c r="I10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J10">
         <v>4.3</v>
@@ -2906,7 +2906,7 @@
         <v>4.5</v>
       </c>
       <c r="L10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M10">
         <v>1.02</v>
@@ -2921,22 +2921,22 @@
         <v>3</v>
       </c>
       <c r="Q10">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S10">
         <v>2.14</v>
       </c>
       <c r="T10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U10">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="V10">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="W10">
         <v>1.37</v>
@@ -2960,7 +2960,7 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE10">
         <v>17.5</v>
@@ -2987,7 +2987,7 @@
         <v>34</v>
       </c>
       <c r="AM10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN10">
         <v>21</v>
@@ -3014,7 +3014,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW10">
         <v>15.5</v>
@@ -3044,10 +3044,10 @@
         <v>40</v>
       </c>
       <c r="BF10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH10">
         <v>5.3</v>
@@ -3068,7 +3068,7 @@
         <v>42</v>
       </c>
       <c r="BN10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO10">
         <v>5.7</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -358,7 +358,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-29 21:05:23</t>
+    <t>2026-09-29 23:15:49</t>
   </si>
 </sst>
 </file>
@@ -952,226 +952,226 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>27</v>
       </c>
       <c r="H2">
-        <v>3.25</v>
+        <v>1.38</v>
       </c>
       <c r="I2">
-        <v>3.35</v>
+        <v>1.9</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>110</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>3.75</v>
       </c>
       <c r="S2">
-        <v>3.65</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.69</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE2">
-        <v>42</v>
+        <v>720</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>730</v>
+      </c>
+      <c r="AI2">
+        <v>990</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>840</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.54</v>
+      </c>
+      <c r="AQ2">
+        <v>1.54</v>
+      </c>
+      <c r="AR2">
+        <v>1.54</v>
+      </c>
+      <c r="AS2">
+        <v>1.54</v>
+      </c>
+      <c r="AT2">
+        <v>1.54</v>
+      </c>
+      <c r="AU2">
+        <v>1.54</v>
+      </c>
+      <c r="AV2">
+        <v>1.39</v>
+      </c>
+      <c r="AW2">
+        <v>1.67</v>
+      </c>
+      <c r="AX2">
+        <v>1.54</v>
+      </c>
+      <c r="AY2">
+        <v>1.54</v>
+      </c>
+      <c r="AZ2">
+        <v>2.86</v>
+      </c>
+      <c r="BA2">
+        <v>1.54</v>
+      </c>
+      <c r="BB2">
+        <v>1.54</v>
+      </c>
+      <c r="BC2">
+        <v>1.54</v>
+      </c>
+      <c r="BD2">
         <v>11.5</v>
       </c>
-      <c r="AH2">
-        <v>17.5</v>
-      </c>
-      <c r="AI2">
-        <v>48</v>
-      </c>
-      <c r="AJ2">
-        <v>32</v>
-      </c>
-      <c r="AK2">
-        <v>26</v>
-      </c>
-      <c r="AL2">
-        <v>42</v>
-      </c>
-      <c r="AM2">
-        <v>110</v>
-      </c>
-      <c r="AN2">
-        <v>21</v>
-      </c>
-      <c r="AO2">
-        <v>38</v>
-      </c>
-      <c r="AP2">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2">
-        <v>11.5</v>
-      </c>
-      <c r="AR2">
-        <v>20</v>
-      </c>
-      <c r="AS2">
-        <v>50</v>
-      </c>
-      <c r="AT2">
-        <v>9.4</v>
-      </c>
-      <c r="AU2">
-        <v>7.2</v>
-      </c>
-      <c r="AV2">
-        <v>12.5</v>
-      </c>
-      <c r="AW2">
-        <v>34</v>
-      </c>
-      <c r="AX2">
-        <v>13.5</v>
-      </c>
-      <c r="AY2">
-        <v>10</v>
-      </c>
-      <c r="AZ2">
-        <v>15.5</v>
-      </c>
-      <c r="BA2">
-        <v>42</v>
-      </c>
-      <c r="BB2">
-        <v>28</v>
-      </c>
-      <c r="BC2">
-        <v>23</v>
-      </c>
-      <c r="BD2">
-        <v>34</v>
-      </c>
       <c r="BE2">
-        <v>75</v>
+        <v>2.32</v>
       </c>
       <c r="BF2">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="BG2">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1194,226 +1194,226 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="G3">
-        <v>3.15</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>2.42</v>
+        <v>1.43</v>
       </c>
       <c r="I3">
+        <v>1.5</v>
+      </c>
+      <c r="J3">
+        <v>4.7</v>
+      </c>
+      <c r="K3">
+        <v>5.6</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>11</v>
+      </c>
+      <c r="O3">
+        <v>1.05</v>
+      </c>
+      <c r="P3">
+        <v>3.2</v>
+      </c>
+      <c r="Q3">
+        <v>1.4</v>
+      </c>
+      <c r="R3">
+        <v>1.71</v>
+      </c>
+      <c r="S3">
+        <v>2.16</v>
+      </c>
+      <c r="T3">
+        <v>1.44</v>
+      </c>
+      <c r="U3">
+        <v>2.88</v>
+      </c>
+      <c r="V3">
+        <v>2.92</v>
+      </c>
+      <c r="W3">
+        <v>1.13</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>12.5</v>
+      </c>
+      <c r="Z3">
+        <v>10</v>
+      </c>
+      <c r="AA3">
+        <v>15.5</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>11</v>
+      </c>
+      <c r="AD3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE3">
+        <v>13</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>20</v>
+      </c>
+      <c r="AH3">
+        <v>14</v>
+      </c>
+      <c r="AI3">
+        <v>23</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>75</v>
+      </c>
+      <c r="AL3">
+        <v>42</v>
+      </c>
+      <c r="AM3">
+        <v>65</v>
+      </c>
+      <c r="AN3">
+        <v>65</v>
+      </c>
+      <c r="AO3">
+        <v>8</v>
+      </c>
+      <c r="AP3">
+        <v>9.4</v>
+      </c>
+      <c r="AQ3">
+        <v>10.5</v>
+      </c>
+      <c r="AR3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS3">
+        <v>13</v>
+      </c>
+      <c r="AT3">
+        <v>9.4</v>
+      </c>
+      <c r="AU3">
+        <v>8.6</v>
+      </c>
+      <c r="AV3">
+        <v>7</v>
+      </c>
+      <c r="AW3">
+        <v>11</v>
+      </c>
+      <c r="AX3">
+        <v>9.4</v>
+      </c>
+      <c r="AY3">
+        <v>16.5</v>
+      </c>
+      <c r="AZ3">
+        <v>12</v>
+      </c>
+      <c r="BA3">
+        <v>15</v>
+      </c>
+      <c r="BB3">
+        <v>9.4</v>
+      </c>
+      <c r="BC3">
+        <v>8.4</v>
+      </c>
+      <c r="BD3">
+        <v>8</v>
+      </c>
+      <c r="BE3">
+        <v>8.4</v>
+      </c>
+      <c r="BF3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG3">
+        <v>6.6</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>8</v>
+      </c>
+      <c r="BJ3">
+        <v>6.8</v>
+      </c>
+      <c r="BK3">
+        <v>5.1</v>
+      </c>
+      <c r="BL3">
+        <v>75</v>
+      </c>
+      <c r="BM3">
+        <v>8</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>6.8</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>6.8</v>
+      </c>
+      <c r="BR3">
+        <v>38</v>
+      </c>
+      <c r="BS3">
+        <v>27</v>
+      </c>
+      <c r="BT3">
+        <v>2.86</v>
+      </c>
+      <c r="BU3">
         <v>2.52</v>
       </c>
-      <c r="J3">
-        <v>3.6</v>
-      </c>
-      <c r="K3">
-        <v>3.8</v>
-      </c>
-      <c r="L3">
-        <v>1.41</v>
-      </c>
-      <c r="M3">
-        <v>1.06</v>
-      </c>
-      <c r="N3">
-        <v>4</v>
-      </c>
-      <c r="O3">
-        <v>1.31</v>
-      </c>
-      <c r="P3">
-        <v>2.02</v>
-      </c>
-      <c r="Q3">
-        <v>1.92</v>
-      </c>
-      <c r="R3">
-        <v>1.38</v>
-      </c>
-      <c r="S3">
-        <v>3.4</v>
-      </c>
-      <c r="T3">
-        <v>1.71</v>
-      </c>
-      <c r="U3">
-        <v>2.22</v>
-      </c>
-      <c r="V3">
-        <v>1.65</v>
-      </c>
-      <c r="W3">
-        <v>1.46</v>
-      </c>
-      <c r="X3">
-        <v>15.5</v>
-      </c>
-      <c r="Y3">
-        <v>11.5</v>
-      </c>
-      <c r="Z3">
-        <v>17</v>
-      </c>
-      <c r="AA3">
-        <v>40</v>
-      </c>
-      <c r="AB3">
-        <v>14.5</v>
-      </c>
-      <c r="AC3">
-        <v>8.4</v>
-      </c>
-      <c r="AD3">
-        <v>12</v>
-      </c>
-      <c r="AE3">
-        <v>30</v>
-      </c>
-      <c r="AF3">
-        <v>22</v>
-      </c>
-      <c r="AG3">
+      <c r="BV3">
+        <v>5.6</v>
+      </c>
+      <c r="BW3">
+        <v>4.6</v>
+      </c>
+      <c r="BX3">
         <v>14</v>
       </c>
-      <c r="AH3">
-        <v>17.5</v>
-      </c>
-      <c r="AI3">
-        <v>50</v>
-      </c>
-      <c r="AJ3">
-        <v>55</v>
-      </c>
-      <c r="AK3">
-        <v>44</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>110</v>
-      </c>
-      <c r="AN3">
-        <v>32</v>
-      </c>
-      <c r="AO3">
-        <v>21</v>
-      </c>
-      <c r="AP3">
-        <v>13</v>
-      </c>
-      <c r="AQ3">
-        <v>9.6</v>
-      </c>
-      <c r="AR3">
-        <v>14</v>
-      </c>
-      <c r="AS3">
-        <v>25</v>
-      </c>
-      <c r="AT3">
-        <v>11</v>
-      </c>
-      <c r="AU3">
-        <v>7</v>
-      </c>
-      <c r="AV3">
+      <c r="BY3">
         <v>10</v>
       </c>
-      <c r="AW3">
-        <v>22</v>
-      </c>
-      <c r="AX3">
-        <v>17.5</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>15</v>
-      </c>
-      <c r="BA3">
-        <v>30</v>
-      </c>
-      <c r="BB3">
-        <v>34</v>
-      </c>
-      <c r="BC3">
-        <v>25</v>
-      </c>
-      <c r="BD3">
-        <v>30</v>
-      </c>
-      <c r="BE3">
-        <v>75</v>
-      </c>
-      <c r="BF3">
-        <v>21</v>
-      </c>
-      <c r="BG3">
-        <v>17</v>
-      </c>
-      <c r="BH3">
-        <v>3.9</v>
-      </c>
-      <c r="BI3">
-        <v>3.1</v>
-      </c>
-      <c r="BJ3">
-        <v>10.5</v>
-      </c>
-      <c r="BK3">
-        <v>3.85</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>90</v>
-      </c>
-      <c r="BN3">
-        <v>7</v>
-      </c>
-      <c r="BO3">
-        <v>5.4</v>
-      </c>
-      <c r="BP3">
-        <v>27</v>
-      </c>
-      <c r="BQ3">
-        <v>5</v>
-      </c>
-      <c r="BR3">
-        <v>40</v>
-      </c>
-      <c r="BS3">
-        <v>5.3</v>
-      </c>
-      <c r="BT3">
-        <v>6.2</v>
-      </c>
-      <c r="BU3">
-        <v>4.8</v>
-      </c>
-      <c r="BV3">
-        <v>21</v>
-      </c>
-      <c r="BW3">
-        <v>4.7</v>
-      </c>
-      <c r="BX3">
-        <v>34</v>
-      </c>
-      <c r="BY3">
-        <v>5.2</v>
-      </c>
       <c r="BZ3">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="CA3">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1436,19 +1436,19 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
         <v>3.9</v>
@@ -1457,7 +1457,7 @@
         <v>1.28</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -1469,7 +1469,7 @@
         <v>2.34</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
         <v>1.54</v>
@@ -1484,7 +1484,7 @@
         <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
         <v>1.65</v>
@@ -1493,7 +1493,7 @@
         <v>25</v>
       </c>
       <c r="Y4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z4">
         <v>24</v>
@@ -1520,7 +1520,7 @@
         <v>13</v>
       </c>
       <c r="AH4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI4">
         <v>40</v>
@@ -1538,7 +1538,7 @@
         <v>70</v>
       </c>
       <c r="AN4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO4">
         <v>21</v>
@@ -1589,7 +1589,7 @@
         <v>16</v>
       </c>
       <c r="BE4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
@@ -1607,7 +1607,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>90</v>
@@ -1619,7 +1619,7 @@
         <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
         <v>19</v>
@@ -1628,7 +1628,7 @@
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
@@ -1637,7 +1637,7 @@
         <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
         <v>24</v>
@@ -1655,7 +1655,7 @@
         <v>20</v>
       </c>
       <c r="CA4">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>114</v>
@@ -1687,7 +1687,7 @@
         <v>1.81</v>
       </c>
       <c r="I5">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -1696,7 +1696,7 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1726,7 +1726,7 @@
         <v>2.28</v>
       </c>
       <c r="V5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W5">
         <v>1.27</v>
@@ -1741,7 +1741,7 @@
         <v>13.5</v>
       </c>
       <c r="AA5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB5">
         <v>21</v>
@@ -1822,7 +1822,7 @@
         <v>14.5</v>
       </c>
       <c r="BB5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC5">
         <v>34</v>
@@ -1837,7 +1837,7 @@
         <v>30</v>
       </c>
       <c r="BG5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
@@ -1861,13 +1861,13 @@
         <v>9.6</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BP5">
         <v>40</v>
       </c>
       <c r="BQ5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>46</v>
@@ -1879,13 +1879,13 @@
         <v>5.6</v>
       </c>
       <c r="BU5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV5">
         <v>14.5</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
         <v>28</v>
@@ -1959,13 +1959,13 @@
         <v>1.73</v>
       </c>
       <c r="S6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T6">
         <v>1.73</v>
       </c>
       <c r="U6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
         <v>1.12</v>
@@ -1989,7 +1989,7 @@
         <v>13</v>
       </c>
       <c r="AC6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AD6">
         <v>32</v>
@@ -2034,10 +2034,10 @@
         <v>19.5</v>
       </c>
       <c r="AR6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2049,7 +2049,7 @@
         <v>17.5</v>
       </c>
       <c r="AW6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX6">
         <v>9.6</v>
@@ -2061,7 +2061,7 @@
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB6">
         <v>11</v>
@@ -2165,13 +2165,13 @@
         <v>3.3</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H7">
         <v>2.26</v>
       </c>
       <c r="I7">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J7">
         <v>3.2</v>
@@ -2189,10 +2189,10 @@
         <v>3.3</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
         <v>2.12</v>
@@ -2210,10 +2210,10 @@
         <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W7">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X7">
         <v>15</v>
@@ -2306,7 +2306,7 @@
         <v>4.7</v>
       </c>
       <c r="BB7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC7">
         <v>4.7</v>
@@ -2404,40 +2404,40 @@
         <v>111</v>
       </c>
       <c r="F8">
+        <v>4.2</v>
+      </c>
+      <c r="G8">
+        <v>5.4</v>
+      </c>
+      <c r="H8">
+        <v>1.76</v>
+      </c>
+      <c r="I8">
+        <v>1.92</v>
+      </c>
+      <c r="J8">
         <v>3.9</v>
       </c>
-      <c r="G8">
-        <v>5.7</v>
-      </c>
-      <c r="H8">
-        <v>1.75</v>
-      </c>
-      <c r="I8">
-        <v>1.95</v>
-      </c>
-      <c r="J8">
-        <v>3.25</v>
-      </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O8">
         <v>1.23</v>
       </c>
       <c r="P8">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R8">
         <v>1.52</v>
@@ -2446,13 +2446,13 @@
         <v>2.7</v>
       </c>
       <c r="T8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U8">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W8">
         <v>1.25</v>
@@ -2515,7 +2515,7 @@
         <v>14</v>
       </c>
       <c r="AQ8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR8">
         <v>9.199999999999999</v>
@@ -2554,7 +2554,7 @@
         <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE8">
         <v>1.01</v>
@@ -2581,7 +2581,7 @@
         <v>120</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BN8">
         <v>9.800000000000001</v>
@@ -2652,7 +2652,7 @@
         <v>3.2</v>
       </c>
       <c r="H9">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I9">
         <v>2.58</v>
@@ -2676,19 +2676,19 @@
         <v>1.38</v>
       </c>
       <c r="P9">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R9">
         <v>1.32</v>
       </c>
       <c r="S9">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T9">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U9">
         <v>2.06</v>
@@ -2730,7 +2730,7 @@
         <v>14</v>
       </c>
       <c r="AH9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI9">
         <v>55</v>
@@ -2742,16 +2742,16 @@
         <v>46</v>
       </c>
       <c r="AL9">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AM9">
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP9">
         <v>11</v>
@@ -2808,10 +2808,10 @@
         <v>21</v>
       </c>
       <c r="BH9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI9">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BJ9">
         <v>12</v>
@@ -2820,7 +2820,7 @@
         <v>3.45</v>
       </c>
       <c r="BL9">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM9">
         <v>4.7</v>
@@ -2838,7 +2838,7 @@
         <v>4.2</v>
       </c>
       <c r="BR9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS9">
         <v>4.4</v>
@@ -2856,13 +2856,13 @@
         <v>4</v>
       </c>
       <c r="BX9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY9">
         <v>4.3</v>
       </c>
       <c r="BZ9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA9">
         <v>4.3</v>
@@ -2891,16 +2891,16 @@
         <v>3.6</v>
       </c>
       <c r="G10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H10">
+        <v>1.98</v>
+      </c>
+      <c r="I10">
         <v>1.99</v>
       </c>
-      <c r="I10">
-        <v>2.02</v>
-      </c>
       <c r="J10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K10">
         <v>4.5</v>
@@ -2912,7 +2912,7 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O10">
         <v>1.15</v>
@@ -2924,7 +2924,7 @@
         <v>1.46</v>
       </c>
       <c r="R10">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S10">
         <v>2.14</v>
@@ -2933,25 +2933,25 @@
         <v>1.48</v>
       </c>
       <c r="U10">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X10">
         <v>34</v>
       </c>
       <c r="Y10">
+        <v>18</v>
+      </c>
+      <c r="Z10">
         <v>17.5</v>
       </c>
-      <c r="Z10">
-        <v>18</v>
-      </c>
       <c r="AA10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB10">
         <v>26</v>
@@ -2960,22 +2960,22 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE10">
         <v>17.5</v>
       </c>
       <c r="AF10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG10">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AH10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ10">
         <v>70</v>
@@ -2987,10 +2987,10 @@
         <v>34</v>
       </c>
       <c r="AM10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AN10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO10">
         <v>7.6</v>
@@ -2999,25 +2999,25 @@
         <v>28</v>
       </c>
       <c r="AQ10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT10">
         <v>22</v>
       </c>
       <c r="AU10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV10">
         <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AX10">
         <v>30</v>
@@ -3026,13 +3026,13 @@
         <v>14.5</v>
       </c>
       <c r="AZ10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA10">
         <v>20</v>
       </c>
       <c r="BB10">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BC10">
         <v>30</v>
@@ -3044,16 +3044,16 @@
         <v>40</v>
       </c>
       <c r="BF10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG10">
         <v>6.8</v>
       </c>
       <c r="BH10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI10">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BJ10">
         <v>8.800000000000001</v>
@@ -3068,7 +3068,7 @@
         <v>42</v>
       </c>
       <c r="BN10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO10">
         <v>5.7</v>
@@ -3089,22 +3089,22 @@
         <v>5.8</v>
       </c>
       <c r="BU10">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BW10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10">
         <v>20</v>
       </c>
       <c r="BY10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA10">
         <v>9</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
   <si>
     <t>League</t>
   </si>
@@ -256,6 +256,9 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Nigerian Premier League</t>
+  </si>
+  <si>
     <t>English National League</t>
   </si>
   <si>
@@ -277,6 +280,9 @@
     <t>2026-09-30</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>18:45:00</t>
   </si>
   <si>
@@ -292,6 +298,12 @@
     <t>23:30:00</t>
   </si>
   <si>
+    <t>Sporting Lagos FC</t>
+  </si>
+  <si>
+    <t>Enyimba</t>
+  </si>
+  <si>
     <t>Tamworth FC</t>
   </si>
   <si>
@@ -313,6 +325,12 @@
     <t>New York Red Bulls</t>
   </si>
   <si>
+    <t>Ikorodu City</t>
+  </si>
+  <si>
+    <t>Shooting Stars</t>
+  </si>
+  <si>
     <t>Sutton Utd</t>
   </si>
   <si>
@@ -334,7 +352,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-30 01:26:25</t>
+    <t>2026-09-30 03:37:03</t>
   </si>
 </sst>
 </file>
@@ -666,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -916,241 +934,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>150</v>
       </c>
       <c r="H2">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="I2">
-        <v>3.1</v>
+        <v>150</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>110</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
         <v>1.04</v>
       </c>
-      <c r="N2">
-        <v>5.1</v>
-      </c>
       <c r="O2">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="Q2">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R2">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="S2">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="T2">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1158,241 +1176,241 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F3">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="G3">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="H3">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="I3">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L3">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P3">
-        <v>2.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q3">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R3">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="T3">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1400,1209 +1418,1693 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F4">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="G4">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>2.94</v>
       </c>
       <c r="I4">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="O4">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="S4">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="U4">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>3.15</v>
+        <v>1.67</v>
       </c>
       <c r="X4">
+        <v>25</v>
+      </c>
+      <c r="Y4">
+        <v>17</v>
+      </c>
+      <c r="Z4">
+        <v>24</v>
+      </c>
+      <c r="AA4">
+        <v>55</v>
+      </c>
+      <c r="AB4">
+        <v>15</v>
+      </c>
+      <c r="AC4">
+        <v>9</v>
+      </c>
+      <c r="AD4">
+        <v>14.5</v>
+      </c>
+      <c r="AE4">
+        <v>32</v>
+      </c>
+      <c r="AF4">
+        <v>19</v>
+      </c>
+      <c r="AG4">
+        <v>13</v>
+      </c>
+      <c r="AH4">
+        <v>17</v>
+      </c>
+      <c r="AI4">
+        <v>42</v>
+      </c>
+      <c r="AJ4">
+        <v>34</v>
+      </c>
+      <c r="AK4">
+        <v>24</v>
+      </c>
+      <c r="AL4">
+        <v>36</v>
+      </c>
+      <c r="AM4">
+        <v>70</v>
+      </c>
+      <c r="AN4">
+        <v>14</v>
+      </c>
+      <c r="AO4">
+        <v>21</v>
+      </c>
+      <c r="AP4">
+        <v>18</v>
+      </c>
+      <c r="AQ4">
+        <v>14</v>
+      </c>
+      <c r="AR4">
+        <v>19.5</v>
+      </c>
+      <c r="AS4">
         <v>38</v>
       </c>
-      <c r="Y4">
-        <v>38</v>
-      </c>
-      <c r="Z4">
+      <c r="AT4">
+        <v>12</v>
+      </c>
+      <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>14.5</v>
+      </c>
+      <c r="AX4">
+        <v>15.5</v>
+      </c>
+      <c r="AY4">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4">
+        <v>13</v>
+      </c>
+      <c r="BA4">
+        <v>18.5</v>
+      </c>
+      <c r="BB4">
+        <v>16.5</v>
+      </c>
+      <c r="BC4">
+        <v>19.5</v>
+      </c>
+      <c r="BD4">
+        <v>25</v>
+      </c>
+      <c r="BE4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF4">
+        <v>12</v>
+      </c>
+      <c r="BG4">
+        <v>17</v>
+      </c>
+      <c r="BH4">
+        <v>4.7</v>
+      </c>
+      <c r="BI4">
+        <v>3.4</v>
+      </c>
+      <c r="BJ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4">
+        <v>6.8</v>
+      </c>
+      <c r="BL4">
         <v>90</v>
-      </c>
-      <c r="AA4">
-        <v>250</v>
-      </c>
-      <c r="AB4">
-        <v>13</v>
-      </c>
-      <c r="AC4">
-        <v>14</v>
-      </c>
-      <c r="AD4">
-        <v>32</v>
-      </c>
-      <c r="AE4">
-        <v>110</v>
-      </c>
-      <c r="AF4">
-        <v>11.5</v>
-      </c>
-      <c r="AG4">
-        <v>11.5</v>
-      </c>
-      <c r="AH4">
-        <v>22</v>
-      </c>
-      <c r="AI4">
-        <v>90</v>
-      </c>
-      <c r="AJ4">
-        <v>14</v>
-      </c>
-      <c r="AK4">
-        <v>14.5</v>
-      </c>
-      <c r="AL4">
-        <v>28</v>
-      </c>
-      <c r="AM4">
-        <v>110</v>
-      </c>
-      <c r="AN4">
-        <v>4.8</v>
-      </c>
-      <c r="AO4">
-        <v>100</v>
-      </c>
-      <c r="AP4">
-        <v>14.5</v>
-      </c>
-      <c r="AQ4">
-        <v>19.5</v>
-      </c>
-      <c r="AR4">
-        <v>34</v>
-      </c>
-      <c r="AS4">
-        <v>9</v>
-      </c>
-      <c r="AT4">
-        <v>11</v>
-      </c>
-      <c r="AU4">
-        <v>11</v>
-      </c>
-      <c r="AV4">
-        <v>17.5</v>
-      </c>
-      <c r="AW4">
-        <v>42</v>
-      </c>
-      <c r="AX4">
-        <v>9.6</v>
-      </c>
-      <c r="AY4">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4">
-        <v>18</v>
-      </c>
-      <c r="BA4">
-        <v>32</v>
-      </c>
-      <c r="BB4">
-        <v>11.5</v>
-      </c>
-      <c r="BC4">
-        <v>12</v>
-      </c>
-      <c r="BD4">
-        <v>14.5</v>
-      </c>
-      <c r="BE4">
-        <v>38</v>
-      </c>
-      <c r="BF4">
-        <v>4.3</v>
-      </c>
-      <c r="BG4">
-        <v>15</v>
-      </c>
-      <c r="BH4">
-        <v>5.6</v>
-      </c>
-      <c r="BI4">
-        <v>3.7</v>
-      </c>
-      <c r="BJ4">
-        <v>10.5</v>
-      </c>
-      <c r="BK4">
-        <v>1.01</v>
-      </c>
-      <c r="BL4">
-        <v>120</v>
       </c>
       <c r="BM4">
         <v>1.02</v>
       </c>
       <c r="BN4">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BR4">
+        <v>28</v>
+      </c>
+      <c r="BS4">
+        <v>1.02</v>
+      </c>
+      <c r="BT4">
+        <v>7.4</v>
+      </c>
+      <c r="BU4">
+        <v>5.2</v>
+      </c>
+      <c r="BV4">
         <v>24</v>
       </c>
-      <c r="BS4">
-        <v>1.01</v>
-      </c>
-      <c r="BT4">
-        <v>12</v>
-      </c>
-      <c r="BU4">
-        <v>1.01</v>
-      </c>
-      <c r="BV4">
-        <v>60</v>
-      </c>
       <c r="BW4">
         <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ4">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F5">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="G5">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="H5">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="I5">
-        <v>2.48</v>
+        <v>1.88</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
+        <v>1.65</v>
+      </c>
+      <c r="R5">
+        <v>1.59</v>
+      </c>
+      <c r="S5">
+        <v>2.62</v>
+      </c>
+      <c r="T5">
+        <v>1.53</v>
+      </c>
+      <c r="U5">
+        <v>2.52</v>
+      </c>
+      <c r="V5">
         <v>2.12</v>
       </c>
-      <c r="R5">
-        <v>1.29</v>
-      </c>
-      <c r="S5">
-        <v>3.85</v>
-      </c>
-      <c r="T5">
-        <v>1.84</v>
-      </c>
-      <c r="U5">
-        <v>2.02</v>
-      </c>
-      <c r="V5">
-        <v>1.67</v>
-      </c>
       <c r="W5">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="X5">
+        <v>32</v>
+      </c>
+      <c r="Y5">
+        <v>14</v>
+      </c>
+      <c r="Z5">
         <v>15</v>
       </c>
-      <c r="Y5">
+      <c r="AA5">
+        <v>25</v>
+      </c>
+      <c r="AB5">
+        <v>23</v>
+      </c>
+      <c r="AC5">
+        <v>9.4</v>
+      </c>
+      <c r="AD5">
+        <v>10.5</v>
+      </c>
+      <c r="AE5">
+        <v>17</v>
+      </c>
+      <c r="AF5">
+        <v>46</v>
+      </c>
+      <c r="AG5">
+        <v>17</v>
+      </c>
+      <c r="AH5">
+        <v>20</v>
+      </c>
+      <c r="AI5">
+        <v>60</v>
+      </c>
+      <c r="AJ5">
+        <v>900</v>
+      </c>
+      <c r="AK5">
+        <v>190</v>
+      </c>
+      <c r="AL5">
+        <v>60</v>
+      </c>
+      <c r="AM5">
+        <v>75</v>
+      </c>
+      <c r="AN5">
+        <v>260</v>
+      </c>
+      <c r="AO5">
+        <v>9</v>
+      </c>
+      <c r="AP5">
+        <v>20</v>
+      </c>
+      <c r="AQ5">
         <v>11</v>
       </c>
-      <c r="Z5">
-        <v>15.5</v>
-      </c>
-      <c r="AA5">
-        <v>40</v>
-      </c>
-      <c r="AB5">
-        <v>14.5</v>
-      </c>
-      <c r="AC5">
-        <v>8</v>
-      </c>
-      <c r="AD5">
+      <c r="AR5">
         <v>12</v>
-      </c>
-      <c r="AE5">
-        <v>34</v>
-      </c>
-      <c r="AF5">
-        <v>30</v>
-      </c>
-      <c r="AG5">
-        <v>18</v>
-      </c>
-      <c r="AH5">
-        <v>23</v>
-      </c>
-      <c r="AI5">
-        <v>55</v>
-      </c>
-      <c r="AJ5">
-        <v>85</v>
-      </c>
-      <c r="AK5">
-        <v>55</v>
-      </c>
-      <c r="AL5">
-        <v>70</v>
-      </c>
-      <c r="AM5">
-        <v>140</v>
-      </c>
-      <c r="AN5">
-        <v>60</v>
-      </c>
-      <c r="AO5">
-        <v>29</v>
-      </c>
-      <c r="AP5">
-        <v>5.8</v>
-      </c>
-      <c r="AQ5">
-        <v>8</v>
-      </c>
-      <c r="AR5">
-        <v>7</v>
       </c>
       <c r="AS5">
         <v>19.5</v>
       </c>
       <c r="AT5">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
+        <v>9</v>
+      </c>
+      <c r="AW5">
+        <v>14</v>
+      </c>
+      <c r="AX5">
+        <v>16</v>
+      </c>
+      <c r="AY5">
+        <v>14.5</v>
+      </c>
+      <c r="AZ5">
+        <v>14</v>
+      </c>
+      <c r="BA5">
+        <v>15</v>
+      </c>
+      <c r="BB5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC5">
+        <v>20</v>
+      </c>
+      <c r="BD5">
+        <v>36</v>
+      </c>
+      <c r="BE5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF5">
+        <v>8</v>
+      </c>
+      <c r="BG5">
         <v>7.6</v>
       </c>
-      <c r="AW5">
-        <v>4.4</v>
-      </c>
-      <c r="AX5">
-        <v>4.4</v>
-      </c>
-      <c r="AY5">
-        <v>4</v>
-      </c>
-      <c r="AZ5">
-        <v>16</v>
-      </c>
-      <c r="BA5">
-        <v>23</v>
-      </c>
-      <c r="BB5">
-        <v>4.9</v>
-      </c>
-      <c r="BC5">
-        <v>4.8</v>
-      </c>
-      <c r="BD5">
-        <v>4.8</v>
-      </c>
-      <c r="BE5">
-        <v>5</v>
-      </c>
-      <c r="BF5">
+      <c r="BH5">
         <v>4.7</v>
       </c>
-      <c r="BG5">
-        <v>5.7</v>
-      </c>
-      <c r="BH5">
-        <v>3.65</v>
-      </c>
       <c r="BI5">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="BM5">
-        <v>4.6</v>
+        <v>1.02</v>
       </c>
       <c r="BN5">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BO5">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ5">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="BR5">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BU5">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV5">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BW5">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BY5">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F6">
-        <v>4.8</v>
+        <v>1.42</v>
       </c>
       <c r="G6">
-        <v>5.4</v>
+        <v>1.45</v>
       </c>
       <c r="H6">
-        <v>1.68</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
-        <v>1.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="L6">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="P6">
+        <v>2.84</v>
+      </c>
+      <c r="Q6">
+        <v>1.52</v>
+      </c>
+      <c r="R6">
+        <v>1.73</v>
+      </c>
+      <c r="S6">
         <v>2.28</v>
       </c>
-      <c r="Q6">
-        <v>1.7</v>
-      </c>
-      <c r="R6">
-        <v>1.51</v>
-      </c>
-      <c r="S6">
-        <v>2.78</v>
-      </c>
       <c r="T6">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
-        <v>2.22</v>
+        <v>1.13</v>
       </c>
       <c r="W6">
-        <v>1.22</v>
+        <v>3.15</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Y6">
+        <v>36</v>
+      </c>
+      <c r="Z6">
+        <v>90</v>
+      </c>
+      <c r="AA6">
+        <v>250</v>
+      </c>
+      <c r="AB6">
+        <v>12.5</v>
+      </c>
+      <c r="AC6">
+        <v>14</v>
+      </c>
+      <c r="AD6">
+        <v>32</v>
+      </c>
+      <c r="AE6">
+        <v>110</v>
+      </c>
+      <c r="AF6">
         <v>11.5</v>
       </c>
-      <c r="Z6">
-        <v>12.5</v>
-      </c>
-      <c r="AA6">
-        <v>19.5</v>
-      </c>
-      <c r="AB6">
-        <v>22</v>
-      </c>
-      <c r="AC6">
-        <v>11.5</v>
-      </c>
-      <c r="AD6">
-        <v>12.5</v>
-      </c>
-      <c r="AE6">
-        <v>21</v>
-      </c>
-      <c r="AF6">
-        <v>44</v>
-      </c>
       <c r="AG6">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AH6">
         <v>22</v>
       </c>
       <c r="AI6">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AJ6">
-        <v>130</v>
+        <v>13.5</v>
       </c>
       <c r="AK6">
+        <v>14.5</v>
+      </c>
+      <c r="AL6">
+        <v>28</v>
+      </c>
+      <c r="AM6">
+        <v>110</v>
+      </c>
+      <c r="AN6">
+        <v>5</v>
+      </c>
+      <c r="AO6">
+        <v>100</v>
+      </c>
+      <c r="AP6">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6">
+        <v>19.5</v>
+      </c>
+      <c r="AR6">
+        <v>34</v>
+      </c>
+      <c r="AS6">
+        <v>9.4</v>
+      </c>
+      <c r="AT6">
+        <v>10.5</v>
+      </c>
+      <c r="AU6">
+        <v>11</v>
+      </c>
+      <c r="AV6">
+        <v>17.5</v>
+      </c>
+      <c r="AW6">
+        <v>44</v>
+      </c>
+      <c r="AX6">
+        <v>9.6</v>
+      </c>
+      <c r="AY6">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6">
+        <v>18</v>
+      </c>
+      <c r="BA6">
+        <v>34</v>
+      </c>
+      <c r="BB6">
+        <v>11.5</v>
+      </c>
+      <c r="BC6">
+        <v>12</v>
+      </c>
+      <c r="BD6">
+        <v>14.5</v>
+      </c>
+      <c r="BE6">
+        <v>40</v>
+      </c>
+      <c r="BF6">
+        <v>4.3</v>
+      </c>
+      <c r="BG6">
+        <v>15</v>
+      </c>
+      <c r="BH6">
+        <v>5.6</v>
+      </c>
+      <c r="BI6">
+        <v>3.9</v>
+      </c>
+      <c r="BJ6">
+        <v>10</v>
+      </c>
+      <c r="BK6">
+        <v>7.2</v>
+      </c>
+      <c r="BL6">
+        <v>110</v>
+      </c>
+      <c r="BM6">
+        <v>1.02</v>
+      </c>
+      <c r="BN6">
+        <v>4.5</v>
+      </c>
+      <c r="BO6">
+        <v>3.95</v>
+      </c>
+      <c r="BP6">
+        <v>8</v>
+      </c>
+      <c r="BQ6">
+        <v>6.4</v>
+      </c>
+      <c r="BR6">
+        <v>19</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>12</v>
+      </c>
+      <c r="BU6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BV6">
         <v>65</v>
       </c>
-      <c r="AL6">
-        <v>65</v>
-      </c>
-      <c r="AM6">
-        <v>100</v>
-      </c>
-      <c r="AN6">
-        <v>65</v>
-      </c>
-      <c r="AO6">
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>60</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
         <v>10.5</v>
       </c>
-      <c r="AP6">
-        <v>1.03</v>
-      </c>
-      <c r="AQ6">
-        <v>9</v>
-      </c>
-      <c r="AR6">
-        <v>1.03</v>
-      </c>
-      <c r="AS6">
-        <v>1.03</v>
-      </c>
-      <c r="AT6">
-        <v>1.03</v>
-      </c>
-      <c r="AU6">
-        <v>7.4</v>
-      </c>
-      <c r="AV6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW6">
-        <v>1.03</v>
-      </c>
-      <c r="AX6">
-        <v>1.03</v>
-      </c>
-      <c r="AY6">
-        <v>1.03</v>
-      </c>
-      <c r="AZ6">
-        <v>1.03</v>
-      </c>
-      <c r="BA6">
-        <v>21</v>
-      </c>
-      <c r="BB6">
-        <v>1.03</v>
-      </c>
-      <c r="BC6">
-        <v>1.03</v>
-      </c>
-      <c r="BD6">
-        <v>1.03</v>
-      </c>
-      <c r="BE6">
-        <v>1.03</v>
-      </c>
-      <c r="BF6">
-        <v>1.01</v>
-      </c>
-      <c r="BG6">
-        <v>7.2</v>
-      </c>
-      <c r="BH6">
-        <v>4.7</v>
-      </c>
-      <c r="BI6">
-        <v>3.15</v>
-      </c>
-      <c r="BJ6">
-        <v>11.5</v>
-      </c>
-      <c r="BK6">
-        <v>7</v>
-      </c>
-      <c r="BL6">
-        <v>120</v>
-      </c>
-      <c r="BM6">
-        <v>1.01</v>
-      </c>
-      <c r="BN6">
-        <v>10.5</v>
-      </c>
-      <c r="BO6">
-        <v>6.4</v>
-      </c>
-      <c r="BP6">
-        <v>48</v>
-      </c>
-      <c r="BQ6">
-        <v>28</v>
-      </c>
-      <c r="BR6">
-        <v>55</v>
-      </c>
-      <c r="BS6">
-        <v>30</v>
-      </c>
-      <c r="BT6">
-        <v>5.4</v>
-      </c>
-      <c r="BU6">
-        <v>3.55</v>
-      </c>
-      <c r="BV6">
-        <v>13.5</v>
-      </c>
-      <c r="BW6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX6">
-        <v>28</v>
-      </c>
-      <c r="BY6">
-        <v>16.5</v>
-      </c>
-      <c r="BZ6">
-        <v>20</v>
-      </c>
       <c r="CA6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="G7">
+        <v>3.7</v>
+      </c>
+      <c r="H7">
+        <v>2.32</v>
+      </c>
+      <c r="I7">
+        <v>2.48</v>
+      </c>
+      <c r="J7">
         <v>3.2</v>
       </c>
-      <c r="H7">
-        <v>2.48</v>
-      </c>
-      <c r="I7">
-        <v>2.58</v>
-      </c>
-      <c r="J7">
-        <v>3.35</v>
-      </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
+        <v>1.38</v>
+      </c>
+      <c r="P7">
+        <v>1.79</v>
+      </c>
+      <c r="Q7">
+        <v>2.12</v>
+      </c>
+      <c r="R7">
+        <v>1.29</v>
+      </c>
+      <c r="S7">
+        <v>3.9</v>
+      </c>
+      <c r="T7">
+        <v>1.84</v>
+      </c>
+      <c r="U7">
+        <v>2.02</v>
+      </c>
+      <c r="V7">
+        <v>1.67</v>
+      </c>
+      <c r="W7">
         <v>1.37</v>
       </c>
-      <c r="P7">
-        <v>1.84</v>
-      </c>
-      <c r="Q7">
-        <v>2.1</v>
-      </c>
-      <c r="R7">
-        <v>1.32</v>
-      </c>
-      <c r="S7">
-        <v>3.85</v>
-      </c>
-      <c r="T7">
-        <v>1.86</v>
-      </c>
-      <c r="U7">
-        <v>2.1</v>
-      </c>
-      <c r="V7">
-        <v>1.63</v>
-      </c>
-      <c r="W7">
-        <v>1.45</v>
-      </c>
       <c r="X7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y7">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA7">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB7">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE7">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF7">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AG7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AH7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AI7">
         <v>55</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AK7">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL7">
-        <v>270</v>
+        <v>70</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN7">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AO7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR7">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AS7">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AT7">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="AX7">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="AY7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AZ7">
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BB7">
-        <v>28</v>
+        <v>4.9</v>
       </c>
       <c r="BC7">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="BD7">
-        <v>28</v>
+        <v>4.8</v>
       </c>
       <c r="BE7">
-        <v>50</v>
+        <v>4.9</v>
       </c>
       <c r="BF7">
-        <v>29</v>
+        <v>4.7</v>
       </c>
       <c r="BG7">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="BH7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
+        <v>4.5</v>
+      </c>
+      <c r="BL7">
+        <v>170</v>
+      </c>
+      <c r="BM7">
         <v>7.4</v>
       </c>
-      <c r="BL7">
-        <v>160</v>
-      </c>
-      <c r="BM7">
-        <v>4.7</v>
-      </c>
       <c r="BN7">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BO7">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
         <v>32</v>
       </c>
       <c r="BQ7">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BR7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS7">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT7">
+        <v>5.3</v>
+      </c>
+      <c r="BU7">
+        <v>3.15</v>
+      </c>
+      <c r="BV7">
+        <v>19</v>
+      </c>
+      <c r="BW7">
+        <v>5.5</v>
+      </c>
+      <c r="BX7">
+        <v>36</v>
+      </c>
+      <c r="BY7">
         <v>6.4</v>
       </c>
-      <c r="BU7">
-        <v>4.6</v>
-      </c>
-      <c r="BV7">
-        <v>24</v>
-      </c>
-      <c r="BW7">
-        <v>4</v>
-      </c>
-      <c r="BX7">
-        <v>42</v>
-      </c>
-      <c r="BY7">
-        <v>4.3</v>
-      </c>
       <c r="BZ7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA7">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="H8">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="I8">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="O8">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="Q8">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="R8">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="S8">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="T8">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="U8">
-        <v>2.98</v>
+        <v>2.32</v>
       </c>
       <c r="V8">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="W8">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="X8">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z8">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AA8">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AB8">
         <v>26</v>
       </c>
       <c r="AC8">
+        <v>11.5</v>
+      </c>
+      <c r="AD8">
+        <v>12.5</v>
+      </c>
+      <c r="AE8">
+        <v>19.5</v>
+      </c>
+      <c r="AF8">
+        <v>44</v>
+      </c>
+      <c r="AG8">
+        <v>23</v>
+      </c>
+      <c r="AH8">
+        <v>19</v>
+      </c>
+      <c r="AI8">
+        <v>34</v>
+      </c>
+      <c r="AJ8">
+        <v>130</v>
+      </c>
+      <c r="AK8">
+        <v>65</v>
+      </c>
+      <c r="AL8">
+        <v>65</v>
+      </c>
+      <c r="AM8">
+        <v>90</v>
+      </c>
+      <c r="AN8">
+        <v>55</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>15</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>5.2</v>
+      </c>
+      <c r="BI8">
+        <v>3.45</v>
+      </c>
+      <c r="BJ8">
         <v>11</v>
       </c>
-      <c r="AD8">
-        <v>11.5</v>
-      </c>
-      <c r="AE8">
-        <v>17.5</v>
-      </c>
-      <c r="AF8">
-        <v>36</v>
-      </c>
-      <c r="AG8">
-        <v>16</v>
-      </c>
-      <c r="AH8">
-        <v>14</v>
-      </c>
-      <c r="AI8">
-        <v>23</v>
-      </c>
-      <c r="AJ8">
-        <v>70</v>
-      </c>
-      <c r="AK8">
-        <v>34</v>
-      </c>
-      <c r="AL8">
-        <v>34</v>
-      </c>
-      <c r="AM8">
+      <c r="BK8">
+        <v>6.8</v>
+      </c>
+      <c r="BL8">
+        <v>110</v>
+      </c>
+      <c r="BM8">
+        <v>55</v>
+      </c>
+      <c r="BN8">
+        <v>11</v>
+      </c>
+      <c r="BO8">
+        <v>6.6</v>
+      </c>
+      <c r="BP8">
+        <v>44</v>
+      </c>
+      <c r="BQ8">
+        <v>26</v>
+      </c>
+      <c r="BR8">
         <v>46</v>
       </c>
-      <c r="AN8">
-        <v>20</v>
-      </c>
-      <c r="AO8">
-        <v>7.4</v>
-      </c>
-      <c r="AP8">
-        <v>28</v>
-      </c>
-      <c r="AQ8">
-        <v>16</v>
-      </c>
-      <c r="AR8">
-        <v>16</v>
-      </c>
-      <c r="AS8">
-        <v>23</v>
-      </c>
-      <c r="AT8">
-        <v>22</v>
-      </c>
-      <c r="AU8">
-        <v>10</v>
-      </c>
-      <c r="AV8">
-        <v>10</v>
-      </c>
-      <c r="AW8">
-        <v>15.5</v>
-      </c>
-      <c r="AX8">
-        <v>30</v>
-      </c>
-      <c r="AY8">
-        <v>14.5</v>
-      </c>
-      <c r="AZ8">
-        <v>13.5</v>
-      </c>
-      <c r="BA8">
-        <v>20</v>
-      </c>
-      <c r="BB8">
-        <v>60</v>
-      </c>
-      <c r="BC8">
-        <v>30</v>
-      </c>
-      <c r="BD8">
-        <v>30</v>
-      </c>
-      <c r="BE8">
-        <v>40</v>
-      </c>
-      <c r="BF8">
-        <v>17.5</v>
-      </c>
-      <c r="BG8">
-        <v>7</v>
-      </c>
-      <c r="BH8">
-        <v>5</v>
-      </c>
-      <c r="BI8">
-        <v>4.6</v>
-      </c>
-      <c r="BJ8">
-        <v>8.4</v>
-      </c>
-      <c r="BK8">
-        <v>6.4</v>
-      </c>
-      <c r="BL8">
-        <v>65</v>
-      </c>
-      <c r="BM8">
-        <v>42</v>
-      </c>
-      <c r="BN8">
-        <v>7.6</v>
-      </c>
-      <c r="BO8">
-        <v>6.8</v>
-      </c>
-      <c r="BP8">
-        <v>24</v>
-      </c>
-      <c r="BQ8">
-        <v>17</v>
-      </c>
-      <c r="BR8">
+      <c r="BS8">
         <v>27</v>
-      </c>
-      <c r="BS8">
-        <v>19</v>
       </c>
       <c r="BT8">
         <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="BV8">
         <v>12.5</v>
       </c>
       <c r="BW8">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX8">
+        <v>25</v>
+      </c>
+      <c r="BY8">
+        <v>14.5</v>
+      </c>
+      <c r="BZ8">
+        <v>16.5</v>
+      </c>
+      <c r="CA8">
+        <v>10</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>3.05</v>
+      </c>
+      <c r="G9">
+        <v>3.2</v>
+      </c>
+      <c r="H9">
+        <v>2.5</v>
+      </c>
+      <c r="I9">
+        <v>2.56</v>
+      </c>
+      <c r="J9">
+        <v>3.4</v>
+      </c>
+      <c r="K9">
+        <v>3.5</v>
+      </c>
+      <c r="L9">
+        <v>1.44</v>
+      </c>
+      <c r="M9">
+        <v>1.08</v>
+      </c>
+      <c r="N9">
+        <v>3.5</v>
+      </c>
+      <c r="O9">
+        <v>1.37</v>
+      </c>
+      <c r="P9">
+        <v>1.84</v>
+      </c>
+      <c r="Q9">
+        <v>2.1</v>
+      </c>
+      <c r="R9">
+        <v>1.32</v>
+      </c>
+      <c r="S9">
+        <v>3.9</v>
+      </c>
+      <c r="T9">
+        <v>1.87</v>
+      </c>
+      <c r="U9">
+        <v>2.08</v>
+      </c>
+      <c r="V9">
+        <v>1.64</v>
+      </c>
+      <c r="W9">
+        <v>1.45</v>
+      </c>
+      <c r="X9">
+        <v>13</v>
+      </c>
+      <c r="Y9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z9">
+        <v>16</v>
+      </c>
+      <c r="AA9">
+        <v>48</v>
+      </c>
+      <c r="AB9">
+        <v>11.5</v>
+      </c>
+      <c r="AC9">
+        <v>7.8</v>
+      </c>
+      <c r="AD9">
+        <v>12.5</v>
+      </c>
+      <c r="AE9">
+        <v>40</v>
+      </c>
+      <c r="AF9">
+        <v>22</v>
+      </c>
+      <c r="AG9">
+        <v>14</v>
+      </c>
+      <c r="AH9">
+        <v>19</v>
+      </c>
+      <c r="AI9">
+        <v>55</v>
+      </c>
+      <c r="AJ9">
+        <v>65</v>
+      </c>
+      <c r="AK9">
+        <v>46</v>
+      </c>
+      <c r="AL9">
+        <v>290</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>80</v>
+      </c>
+      <c r="AO9">
+        <v>25</v>
+      </c>
+      <c r="AP9">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9">
+        <v>9</v>
+      </c>
+      <c r="AR9">
+        <v>13.5</v>
+      </c>
+      <c r="AS9">
+        <v>28</v>
+      </c>
+      <c r="AT9">
+        <v>10</v>
+      </c>
+      <c r="AU9">
+        <v>7</v>
+      </c>
+      <c r="AV9">
+        <v>10.5</v>
+      </c>
+      <c r="AW9">
         <v>20</v>
       </c>
-      <c r="BY8">
+      <c r="AX9">
+        <v>18</v>
+      </c>
+      <c r="AY9">
+        <v>12</v>
+      </c>
+      <c r="AZ9">
         <v>16</v>
       </c>
-      <c r="BZ8">
-        <v>12.5</v>
-      </c>
-      <c r="CA8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>106</v>
+      <c r="BA9">
+        <v>36</v>
+      </c>
+      <c r="BB9">
+        <v>28</v>
+      </c>
+      <c r="BC9">
+        <v>25</v>
+      </c>
+      <c r="BD9">
+        <v>28</v>
+      </c>
+      <c r="BE9">
+        <v>50</v>
+      </c>
+      <c r="BF9">
+        <v>29</v>
+      </c>
+      <c r="BG9">
+        <v>21</v>
+      </c>
+      <c r="BH9">
+        <v>970</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10">
+        <v>3.7</v>
+      </c>
+      <c r="G10">
+        <v>3.8</v>
+      </c>
+      <c r="H10">
+        <v>1.98</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>4.3</v>
+      </c>
+      <c r="K10">
+        <v>4.4</v>
+      </c>
+      <c r="L10">
+        <v>1.26</v>
+      </c>
+      <c r="M10">
+        <v>1.03</v>
+      </c>
+      <c r="N10">
+        <v>6.8</v>
+      </c>
+      <c r="O10">
+        <v>1.16</v>
+      </c>
+      <c r="P10">
+        <v>2.94</v>
+      </c>
+      <c r="Q10">
+        <v>1.49</v>
+      </c>
+      <c r="R10">
+        <v>1.8</v>
+      </c>
+      <c r="S10">
+        <v>2.18</v>
+      </c>
+      <c r="T10">
+        <v>1.49</v>
+      </c>
+      <c r="U10">
+        <v>2.9</v>
+      </c>
+      <c r="V10">
+        <v>2</v>
+      </c>
+      <c r="W10">
+        <v>1.36</v>
+      </c>
+      <c r="X10">
+        <v>32</v>
+      </c>
+      <c r="Y10">
+        <v>17</v>
+      </c>
+      <c r="Z10">
+        <v>17</v>
+      </c>
+      <c r="AA10">
+        <v>25</v>
+      </c>
+      <c r="AB10">
+        <v>24</v>
+      </c>
+      <c r="AC10">
+        <v>11</v>
+      </c>
+      <c r="AD10">
+        <v>11</v>
+      </c>
+      <c r="AE10">
+        <v>17.5</v>
+      </c>
+      <c r="AF10">
+        <v>34</v>
+      </c>
+      <c r="AG10">
+        <v>15.5</v>
+      </c>
+      <c r="AH10">
+        <v>15</v>
+      </c>
+      <c r="AI10">
+        <v>24</v>
+      </c>
+      <c r="AJ10">
+        <v>70</v>
+      </c>
+      <c r="AK10">
+        <v>36</v>
+      </c>
+      <c r="AL10">
+        <v>36</v>
+      </c>
+      <c r="AM10">
+        <v>48</v>
+      </c>
+      <c r="AN10">
+        <v>22</v>
+      </c>
+      <c r="AO10">
+        <v>7.6</v>
+      </c>
+      <c r="AP10">
+        <v>27</v>
+      </c>
+      <c r="AQ10">
+        <v>15</v>
+      </c>
+      <c r="AR10">
+        <v>15.5</v>
+      </c>
+      <c r="AS10">
+        <v>23</v>
+      </c>
+      <c r="AT10">
+        <v>21</v>
+      </c>
+      <c r="AU10">
+        <v>9.6</v>
+      </c>
+      <c r="AV10">
+        <v>10</v>
+      </c>
+      <c r="AW10">
+        <v>16.5</v>
+      </c>
+      <c r="AX10">
+        <v>30</v>
+      </c>
+      <c r="AY10">
+        <v>14.5</v>
+      </c>
+      <c r="AZ10">
+        <v>13.5</v>
+      </c>
+      <c r="BA10">
+        <v>22</v>
+      </c>
+      <c r="BB10">
+        <v>60</v>
+      </c>
+      <c r="BC10">
+        <v>32</v>
+      </c>
+      <c r="BD10">
+        <v>32</v>
+      </c>
+      <c r="BE10">
+        <v>42</v>
+      </c>
+      <c r="BF10">
+        <v>19.5</v>
+      </c>
+      <c r="BG10">
+        <v>7.2</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>3.9</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>6.2</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>5.8</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>4.2</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>11.5</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -352,7 +352,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-30 03:37:03</t>
+    <t>2026-09-30 05:48:49</t>
   </si>
 </sst>
 </file>
@@ -946,166 +946,166 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="I2">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="K2">
-        <v>110</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="O2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1188,61 +1188,61 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="G3">
-        <v>110</v>
+        <v>1.61</v>
       </c>
       <c r="H3">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J3">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L3">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
+        <v>1.28</v>
+      </c>
+      <c r="O3">
         <v>1.25</v>
       </c>
-      <c r="O3">
-        <v>1.01</v>
-      </c>
       <c r="P3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y3">
         <v>1000</v>
@@ -1254,10 +1254,10 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD3">
         <v>1000</v>
@@ -1266,88 +1266,88 @@
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AI3">
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1430,19 +1430,19 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G4">
         <v>2.5</v>
       </c>
       <c r="H4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I4">
         <v>3.1</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>3.95</v>
@@ -1451,7 +1451,7 @@
         <v>1.31</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
         <v>5.2</v>
@@ -1463,7 +1463,7 @@
         <v>2.42</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
         <v>1.57</v>
@@ -1481,10 +1481,10 @@
         <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y4">
         <v>17</v>
@@ -1493,7 +1493,7 @@
         <v>24</v>
       </c>
       <c r="AA4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB4">
         <v>15</v>
@@ -1502,22 +1502,22 @@
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ4">
         <v>34</v>
@@ -1526,10 +1526,10 @@
         <v>24</v>
       </c>
       <c r="AL4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN4">
         <v>14</v>
@@ -1541,49 +1541,49 @@
         <v>18</v>
       </c>
       <c r="AQ4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT4">
+        <v>12.5</v>
+      </c>
+      <c r="AU4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV4">
         <v>12</v>
       </c>
-      <c r="AU4">
-        <v>8</v>
-      </c>
-      <c r="AV4">
-        <v>11.5</v>
-      </c>
       <c r="AW4">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AX4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="BB4">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BC4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BF4">
         <v>12</v>
@@ -1601,40 +1601,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BM4">
         <v>1.02</v>
       </c>
       <c r="BN4">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ4">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>28</v>
       </c>
       <c r="BS4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
         <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
@@ -1646,10 +1646,10 @@
         <v>1.02</v>
       </c>
       <c r="BZ4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="CA4">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1672,16 +1672,16 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="G5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H5">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="I5">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -1690,154 +1690,154 @@
         <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S5">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U5">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="V5">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X5">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Y5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB5">
         <v>23</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE5">
         <v>17</v>
       </c>
       <c r="AF5">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AG5">
         <v>17</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AJ5">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK5">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN5">
-        <v>260</v>
+        <v>46</v>
       </c>
       <c r="AO5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR5">
         <v>12</v>
       </c>
       <c r="AS5">
+        <v>20</v>
+      </c>
+      <c r="AT5">
         <v>19.5</v>
       </c>
-      <c r="AT5">
-        <v>19</v>
-      </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AW5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AY5">
+        <v>15</v>
+      </c>
+      <c r="AZ5">
         <v>14.5</v>
       </c>
-      <c r="AZ5">
-        <v>14</v>
-      </c>
       <c r="BA5">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BB5">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BC5">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BF5">
+        <v>30</v>
+      </c>
+      <c r="BG5">
         <v>8</v>
-      </c>
-      <c r="BG5">
-        <v>7.6</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
       </c>
       <c r="BI5">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5">
         <v>11</v>
@@ -1846,7 +1846,7 @@
         <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM5">
         <v>1.02</v>
@@ -1864,7 +1864,7 @@
         <v>1.02</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
@@ -1882,13 +1882,13 @@
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -1914,7 +1914,7 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G6">
         <v>1.45</v>
@@ -1923,7 +1923,7 @@
         <v>7.6</v>
       </c>
       <c r="I6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>5.3</v>
@@ -1944,7 +1944,7 @@
         <v>1.17</v>
       </c>
       <c r="P6">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q6">
         <v>1.52</v>
@@ -1956,7 +1956,7 @@
         <v>2.28</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
         <v>2.2</v>
@@ -1965,7 +1965,7 @@
         <v>1.13</v>
       </c>
       <c r="W6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X6">
         <v>32</v>
@@ -2022,16 +2022,16 @@
         <v>100</v>
       </c>
       <c r="AP6">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AQ6">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="AR6">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AS6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
@@ -2040,10 +2040,10 @@
         <v>11</v>
       </c>
       <c r="AV6">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AW6">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AX6">
         <v>9.6</v>
@@ -2055,7 +2055,7 @@
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BB6">
         <v>11.5</v>
@@ -2064,28 +2064,28 @@
         <v>12</v>
       </c>
       <c r="BD6">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BE6">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BF6">
         <v>4.3</v>
       </c>
       <c r="BG6">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="BH6">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BI6">
         <v>3.9</v>
       </c>
       <c r="BJ6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK6">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL6">
         <v>110</v>
@@ -2094,46 +2094,46 @@
         <v>1.02</v>
       </c>
       <c r="BN6">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BO6">
         <v>3.95</v>
       </c>
       <c r="BP6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BQ6">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BU6">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BV6">
         <v>65</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BX6">
         <v>60</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BZ6">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CA6">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="s">
         <v>112</v>
@@ -2156,40 +2156,40 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I7">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R7">
         <v>1.29</v>
@@ -2198,16 +2198,16 @@
         <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U7">
         <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X7">
         <v>15</v>
@@ -2234,7 +2234,7 @@
         <v>34</v>
       </c>
       <c r="AF7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG7">
         <v>18</v>
@@ -2246,7 +2246,7 @@
         <v>55</v>
       </c>
       <c r="AJ7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK7">
         <v>55</v>
@@ -2261,10 +2261,10 @@
         <v>60</v>
       </c>
       <c r="AO7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP7">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
         <v>8</v>
@@ -2273,7 +2273,7 @@
         <v>7</v>
       </c>
       <c r="AS7">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AT7">
         <v>6.4</v>
@@ -2285,19 +2285,19 @@
         <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX7">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AY7">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>23</v>
+        <v>4.8</v>
       </c>
       <c r="BB7">
         <v>4.9</v>
@@ -2309,19 +2309,19 @@
         <v>4.8</v>
       </c>
       <c r="BE7">
+        <v>5</v>
+      </c>
+      <c r="BF7">
         <v>4.9</v>
-      </c>
-      <c r="BF7">
-        <v>4.7</v>
       </c>
       <c r="BG7">
         <v>5.7</v>
       </c>
       <c r="BH7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI7">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
@@ -2333,43 +2333,43 @@
         <v>170</v>
       </c>
       <c r="BM7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN7">
         <v>6.8</v>
       </c>
       <c r="BO7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP7">
         <v>32</v>
       </c>
       <c r="BQ7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR7">
         <v>46</v>
       </c>
       <c r="BS7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT7">
         <v>5.3</v>
       </c>
       <c r="BU7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BV7">
         <v>19</v>
       </c>
       <c r="BW7">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX7">
         <v>36</v>
       </c>
       <c r="BY7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2401,34 +2401,34 @@
         <v>4.6</v>
       </c>
       <c r="G8">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="H8">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I8">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="J8">
         <v>4.2</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O8">
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q8">
         <v>1.56</v>
@@ -2437,7 +2437,7 @@
         <v>1.62</v>
       </c>
       <c r="S8">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T8">
         <v>1.52</v>
@@ -2446,10 +2446,10 @@
         <v>2.32</v>
       </c>
       <c r="V8">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="W8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X8">
         <v>28</v>
@@ -2473,7 +2473,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AF8">
         <v>44</v>
@@ -2494,76 +2494,76 @@
         <v>65</v>
       </c>
       <c r="AL8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN8">
         <v>55</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI8">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8">
         <v>11</v>
@@ -2572,7 +2572,7 @@
         <v>6.8</v>
       </c>
       <c r="BL8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM8">
         <v>55</v>
@@ -2587,7 +2587,7 @@
         <v>44</v>
       </c>
       <c r="BQ8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BR8">
         <v>46</v>
@@ -2596,7 +2596,7 @@
         <v>27</v>
       </c>
       <c r="BT8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU8">
         <v>3.65</v>
@@ -2605,7 +2605,7 @@
         <v>12.5</v>
       </c>
       <c r="BW8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX8">
         <v>25</v>
@@ -2614,10 +2614,10 @@
         <v>14.5</v>
       </c>
       <c r="BZ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2646,19 +2646,19 @@
         <v>3.2</v>
       </c>
       <c r="H9">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I9">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J9">
         <v>3.4</v>
       </c>
       <c r="K9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M9">
         <v>1.08</v>
@@ -2673,22 +2673,22 @@
         <v>1.84</v>
       </c>
       <c r="Q9">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R9">
         <v>1.32</v>
       </c>
       <c r="S9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T9">
         <v>1.87</v>
       </c>
       <c r="U9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W9">
         <v>1.45</v>
@@ -2721,7 +2721,7 @@
         <v>22</v>
       </c>
       <c r="AG9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
         <v>19</v>
@@ -2736,13 +2736,13 @@
         <v>46</v>
       </c>
       <c r="AL9">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AN9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO9">
         <v>25</v>
@@ -2802,64 +2802,64 @@
         <v>21</v>
       </c>
       <c r="BH9">
-        <v>970</v>
+        <v>3.7</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB9" t="s">
         <v>112</v>
@@ -2885,19 +2885,19 @@
         <v>3.7</v>
       </c>
       <c r="G10">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H10">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J10">
         <v>4.3</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>1.26</v>
@@ -2906,7 +2906,7 @@
         <v>1.03</v>
       </c>
       <c r="N10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>1.16</v>
@@ -2915,7 +2915,7 @@
         <v>2.94</v>
       </c>
       <c r="Q10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R10">
         <v>1.8</v>
@@ -2924,7 +2924,7 @@
         <v>2.18</v>
       </c>
       <c r="T10">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U10">
         <v>2.9</v>
@@ -2933,7 +2933,7 @@
         <v>2</v>
       </c>
       <c r="W10">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X10">
         <v>32</v>
@@ -2963,10 +2963,10 @@
         <v>34</v>
       </c>
       <c r="AG10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI10">
         <v>24</v>
@@ -2990,7 +2990,7 @@
         <v>7.6</v>
       </c>
       <c r="AP10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ10">
         <v>15</v>
@@ -3011,7 +3011,7 @@
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX10">
         <v>30</v>
@@ -3038,70 +3038,70 @@
         <v>42</v>
       </c>
       <c r="BF10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI10">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO10">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU10">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW10">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -352,7 +352,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-30 05:48:49</t>
+    <t>2026-09-30 07:58:21</t>
   </si>
 </sst>
 </file>
@@ -946,175 +946,175 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="H2">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J2">
+        <v>2.78</v>
+      </c>
+      <c r="K2">
+        <v>3.45</v>
+      </c>
+      <c r="L2">
+        <v>1.54</v>
+      </c>
+      <c r="M2">
+        <v>1.11</v>
+      </c>
+      <c r="N2">
         <v>2.56</v>
       </c>
-      <c r="K2">
-        <v>4.4</v>
-      </c>
-      <c r="L2">
+      <c r="O2">
         <v>1.5</v>
       </c>
-      <c r="M2">
-        <v>1.1</v>
-      </c>
-      <c r="N2">
-        <v>1.52</v>
-      </c>
-      <c r="O2">
-        <v>1.44</v>
-      </c>
       <c r="P2">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q2">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="AA2">
-        <v>470</v>
+        <v>65</v>
       </c>
       <c r="AB2">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC2">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>330</v>
+        <v>50</v>
       </c>
       <c r="AF2">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="AG2">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH2">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>470</v>
+        <v>170</v>
       </c>
       <c r="AJ2">
+        <v>65</v>
+      </c>
+      <c r="AK2">
+        <v>55</v>
+      </c>
+      <c r="AL2">
+        <v>170</v>
+      </c>
+      <c r="AM2">
         <v>200</v>
       </c>
-      <c r="AK2">
-        <v>240</v>
-      </c>
-      <c r="AL2">
-        <v>380</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
       <c r="AN2">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AO2">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP2">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>1.64</v>
+        <v>7.2</v>
       </c>
       <c r="AR2">
-        <v>1.64</v>
+        <v>14.5</v>
       </c>
       <c r="AS2">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="AT2">
-        <v>1.65</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV2">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AW2">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="AX2">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AY2">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>1.65</v>
+        <v>17</v>
       </c>
       <c r="BA2">
-        <v>1.67</v>
+        <v>4.6</v>
       </c>
       <c r="BB2">
-        <v>1.67</v>
+        <v>5.2</v>
       </c>
       <c r="BC2">
-        <v>1.66</v>
+        <v>13</v>
       </c>
       <c r="BD2">
-        <v>1.67</v>
+        <v>5.3</v>
       </c>
       <c r="BE2">
-        <v>1.69</v>
+        <v>4.7</v>
       </c>
       <c r="BF2">
         <v>5.5</v>
       </c>
       <c r="BG2">
-        <v>1.68</v>
+        <v>5.1</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
@@ -1126,43 +1126,43 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1188,175 +1188,175 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G3">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>1.28</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="P3">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V3">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="W3">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="X3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF3">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG3">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ3">
-        <v>110</v>
+        <v>19.5</v>
       </c>
       <c r="AK3">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="AL3">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AP3">
         <v>4.4</v>
       </c>
       <c r="AQ3">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="AR3">
-        <v>1.87</v>
+        <v>5.2</v>
       </c>
       <c r="AS3">
-        <v>1.87</v>
+        <v>5.5</v>
       </c>
       <c r="AT3">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="AU3">
         <v>4.9</v>
       </c>
       <c r="AV3">
-        <v>1.87</v>
+        <v>4.8</v>
       </c>
       <c r="AW3">
-        <v>1.87</v>
+        <v>5.4</v>
       </c>
       <c r="AX3">
+        <v>3.5</v>
+      </c>
+      <c r="AY3">
         <v>3.85</v>
       </c>
-      <c r="AY3">
+      <c r="AZ3">
+        <v>4.8</v>
+      </c>
+      <c r="BA3">
+        <v>5.4</v>
+      </c>
+      <c r="BB3">
+        <v>4.3</v>
+      </c>
+      <c r="BC3">
+        <v>4.6</v>
+      </c>
+      <c r="BD3">
+        <v>5.1</v>
+      </c>
+      <c r="BE3">
+        <v>5.5</v>
+      </c>
+      <c r="BF3">
         <v>4.2</v>
       </c>
-      <c r="AZ3">
-        <v>1.7</v>
-      </c>
-      <c r="BA3">
-        <v>1.87</v>
-      </c>
-      <c r="BB3">
-        <v>6.2</v>
-      </c>
-      <c r="BC3">
-        <v>1.69</v>
-      </c>
-      <c r="BD3">
-        <v>1.71</v>
-      </c>
-      <c r="BE3">
-        <v>1.73</v>
-      </c>
-      <c r="BF3">
-        <v>3.4</v>
-      </c>
       <c r="BG3">
-        <v>1.87</v>
+        <v>5.5</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
@@ -1368,25 +1368,25 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO3">
         <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
@@ -1398,13 +1398,13 @@
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1436,67 +1436,67 @@
         <v>2.5</v>
       </c>
       <c r="H4">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="I4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q4">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="R4">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S4">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="T4">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="U4">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
         <v>1.66</v>
       </c>
       <c r="X4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC4">
         <v>9</v>
@@ -1505,10 +1505,10 @@
         <v>14</v>
       </c>
       <c r="AE4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF4">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AG4">
         <v>12</v>
@@ -1517,7 +1517,7 @@
         <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
         <v>34</v>
@@ -1526,22 +1526,22 @@
         <v>24</v>
       </c>
       <c r="AL4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO4">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AP4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR4">
         <v>20</v>
@@ -1550,7 +1550,7 @@
         <v>40</v>
       </c>
       <c r="AT4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU4">
         <v>8.199999999999999</v>
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
@@ -1571,31 +1571,31 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB4">
         <v>28</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE4">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BH4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ4">
         <v>9.800000000000001</v>
@@ -1610,13 +1610,13 @@
         <v>1.02</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
@@ -1631,10 +1631,10 @@
         <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
@@ -1646,10 +1646,10 @@
         <v>1.02</v>
       </c>
       <c r="BZ4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1672,16 +1672,16 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G5">
         <v>4.6</v>
       </c>
       <c r="H5">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="I5">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -1699,31 +1699,31 @@
         <v>5.6</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S5">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T5">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U5">
         <v>2.68</v>
       </c>
       <c r="V5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="W5">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X5">
         <v>25</v>
@@ -1732,7 +1732,7 @@
         <v>13</v>
       </c>
       <c r="Z5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA5">
         <v>23</v>
@@ -1741,70 +1741,70 @@
         <v>23</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>10</v>
       </c>
       <c r="AE5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG5">
         <v>17</v>
       </c>
       <c r="AH5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AJ5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK5">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL5">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM5">
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AO5">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
         <v>12</v>
       </c>
       <c r="AR5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS5">
+        <v>19.5</v>
+      </c>
+      <c r="AT5">
         <v>20</v>
       </c>
-      <c r="AT5">
-        <v>19.5</v>
-      </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW5">
         <v>14.5</v>
       </c>
       <c r="AX5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AY5">
         <v>15</v>
@@ -1816,7 +1816,7 @@
         <v>23</v>
       </c>
       <c r="BB5">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BC5">
         <v>38</v>
@@ -1825,19 +1825,19 @@
         <v>38</v>
       </c>
       <c r="BE5">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF5">
         <v>30</v>
       </c>
       <c r="BG5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BI5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5">
         <v>11</v>
@@ -1855,25 +1855,25 @@
         <v>9.6</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP5">
         <v>38</v>
       </c>
       <c r="BQ5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
         <v>42</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BT5">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BU5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV5">
         <v>14.5</v>
@@ -1882,13 +1882,13 @@
         <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -1914,178 +1914,178 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="G6">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
+        <v>4.9</v>
+      </c>
+      <c r="K6">
         <v>5.3</v>
       </c>
-      <c r="K6">
-        <v>5.8</v>
-      </c>
       <c r="L6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M6">
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P6">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="Q6">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="R6">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="S6">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="T6">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="U6">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V6">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="X6">
         <v>32</v>
       </c>
       <c r="Y6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z6">
+        <v>75</v>
+      </c>
+      <c r="AA6">
+        <v>200</v>
+      </c>
+      <c r="AB6">
+        <v>12</v>
+      </c>
+      <c r="AC6">
+        <v>12.5</v>
+      </c>
+      <c r="AD6">
+        <v>27</v>
+      </c>
+      <c r="AE6">
         <v>90</v>
-      </c>
-      <c r="AA6">
-        <v>250</v>
-      </c>
-      <c r="AB6">
-        <v>12.5</v>
-      </c>
-      <c r="AC6">
-        <v>14</v>
-      </c>
-      <c r="AD6">
-        <v>32</v>
-      </c>
-      <c r="AE6">
-        <v>110</v>
       </c>
       <c r="AF6">
         <v>11.5</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL6">
         <v>28</v>
       </c>
       <c r="AM6">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN6">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AO6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AP6">
         <v>23</v>
       </c>
       <c r="AQ6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AR6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT6">
         <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX6">
         <v>9.6</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE6">
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG6">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH6">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BI6">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BL6">
         <v>110</v>
@@ -2094,46 +2094,46 @@
         <v>1.02</v>
       </c>
       <c r="BN6">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BO6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU6">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV6">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="BW6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BY6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
         <v>112</v>
@@ -2156,28 +2156,28 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H7">
         <v>2.34</v>
       </c>
       <c r="I7">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J7">
         <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
         <v>3.4</v>
@@ -2192,28 +2192,28 @@
         <v>2.16</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T7">
         <v>1.85</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W7">
         <v>1.38</v>
       </c>
       <c r="X7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z7">
         <v>15.5</v>
@@ -2222,7 +2222,7 @@
         <v>40</v>
       </c>
       <c r="AB7">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -2231,22 +2231,22 @@
         <v>12</v>
       </c>
       <c r="AE7">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG7">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI7">
         <v>55</v>
       </c>
       <c r="AJ7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK7">
         <v>55</v>
@@ -2261,7 +2261,7 @@
         <v>60</v>
       </c>
       <c r="AO7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP7">
         <v>10</v>
@@ -2270,22 +2270,22 @@
         <v>8</v>
       </c>
       <c r="AR7">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AS7">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AT7">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AX7">
         <v>20</v>
@@ -2297,79 +2297,79 @@
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="BB7">
-        <v>4.9</v>
+        <v>42</v>
       </c>
       <c r="BC7">
-        <v>4.8</v>
+        <v>29</v>
       </c>
       <c r="BD7">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="BE7">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="BF7">
-        <v>4.9</v>
+        <v>30</v>
       </c>
       <c r="BG7">
-        <v>5.7</v>
+        <v>19.5</v>
       </c>
       <c r="BH7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI7">
         <v>2.56</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK7">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="BL7">
         <v>170</v>
       </c>
       <c r="BM7">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="BN7">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BO7">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ7">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BR7">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BS7">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BT7">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BU7">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="BV7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BW7">
-        <v>5.7</v>
+        <v>3.95</v>
       </c>
       <c r="BX7">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BY7">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2398,184 +2398,184 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G8">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I8">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K8">
         <v>4.9</v>
       </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q8">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S8">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T8">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="U8">
         <v>2.32</v>
       </c>
       <c r="V8">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="W8">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X8">
         <v>28</v>
       </c>
       <c r="Y8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z8">
+        <v>14.5</v>
+      </c>
+      <c r="AA8">
+        <v>19</v>
+      </c>
+      <c r="AB8">
+        <v>28</v>
+      </c>
+      <c r="AC8">
         <v>13</v>
-      </c>
-      <c r="AA8">
-        <v>22</v>
-      </c>
-      <c r="AB8">
-        <v>26</v>
-      </c>
-      <c r="AC8">
-        <v>11.5</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AF8">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AG8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH8">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI8">
         <v>34</v>
       </c>
       <c r="AJ8">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AK8">
+        <v>75</v>
+      </c>
+      <c r="AL8">
+        <v>70</v>
+      </c>
+      <c r="AM8">
+        <v>95</v>
+      </c>
+      <c r="AN8">
         <v>65</v>
       </c>
-      <c r="AL8">
-        <v>60</v>
-      </c>
-      <c r="AM8">
-        <v>85</v>
-      </c>
-      <c r="AN8">
-        <v>55</v>
-      </c>
       <c r="AO8">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP8">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="AQ8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS8">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="AT8">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="AU8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV8">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="AX8">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AY8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA8">
         <v>5</v>
       </c>
       <c r="BB8">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BC8">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD8">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE8">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF8">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG8">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH8">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BJ8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL8">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BM8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BN8">
         <v>11</v>
@@ -2584,22 +2584,22 @@
         <v>6.6</v>
       </c>
       <c r="BP8">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BQ8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BR8">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BT8">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BV8">
         <v>12.5</v>
@@ -2608,16 +2608,16 @@
         <v>7.6</v>
       </c>
       <c r="BX8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ8">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="CA8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2646,10 +2646,10 @@
         <v>3.2</v>
       </c>
       <c r="H9">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I9">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J9">
         <v>3.4</v>
@@ -2667,13 +2667,13 @@
         <v>3.5</v>
       </c>
       <c r="O9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
         <v>1.32</v>
@@ -2682,13 +2682,13 @@
         <v>3.85</v>
       </c>
       <c r="T9">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U9">
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W9">
         <v>1.45</v>
@@ -2697,70 +2697,70 @@
         <v>13</v>
       </c>
       <c r="Y9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>16</v>
       </c>
       <c r="AA9">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AB9">
+        <v>12.5</v>
+      </c>
+      <c r="AC9">
+        <v>7.6</v>
+      </c>
+      <c r="AD9">
         <v>11.5</v>
       </c>
-      <c r="AC9">
-        <v>7.8</v>
-      </c>
-      <c r="AD9">
-        <v>12.5</v>
-      </c>
       <c r="AE9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AF9">
         <v>22</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ9">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="AK9">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AL9">
         <v>280</v>
       </c>
       <c r="AM9">
-        <v>980</v>
+        <v>920</v>
       </c>
       <c r="AN9">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AO9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
         <v>9</v>
       </c>
       <c r="AR9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AT9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU9">
         <v>7</v>
@@ -2769,7 +2769,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX9">
         <v>18</v>
@@ -2781,22 +2781,22 @@
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BB9">
+        <v>32</v>
+      </c>
+      <c r="BC9">
         <v>28</v>
-      </c>
-      <c r="BC9">
-        <v>25</v>
       </c>
       <c r="BD9">
         <v>28</v>
       </c>
       <c r="BE9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BF9">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BG9">
         <v>21</v>
@@ -2808,19 +2808,19 @@
         <v>2.58</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BL9">
         <v>160</v>
       </c>
       <c r="BM9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BN9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO9">
         <v>5.3</v>
@@ -2829,16 +2829,16 @@
         <v>32</v>
       </c>
       <c r="BQ9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR9">
         <v>48</v>
       </c>
       <c r="BS9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BT9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU9">
         <v>4.6</v>
@@ -2853,13 +2853,13 @@
         <v>42</v>
       </c>
       <c r="BY9">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BZ9">
         <v>38</v>
       </c>
       <c r="CA9">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="CB9" t="s">
         <v>112</v>
@@ -2882,13 +2882,13 @@
         <v>111</v>
       </c>
       <c r="F10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H10">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I10">
         <v>1.99</v>
@@ -2897,37 +2897,37 @@
         <v>4.3</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M10">
         <v>1.03</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="O10">
         <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="Q10">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R10">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="S10">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="T10">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U10">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V10">
         <v>2</v>
@@ -2936,22 +2936,22 @@
         <v>1.35</v>
       </c>
       <c r="X10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y10">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA10">
         <v>25</v>
       </c>
       <c r="AB10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD10">
         <v>11</v>
@@ -2960,7 +2960,7 @@
         <v>17.5</v>
       </c>
       <c r="AF10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG10">
         <v>16</v>
@@ -2969,10 +2969,10 @@
         <v>14.5</v>
       </c>
       <c r="AI10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ10">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK10">
         <v>36</v>
@@ -2981,25 +2981,25 @@
         <v>36</v>
       </c>
       <c r="AM10">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AN10">
+        <v>23</v>
+      </c>
+      <c r="AO10">
+        <v>8</v>
+      </c>
+      <c r="AP10">
+        <v>26</v>
+      </c>
+      <c r="AQ10">
+        <v>14.5</v>
+      </c>
+      <c r="AR10">
+        <v>15</v>
+      </c>
+      <c r="AS10">
         <v>22</v>
-      </c>
-      <c r="AO10">
-        <v>7.6</v>
-      </c>
-      <c r="AP10">
-        <v>28</v>
-      </c>
-      <c r="AQ10">
-        <v>15</v>
-      </c>
-      <c r="AR10">
-        <v>15.5</v>
-      </c>
-      <c r="AS10">
-        <v>23</v>
       </c>
       <c r="AT10">
         <v>21</v>
@@ -3011,7 +3011,7 @@
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX10">
         <v>30</v>
@@ -3035,73 +3035,73 @@
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF10">
         <v>20</v>
       </c>
       <c r="BG10">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH10">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BI10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL10">
         <v>70</v>
       </c>
       <c r="BM10">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BN10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO10">
         <v>6.8</v>
       </c>
       <c r="BP10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ10">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BR10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS10">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BT10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV10">
         <v>12.5</v>
       </c>
       <c r="BW10">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX10">
         <v>21</v>
       </c>
       <c r="BY10">
+        <v>15</v>
+      </c>
+      <c r="BZ10">
         <v>14</v>
       </c>
-      <c r="BZ10">
-        <v>13.5</v>
-      </c>
       <c r="CA10">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
         <v>112</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -352,7 +352,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-30 07:58:21</t>
+    <t>2026-09-30 10:09:30</t>
   </si>
 </sst>
 </file>
@@ -946,19 +946,19 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G2">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H2">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="I2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J2">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K2">
         <v>3.45</v>
@@ -970,52 +970,52 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O2">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P2">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="V2">
         <v>1.47</v>
       </c>
       <c r="W2">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y2">
         <v>11</v>
       </c>
       <c r="Z2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AB2">
         <v>11</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
@@ -1024,7 +1024,7 @@
         <v>50</v>
       </c>
       <c r="AF2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG2">
         <v>16.5</v>
@@ -1036,46 +1036,46 @@
         <v>170</v>
       </c>
       <c r="AJ2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL2">
         <v>170</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO2">
         <v>60</v>
       </c>
       <c r="AP2">
+        <v>7.6</v>
+      </c>
+      <c r="AQ2">
         <v>7.4</v>
       </c>
-      <c r="AQ2">
-        <v>7.2</v>
-      </c>
       <c r="AR2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS2">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="AT2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV2">
         <v>11</v>
       </c>
       <c r="AW2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AX2">
         <v>14.5</v>
@@ -1084,31 +1084,31 @@
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB2">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC2">
         <v>13</v>
       </c>
       <c r="BD2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE2">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF2">
         <v>5.5</v>
       </c>
       <c r="BG2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI2">
         <v>2.26</v>
@@ -1117,13 +1117,13 @@
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
@@ -1135,13 +1135,13 @@
         <v>32</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR2">
         <v>60</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
@@ -1153,19 +1153,19 @@
         <v>32</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ2">
         <v>60</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1188,7 +1188,7 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G3">
         <v>1.75</v>
@@ -1200,7 +1200,7 @@
         <v>8.6</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
         <v>4.2</v>
@@ -1215,22 +1215,22 @@
         <v>2.52</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
         <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>2.62</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U3">
         <v>1.56</v>
@@ -1242,28 +1242,28 @@
         <v>2.32</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z3">
         <v>75</v>
       </c>
       <c r="AA3">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="AB3">
         <v>6.8</v>
       </c>
       <c r="AC3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD3">
         <v>36</v>
       </c>
       <c r="AE3">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AF3">
         <v>9.6</v>
@@ -1275,7 +1275,7 @@
         <v>36</v>
       </c>
       <c r="AI3">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AJ3">
         <v>19.5</v>
@@ -1287,67 +1287,67 @@
         <v>70</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN3">
         <v>17.5</v>
       </c>
       <c r="AO3">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="AP3">
         <v>4.4</v>
       </c>
       <c r="AQ3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS3">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT3">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AU3">
         <v>4.9</v>
       </c>
       <c r="AV3">
+        <v>5</v>
+      </c>
+      <c r="AW3">
+        <v>5.7</v>
+      </c>
+      <c r="AX3">
+        <v>3.65</v>
+      </c>
+      <c r="AY3">
+        <v>4</v>
+      </c>
+      <c r="AZ3">
+        <v>5</v>
+      </c>
+      <c r="BA3">
+        <v>5.7</v>
+      </c>
+      <c r="BB3">
+        <v>4.5</v>
+      </c>
+      <c r="BC3">
         <v>4.8</v>
       </c>
-      <c r="AW3">
+      <c r="BD3">
         <v>5.4</v>
       </c>
-      <c r="AX3">
-        <v>3.5</v>
-      </c>
-      <c r="AY3">
-        <v>3.85</v>
-      </c>
-      <c r="AZ3">
-        <v>4.8</v>
-      </c>
-      <c r="BA3">
-        <v>5.4</v>
-      </c>
-      <c r="BB3">
-        <v>4.3</v>
-      </c>
-      <c r="BC3">
-        <v>4.6</v>
-      </c>
-      <c r="BD3">
-        <v>5.1</v>
-      </c>
       <c r="BE3">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG3">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH3">
         <v>3.2</v>
@@ -1359,55 +1359,55 @@
         <v>15</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN3">
         <v>4.4</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BP3">
         <v>14</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BT3">
         <v>12</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX3">
         <v>120</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BZ3">
         <v>38</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB3" t="s">
         <v>112</v>
@@ -1430,22 +1430,22 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G4">
         <v>2.5</v>
       </c>
       <c r="H4">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.3</v>
@@ -1460,22 +1460,22 @@
         <v>1.2</v>
       </c>
       <c r="P4">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R4">
         <v>1.6</v>
       </c>
       <c r="S4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T4">
         <v>1.53</v>
       </c>
       <c r="U4">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V4">
         <v>1.5</v>
@@ -1487,13 +1487,13 @@
         <v>24</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
         <v>25</v>
       </c>
       <c r="AA4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB4">
         <v>16</v>
@@ -1541,7 +1541,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR4">
         <v>20</v>
@@ -1550,16 +1550,16 @@
         <v>40</v>
       </c>
       <c r="AT4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX4">
         <v>16.5</v>
@@ -1577,7 +1577,7 @@
         <v>28</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD4">
         <v>25</v>
@@ -1595,37 +1595,37 @@
         <v>4.8</v>
       </c>
       <c r="BI4">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BJ4">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BL4">
         <v>80</v>
       </c>
       <c r="BM4">
-        <v>1.02</v>
+        <v>60</v>
       </c>
       <c r="BN4">
         <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP4">
         <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR4">
         <v>28</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT4">
         <v>7.4</v>
@@ -1637,13 +1637,13 @@
         <v>24</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX4">
         <v>32</v>
       </c>
       <c r="BY4">
-        <v>1.02</v>
+        <v>4.8</v>
       </c>
       <c r="BZ4">
         <v>19</v>
@@ -1672,40 +1672,40 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H5">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="I5">
         <v>1.87</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.3</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
         <v>5.6</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
         <v>2.52</v>
       </c>
       <c r="Q5">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R5">
         <v>1.61</v>
@@ -1714,22 +1714,22 @@
         <v>2.54</v>
       </c>
       <c r="T5">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="U5">
         <v>2.68</v>
       </c>
       <c r="V5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W5">
         <v>1.27</v>
       </c>
       <c r="X5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z5">
         <v>14</v>
@@ -1747,25 +1747,25 @@
         <v>10</v>
       </c>
       <c r="AE5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AF5">
         <v>42</v>
       </c>
       <c r="AG5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH5">
         <v>17</v>
       </c>
       <c r="AI5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AK5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL5">
         <v>48</v>
@@ -1777,34 +1777,34 @@
         <v>38</v>
       </c>
       <c r="AO5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
         <v>12.5</v>
       </c>
       <c r="AS5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU5">
         <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5">
         <v>14.5</v>
       </c>
       <c r="AX5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AY5">
         <v>15</v>
@@ -1816,19 +1816,19 @@
         <v>23</v>
       </c>
       <c r="BB5">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="BC5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE5">
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG5">
         <v>7.8</v>
@@ -1837,61 +1837,61 @@
         <v>5.1</v>
       </c>
       <c r="BI5">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BL5">
         <v>100</v>
       </c>
       <c r="BM5">
-        <v>1.02</v>
+        <v>65</v>
       </c>
       <c r="BN5">
         <v>9.6</v>
       </c>
       <c r="BO5">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="BP5">
         <v>38</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR5">
         <v>42</v>
       </c>
       <c r="BS5">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="BT5">
         <v>5.8</v>
       </c>
       <c r="BU5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV5">
         <v>14.5</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BX5">
         <v>26</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BZ5">
         <v>18</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="CB5" t="s">
         <v>112</v>
@@ -1917,10 +1917,10 @@
         <v>1.51</v>
       </c>
       <c r="G6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>7.2</v>
@@ -1932,7 +1932,7 @@
         <v>5.3</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.03</v>
@@ -1944,19 +1944,19 @@
         <v>1.18</v>
       </c>
       <c r="P6">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="Q6">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R6">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S6">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T6">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U6">
         <v>2.26</v>
@@ -1965,7 +1965,7 @@
         <v>1.16</v>
       </c>
       <c r="W6">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X6">
         <v>32</v>
@@ -1989,7 +1989,7 @@
         <v>27</v>
       </c>
       <c r="AE6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF6">
         <v>11.5</v>
@@ -2004,7 +2004,7 @@
         <v>80</v>
       </c>
       <c r="AJ6">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AK6">
         <v>15</v>
@@ -2022,25 +2022,25 @@
         <v>80</v>
       </c>
       <c r="AP6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR6">
         <v>50</v>
       </c>
       <c r="AS6">
+        <v>48</v>
+      </c>
+      <c r="AT6">
         <v>10</v>
-      </c>
-      <c r="AT6">
-        <v>10.5</v>
       </c>
       <c r="AU6">
         <v>10.5</v>
       </c>
       <c r="AV6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW6">
         <v>55</v>
@@ -2058,28 +2058,28 @@
         <v>42</v>
       </c>
       <c r="BB6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
         <v>13</v>
       </c>
       <c r="BD6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE6">
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG6">
         <v>42</v>
       </c>
       <c r="BH6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ6">
         <v>9.6</v>
@@ -2124,7 +2124,7 @@
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
@@ -2156,16 +2156,16 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H7">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I7">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="J7">
         <v>3.25</v>
@@ -2183,10 +2183,10 @@
         <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
         <v>2.16</v>
@@ -2195,34 +2195,34 @@
         <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U7">
         <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W7">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA7">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -2231,25 +2231,25 @@
         <v>12</v>
       </c>
       <c r="AE7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH7">
         <v>19.5</v>
       </c>
       <c r="AI7">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AK7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL7">
         <v>70</v>
@@ -2261,10 +2261,10 @@
         <v>60</v>
       </c>
       <c r="AO7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
         <v>8</v>
@@ -2273,25 +2273,25 @@
         <v>12.5</v>
       </c>
       <c r="AS7">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AT7">
         <v>10.5</v>
       </c>
       <c r="AU7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
         <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
         <v>16</v>
@@ -2300,7 +2300,7 @@
         <v>30</v>
       </c>
       <c r="BB7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC7">
         <v>29</v>
@@ -2315,7 +2315,7 @@
         <v>30</v>
       </c>
       <c r="BG7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH7">
         <v>3.65</v>
@@ -2327,43 +2327,43 @@
         <v>12</v>
       </c>
       <c r="BK7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL7">
         <v>170</v>
       </c>
       <c r="BM7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BN7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP7">
         <v>36</v>
       </c>
       <c r="BQ7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR7">
         <v>55</v>
       </c>
       <c r="BS7">
+        <v>4.5</v>
+      </c>
+      <c r="BT7">
+        <v>6</v>
+      </c>
+      <c r="BU7">
         <v>4.4</v>
-      </c>
-      <c r="BT7">
-        <v>6.2</v>
-      </c>
-      <c r="BU7">
-        <v>3.95</v>
       </c>
       <c r="BV7">
         <v>22</v>
       </c>
       <c r="BW7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX7">
         <v>42</v>
@@ -2398,52 +2398,52 @@
         <v>109</v>
       </c>
       <c r="F8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H8">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="I8">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
         <v>4.9</v>
       </c>
       <c r="L8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="Q8">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="R8">
+        <v>1.67</v>
+      </c>
+      <c r="S8">
+        <v>2.32</v>
+      </c>
+      <c r="T8">
         <v>1.58</v>
       </c>
-      <c r="S8">
-        <v>2.48</v>
-      </c>
-      <c r="T8">
-        <v>1.66</v>
-      </c>
       <c r="U8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V8">
         <v>2.34</v>
@@ -2452,13 +2452,13 @@
         <v>1.22</v>
       </c>
       <c r="X8">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Y8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA8">
         <v>19</v>
@@ -2467,13 +2467,13 @@
         <v>28</v>
       </c>
       <c r="AC8">
+        <v>13.5</v>
+      </c>
+      <c r="AD8">
         <v>13</v>
       </c>
-      <c r="AD8">
-        <v>12.5</v>
-      </c>
       <c r="AE8">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AF8">
         <v>55</v>
@@ -2485,31 +2485,31 @@
         <v>22</v>
       </c>
       <c r="AI8">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AJ8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK8">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN8">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AO8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP8">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AQ8">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR8">
         <v>10</v>
@@ -2518,10 +2518,10 @@
         <v>15</v>
       </c>
       <c r="AT8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV8">
         <v>8.800000000000001</v>
@@ -2530,52 +2530,52 @@
         <v>13.5</v>
       </c>
       <c r="AX8">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AY8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="BB8">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC8">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD8">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE8">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF8">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG8">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH8">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BI8">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BJ8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BM8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BN8">
         <v>11</v>
@@ -2584,22 +2584,22 @@
         <v>6.6</v>
       </c>
       <c r="BP8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BQ8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BR8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BS8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BT8">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BU8">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV8">
         <v>12.5</v>
@@ -2608,16 +2608,16 @@
         <v>7.6</v>
       </c>
       <c r="BX8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BY8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2640,16 +2640,16 @@
         <v>110</v>
       </c>
       <c r="F9">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H9">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I9">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J9">
         <v>3.4</v>
@@ -2664,10 +2664,10 @@
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O9">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P9">
         <v>1.85</v>
@@ -2679,7 +2679,7 @@
         <v>1.32</v>
       </c>
       <c r="S9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T9">
         <v>1.86</v>
@@ -2688,7 +2688,7 @@
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W9">
         <v>1.45</v>
@@ -2703,10 +2703,10 @@
         <v>16</v>
       </c>
       <c r="AA9">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AB9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC9">
         <v>7.6</v>
@@ -2715,7 +2715,7 @@
         <v>11.5</v>
       </c>
       <c r="AE9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF9">
         <v>22</v>
@@ -2727,25 +2727,25 @@
         <v>19.5</v>
       </c>
       <c r="AI9">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ9">
         <v>210</v>
       </c>
       <c r="AK9">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL9">
-        <v>280</v>
+        <v>65</v>
       </c>
       <c r="AM9">
-        <v>920</v>
+        <v>840</v>
       </c>
       <c r="AN9">
         <v>48</v>
       </c>
       <c r="AO9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP9">
         <v>11</v>
@@ -2754,10 +2754,10 @@
         <v>9</v>
       </c>
       <c r="AR9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT9">
         <v>10.5</v>
@@ -2778,25 +2778,25 @@
         <v>12</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BB9">
+        <v>27</v>
+      </c>
+      <c r="BC9">
         <v>32</v>
       </c>
-      <c r="BC9">
-        <v>28</v>
-      </c>
       <c r="BD9">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BE9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF9">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BG9">
         <v>21</v>
@@ -2811,55 +2811,55 @@
         <v>12</v>
       </c>
       <c r="BK9">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BL9">
         <v>160</v>
       </c>
       <c r="BM9">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BN9">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO9">
         <v>5.3</v>
       </c>
       <c r="BP9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ9">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR9">
         <v>48</v>
       </c>
       <c r="BS9">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BT9">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU9">
         <v>4.6</v>
       </c>
       <c r="BV9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW9">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BX9">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BY9">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BZ9">
         <v>38</v>
       </c>
       <c r="CA9">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB9" t="s">
         <v>112</v>
@@ -2882,22 +2882,22 @@
         <v>111</v>
       </c>
       <c r="F10">
+        <v>3.7</v>
+      </c>
+      <c r="G10">
         <v>3.75</v>
       </c>
-      <c r="G10">
-        <v>3.8</v>
-      </c>
       <c r="H10">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I10">
         <v>1.99</v>
       </c>
       <c r="J10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10">
         <v>1.27</v>
@@ -2912,37 +2912,37 @@
         <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q10">
         <v>1.51</v>
       </c>
       <c r="R10">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S10">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T10">
         <v>1.51</v>
       </c>
       <c r="U10">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V10">
         <v>2</v>
       </c>
       <c r="W10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y10">
         <v>16</v>
       </c>
       <c r="Z10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA10">
         <v>25</v>
@@ -2960,7 +2960,7 @@
         <v>17.5</v>
       </c>
       <c r="AF10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG10">
         <v>16</v>
@@ -2981,7 +2981,7 @@
         <v>36</v>
       </c>
       <c r="AM10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN10">
         <v>23</v>
@@ -3005,7 +3005,7 @@
         <v>21</v>
       </c>
       <c r="AU10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10">
         <v>10</v>
@@ -3038,13 +3038,13 @@
         <v>44</v>
       </c>
       <c r="BF10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG10">
         <v>7.4</v>
       </c>
       <c r="BH10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI10">
         <v>4.2</v>
@@ -3059,16 +3059,16 @@
         <v>70</v>
       </c>
       <c r="BM10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BN10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO10">
         <v>6.8</v>
       </c>
       <c r="BP10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ10">
         <v>18.5</v>
@@ -3083,7 +3083,7 @@
         <v>5.3</v>
       </c>
       <c r="BU10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
         <v>12.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -352,7 +352,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-30 10:09:30</t>
+    <t>2026-09-30 12:19:18</t>
   </si>
 </sst>
 </file>
@@ -946,226 +946,226 @@
         <v>103</v>
       </c>
       <c r="F2">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="G2">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="H2">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J2">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="O2">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Q2">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="U2">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="V2">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AB2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AC2">
         <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AE2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF2">
         <v>22</v>
       </c>
       <c r="AG2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AI2">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL2">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>310</v>
       </c>
       <c r="AN2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
         <v>6</v>
       </c>
       <c r="AV2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AX2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>5.4</v>
+        <v>70</v>
       </c>
       <c r="BB2">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="BC2">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="BD2">
-        <v>5.4</v>
+        <v>75</v>
       </c>
       <c r="BE2">
-        <v>5</v>
+        <v>220</v>
       </c>
       <c r="BF2">
-        <v>5.5</v>
+        <v>48</v>
       </c>
       <c r="BG2">
-        <v>5.3</v>
+        <v>46</v>
       </c>
       <c r="BH2">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="BI2">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BK2">
-        <v>3.65</v>
+        <v>15.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP2">
+        <v>46</v>
+      </c>
+      <c r="BQ2">
         <v>32</v>
       </c>
-      <c r="BQ2">
-        <v>4.4</v>
-      </c>
       <c r="BR2">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="BS2">
-        <v>4.7</v>
+        <v>90</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BW2">
-        <v>4.4</v>
+        <v>36</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="BY2">
-        <v>4.7</v>
+        <v>85</v>
       </c>
       <c r="BZ2">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="CA2">
-        <v>4.7</v>
+        <v>55</v>
       </c>
       <c r="CB2" t="s">
         <v>112</v>
@@ -1188,226 +1188,226 @@
         <v>104</v>
       </c>
       <c r="F3">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="G3">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="H3">
+        <v>21</v>
+      </c>
+      <c r="I3">
+        <v>40</v>
+      </c>
+      <c r="J3">
+        <v>6.8</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>6.6</v>
+      </c>
+      <c r="O3">
+        <v>1.15</v>
+      </c>
+      <c r="P3">
+        <v>2.38</v>
+      </c>
+      <c r="Q3">
+        <v>1.64</v>
+      </c>
+      <c r="R3">
+        <v>1.45</v>
+      </c>
+      <c r="S3">
+        <v>2.96</v>
+      </c>
+      <c r="T3">
+        <v>2.06</v>
+      </c>
+      <c r="U3">
+        <v>1.8</v>
+      </c>
+      <c r="V3">
+        <v>1.03</v>
+      </c>
+      <c r="W3">
+        <v>5.7</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>7.8</v>
+      </c>
+      <c r="AC3">
+        <v>13</v>
+      </c>
+      <c r="AD3">
+        <v>55</v>
+      </c>
+      <c r="AE3">
+        <v>470</v>
+      </c>
+      <c r="AF3">
+        <v>5.8</v>
+      </c>
+      <c r="AG3">
+        <v>9</v>
+      </c>
+      <c r="AH3">
+        <v>34</v>
+      </c>
+      <c r="AI3">
+        <v>200</v>
+      </c>
+      <c r="AJ3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK3">
+        <v>15.5</v>
+      </c>
+      <c r="AL3">
+        <v>44</v>
+      </c>
+      <c r="AM3">
+        <v>260</v>
+      </c>
+      <c r="AN3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>6.8</v>
+      </c>
+      <c r="AQ3">
+        <v>6.8</v>
+      </c>
+      <c r="AR3">
+        <v>6.8</v>
+      </c>
+      <c r="AS3">
+        <v>6.8</v>
+      </c>
+      <c r="AT3">
+        <v>6.4</v>
+      </c>
+      <c r="AU3">
+        <v>5.6</v>
+      </c>
+      <c r="AV3">
+        <v>6.4</v>
+      </c>
+      <c r="AW3">
+        <v>6.6</v>
+      </c>
+      <c r="AX3">
+        <v>4.8</v>
+      </c>
+      <c r="AY3">
+        <v>7.2</v>
+      </c>
+      <c r="AZ3">
+        <v>6.4</v>
+      </c>
+      <c r="BA3">
+        <v>6.6</v>
+      </c>
+      <c r="BB3">
+        <v>7</v>
+      </c>
+      <c r="BC3">
         <v>6</v>
       </c>
-      <c r="I3">
-        <v>8.6</v>
-      </c>
-      <c r="J3">
-        <v>3.35</v>
-      </c>
-      <c r="K3">
-        <v>4.2</v>
-      </c>
-      <c r="L3">
-        <v>1.46</v>
-      </c>
-      <c r="M3">
-        <v>1.1</v>
-      </c>
-      <c r="N3">
-        <v>2.52</v>
-      </c>
-      <c r="O3">
-        <v>1.46</v>
-      </c>
-      <c r="P3">
-        <v>1.51</v>
-      </c>
-      <c r="Q3">
+      <c r="BD3">
+        <v>6.6</v>
+      </c>
+      <c r="BE3">
+        <v>6.6</v>
+      </c>
+      <c r="BF3">
+        <v>5.9</v>
+      </c>
+      <c r="BG3">
+        <v>6.6</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BJ3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK3">
+        <v>7.4</v>
+      </c>
+      <c r="BL3">
+        <v>950</v>
+      </c>
+      <c r="BM3">
+        <v>8</v>
+      </c>
+      <c r="BN3">
         <v>2.26</v>
       </c>
-      <c r="R3">
-        <v>1.2</v>
-      </c>
-      <c r="S3">
-        <v>4.7</v>
-      </c>
-      <c r="T3">
-        <v>2.24</v>
-      </c>
-      <c r="U3">
-        <v>1.56</v>
-      </c>
-      <c r="V3">
-        <v>1.13</v>
-      </c>
-      <c r="W3">
-        <v>2.32</v>
-      </c>
-      <c r="X3">
-        <v>10.5</v>
-      </c>
-      <c r="Y3">
-        <v>20</v>
-      </c>
-      <c r="Z3">
-        <v>75</v>
-      </c>
-      <c r="AA3">
-        <v>700</v>
-      </c>
-      <c r="AB3">
-        <v>6.8</v>
-      </c>
-      <c r="AC3">
-        <v>9.4</v>
-      </c>
-      <c r="AD3">
-        <v>36</v>
-      </c>
-      <c r="AE3">
-        <v>700</v>
-      </c>
-      <c r="AF3">
-        <v>9.6</v>
-      </c>
-      <c r="AG3">
-        <v>12.5</v>
-      </c>
-      <c r="AH3">
-        <v>36</v>
-      </c>
-      <c r="AI3">
-        <v>700</v>
-      </c>
-      <c r="AJ3">
-        <v>19.5</v>
-      </c>
-      <c r="AK3">
-        <v>27</v>
-      </c>
-      <c r="AL3">
-        <v>70</v>
-      </c>
-      <c r="AM3">
-        <v>700</v>
-      </c>
-      <c r="AN3">
-        <v>17.5</v>
-      </c>
-      <c r="AO3">
-        <v>700</v>
-      </c>
-      <c r="AP3">
+      <c r="BO3">
+        <v>2.02</v>
+      </c>
+      <c r="BP3">
         <v>4.4</v>
       </c>
-      <c r="AQ3">
-        <v>4.5</v>
-      </c>
-      <c r="AR3">
-        <v>5.4</v>
-      </c>
-      <c r="AS3">
-        <v>5.8</v>
-      </c>
-      <c r="AT3">
-        <v>3.15</v>
-      </c>
-      <c r="AU3">
-        <v>4.9</v>
-      </c>
-      <c r="AV3">
-        <v>5</v>
-      </c>
-      <c r="AW3">
-        <v>5.7</v>
-      </c>
-      <c r="AX3">
-        <v>3.65</v>
-      </c>
-      <c r="AY3">
-        <v>4</v>
-      </c>
-      <c r="AZ3">
-        <v>5</v>
-      </c>
-      <c r="BA3">
-        <v>5.7</v>
-      </c>
-      <c r="BB3">
-        <v>4.5</v>
-      </c>
-      <c r="BC3">
-        <v>4.8</v>
-      </c>
-      <c r="BD3">
-        <v>5.4</v>
-      </c>
-      <c r="BE3">
-        <v>5.8</v>
-      </c>
-      <c r="BF3">
-        <v>4.4</v>
-      </c>
-      <c r="BG3">
-        <v>5.8</v>
-      </c>
-      <c r="BH3">
-        <v>3.2</v>
-      </c>
-      <c r="BI3">
-        <v>2.4</v>
-      </c>
-      <c r="BJ3">
-        <v>15</v>
-      </c>
-      <c r="BK3">
-        <v>4.2</v>
-      </c>
-      <c r="BL3">
+      <c r="BQ3">
+        <v>3.7</v>
+      </c>
+      <c r="BR3">
+        <v>23</v>
+      </c>
+      <c r="BS3">
+        <v>16</v>
+      </c>
+      <c r="BT3">
         <v>1000</v>
       </c>
-      <c r="BM3">
-        <v>5.8</v>
-      </c>
-      <c r="BN3">
-        <v>4.4</v>
-      </c>
-      <c r="BO3">
-        <v>2.52</v>
-      </c>
-      <c r="BP3">
-        <v>14</v>
-      </c>
-      <c r="BQ3">
-        <v>4.1</v>
-      </c>
-      <c r="BR3">
-        <v>44</v>
-      </c>
-      <c r="BS3">
-        <v>5.2</v>
-      </c>
-      <c r="BT3">
-        <v>12</v>
-      </c>
       <c r="BU3">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BY3">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="CA3">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>112</v>
@@ -1430,16 +1430,16 @@
         <v>105</v>
       </c>
       <c r="F4">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G4">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H4">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J4">
         <v>3.75</v>
@@ -1454,25 +1454,25 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P4">
+        <v>2.54</v>
+      </c>
+      <c r="Q4">
+        <v>1.62</v>
+      </c>
+      <c r="R4">
+        <v>1.61</v>
+      </c>
+      <c r="S4">
         <v>2.5</v>
       </c>
-      <c r="Q4">
-        <v>1.61</v>
-      </c>
-      <c r="R4">
-        <v>1.6</v>
-      </c>
-      <c r="S4">
-        <v>2.52</v>
-      </c>
       <c r="T4">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="U4">
         <v>2.74</v>
@@ -1481,13 +1481,13 @@
         <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X4">
         <v>24</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z4">
         <v>25</v>
@@ -1502,10 +1502,10 @@
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF4">
         <v>20</v>
@@ -1514,43 +1514,43 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI4">
+        <v>34</v>
+      </c>
+      <c r="AJ4">
         <v>36</v>
       </c>
-      <c r="AJ4">
-        <v>34</v>
-      </c>
       <c r="AK4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4">
         <v>30</v>
       </c>
       <c r="AM4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN4">
         <v>13.5</v>
       </c>
       <c r="AO4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4">
         <v>40</v>
       </c>
       <c r="AT4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU4">
         <v>8.4</v>
@@ -1559,34 +1559,34 @@
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA4">
         <v>28</v>
       </c>
       <c r="BB4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG4">
         <v>15.5</v>
@@ -1601,7 +1601,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BL4">
         <v>80</v>
@@ -1619,37 +1619,37 @@
         <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BR4">
         <v>28</v>
       </c>
       <c r="BS4">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
         <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW4">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BX4">
         <v>32</v>
       </c>
       <c r="BY4">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BZ4">
         <v>19</v>
       </c>
       <c r="CA4">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="CB4" t="s">
         <v>112</v>
@@ -1672,67 +1672,67 @@
         <v>106</v>
       </c>
       <c r="F5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H5">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="I5">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="R5">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="S5">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="T5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U5">
         <v>2.68</v>
       </c>
       <c r="V5">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="W5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X5">
         <v>26</v>
       </c>
       <c r="Y5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA5">
         <v>23</v>
@@ -1741,31 +1741,31 @@
         <v>23</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5">
         <v>42</v>
       </c>
       <c r="AG5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AJ5">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AK5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL5">
         <v>48</v>
@@ -1774,16 +1774,16 @@
         <v>70</v>
       </c>
       <c r="AN5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO5">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AP5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR5">
         <v>12.5</v>
@@ -1795,7 +1795,7 @@
         <v>21</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV5">
         <v>9.199999999999999</v>
@@ -1804,70 +1804,70 @@
         <v>14.5</v>
       </c>
       <c r="AX5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ5">
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BC5">
         <v>40</v>
       </c>
       <c r="BD5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE5">
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH5">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BI5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BK5">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BL5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM5">
         <v>65</v>
       </c>
       <c r="BN5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BO5">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="BP5">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BQ5">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS5">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT5">
         <v>5.8</v>
@@ -1876,22 +1876,22 @@
         <v>4.3</v>
       </c>
       <c r="BV5">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BW5">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BX5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY5">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BZ5">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="CA5">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="CB5" t="s">
         <v>112</v>
@@ -1914,10 +1914,10 @@
         <v>107</v>
       </c>
       <c r="F6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H6">
         <v>6.6</v>
@@ -1932,7 +1932,7 @@
         <v>5.3</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M6">
         <v>1.03</v>
@@ -1941,37 +1941,37 @@
         <v>6</v>
       </c>
       <c r="O6">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S6">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U6">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
         <v>1.16</v>
       </c>
       <c r="W6">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z6">
         <v>75</v>
@@ -1983,7 +1983,7 @@
         <v>12</v>
       </c>
       <c r="AC6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD6">
         <v>27</v>
@@ -1992,25 +1992,25 @@
         <v>100</v>
       </c>
       <c r="AF6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI6">
         <v>80</v>
       </c>
       <c r="AJ6">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AK6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM6">
         <v>95</v>
@@ -2022,25 +2022,25 @@
         <v>80</v>
       </c>
       <c r="AP6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AR6">
         <v>50</v>
       </c>
       <c r="AS6">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AT6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU6">
         <v>10.5</v>
       </c>
       <c r="AV6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW6">
         <v>55</v>
@@ -2052,19 +2052,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA6">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC6">
         <v>13</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE6">
         <v>55</v>
@@ -2073,7 +2073,7 @@
         <v>5.2</v>
       </c>
       <c r="BG6">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BH6">
         <v>5.6</v>
@@ -2094,13 +2094,13 @@
         <v>1.02</v>
       </c>
       <c r="BN6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO6">
         <v>4</v>
       </c>
       <c r="BP6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ6">
         <v>5.9</v>
@@ -2156,46 +2156,46 @@
         <v>108</v>
       </c>
       <c r="F7">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="G7">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="H7">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="I7">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>1.45</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
         <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q7">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T7">
         <v>1.86</v>
@@ -2204,172 +2204,172 @@
         <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="W7">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AA7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AB7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
         <v>8</v>
       </c>
       <c r="AD7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF7">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AG7">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH7">
         <v>19.5</v>
       </c>
       <c r="AI7">
+        <v>42</v>
+      </c>
+      <c r="AJ7">
         <v>120</v>
       </c>
-      <c r="AJ7">
-        <v>75</v>
-      </c>
       <c r="AK7">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AL7">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AO7">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AP7">
+        <v>11</v>
+      </c>
+      <c r="AQ7">
+        <v>7.6</v>
+      </c>
+      <c r="AR7">
         <v>10.5</v>
       </c>
-      <c r="AQ7">
-        <v>8</v>
-      </c>
-      <c r="AR7">
-        <v>12.5</v>
-      </c>
       <c r="AS7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AY7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB7">
+        <v>55</v>
+      </c>
+      <c r="BC7">
+        <v>36</v>
+      </c>
+      <c r="BD7">
         <v>44</v>
-      </c>
-      <c r="BC7">
-        <v>29</v>
-      </c>
-      <c r="BD7">
-        <v>38</v>
       </c>
       <c r="BE7">
         <v>80</v>
       </c>
       <c r="BF7">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BG7">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BH7">
         <v>3.65</v>
       </c>
       <c r="BI7">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7">
         <v>12</v>
       </c>
       <c r="BK7">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BL7">
         <v>170</v>
       </c>
       <c r="BM7">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BN7">
         <v>8</v>
       </c>
       <c r="BO7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BP7">
         <v>36</v>
       </c>
       <c r="BQ7">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BR7">
         <v>55</v>
       </c>
       <c r="BS7">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT7">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BU7">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BV7">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="BW7">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BX7">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BY7">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2401,19 +2401,19 @@
         <v>4.7</v>
       </c>
       <c r="G8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H8">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="I8">
         <v>1.72</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L8">
         <v>1.28</v>
@@ -2422,31 +2422,31 @@
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P8">
         <v>2.72</v>
       </c>
       <c r="Q8">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R8">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S8">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T8">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U8">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V8">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="W8">
         <v>1.22</v>
@@ -2455,31 +2455,31 @@
         <v>34</v>
       </c>
       <c r="Y8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z8">
         <v>13.5</v>
       </c>
       <c r="AA8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB8">
         <v>28</v>
       </c>
       <c r="AC8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD8">
         <v>13</v>
       </c>
       <c r="AE8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF8">
         <v>55</v>
       </c>
       <c r="AG8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH8">
         <v>22</v>
@@ -2500,16 +2500,16 @@
         <v>80</v>
       </c>
       <c r="AN8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO8">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AP8">
         <v>23</v>
       </c>
       <c r="AQ8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
         <v>10</v>
@@ -2518,52 +2518,52 @@
         <v>15</v>
       </c>
       <c r="AT8">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="AU8">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV8">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8">
         <v>13.5</v>
       </c>
       <c r="AX8">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="AY8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA8">
         <v>21</v>
       </c>
       <c r="BB8">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BC8">
+        <v>5.4</v>
+      </c>
+      <c r="BD8">
+        <v>5.4</v>
+      </c>
+      <c r="BE8">
         <v>5.5</v>
       </c>
-      <c r="BD8">
-        <v>5.5</v>
-      </c>
-      <c r="BE8">
-        <v>5.2</v>
-      </c>
       <c r="BF8">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="BG8">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI8">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8">
         <v>11</v>
@@ -2572,7 +2572,7 @@
         <v>6.8</v>
       </c>
       <c r="BL8">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM8">
         <v>55</v>
@@ -2581,16 +2581,16 @@
         <v>11</v>
       </c>
       <c r="BO8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BP8">
         <v>44</v>
       </c>
       <c r="BQ8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BR8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS8">
         <v>26</v>
@@ -2599,25 +2599,25 @@
         <v>5.6</v>
       </c>
       <c r="BU8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW8">
         <v>7.6</v>
       </c>
       <c r="BX8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY8">
         <v>14</v>
       </c>
       <c r="BZ8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB8" t="s">
         <v>112</v>
@@ -2664,13 +2664,13 @@
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
         <v>1.37</v>
       </c>
       <c r="P9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q9">
         <v>2.1</v>
@@ -2679,7 +2679,7 @@
         <v>1.32</v>
       </c>
       <c r="S9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T9">
         <v>1.86</v>
@@ -2688,10 +2688,10 @@
         <v>2.06</v>
       </c>
       <c r="V9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W9">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X9">
         <v>13</v>
@@ -2709,7 +2709,7 @@
         <v>12</v>
       </c>
       <c r="AC9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD9">
         <v>11.5</v>
@@ -2730,16 +2730,16 @@
         <v>140</v>
       </c>
       <c r="AJ9">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AK9">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AL9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM9">
-        <v>840</v>
+        <v>740</v>
       </c>
       <c r="AN9">
         <v>48</v>
@@ -2769,7 +2769,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AX9">
         <v>18</v>
@@ -2781,10 +2781,10 @@
         <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BB9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC9">
         <v>32</v>
@@ -2793,7 +2793,7 @@
         <v>38</v>
       </c>
       <c r="BE9">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BF9">
         <v>32</v>
@@ -2882,22 +2882,22 @@
         <v>111</v>
       </c>
       <c r="F10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G10">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H10">
+        <v>1.95</v>
+      </c>
+      <c r="I10">
         <v>1.97</v>
-      </c>
-      <c r="I10">
-        <v>1.99</v>
       </c>
       <c r="J10">
         <v>4.4</v>
       </c>
       <c r="K10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
         <v>1.27</v>
@@ -2906,22 +2906,22 @@
         <v>1.03</v>
       </c>
       <c r="N10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O10">
         <v>1.16</v>
       </c>
       <c r="P10">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R10">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S10">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T10">
         <v>1.51</v>
@@ -2930,28 +2930,28 @@
         <v>2.84</v>
       </c>
       <c r="V10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W10">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y10">
         <v>16</v>
       </c>
       <c r="Z10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA10">
         <v>25</v>
       </c>
       <c r="AB10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD10">
         <v>11</v>
@@ -2963,7 +2963,7 @@
         <v>34</v>
       </c>
       <c r="AG10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH10">
         <v>14.5</v>
@@ -2987,7 +2987,7 @@
         <v>23</v>
       </c>
       <c r="AO10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP10">
         <v>26</v>
@@ -3002,10 +3002,10 @@
         <v>22</v>
       </c>
       <c r="AT10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV10">
         <v>10</v>
@@ -3023,7 +3023,7 @@
         <v>13.5</v>
       </c>
       <c r="BA10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB10">
         <v>60</v>
@@ -3038,7 +3038,7 @@
         <v>44</v>
       </c>
       <c r="BF10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG10">
         <v>7.4</v>
@@ -3074,7 +3074,7 @@
         <v>18.5</v>
       </c>
       <c r="BR10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS10">
         <v>20</v>
@@ -3092,13 +3092,13 @@
         <v>8.4</v>
       </c>
       <c r="BX10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY10">
         <v>15</v>
       </c>
       <c r="BZ10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CA10">
         <v>10</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -334,7 +334,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-30 14:31:07</t>
+    <t>2026-09-30 16:43:55</t>
   </si>
 </sst>
 </file>
@@ -928,226 +928,226 @@
         <v>99</v>
       </c>
       <c r="F2">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="G2">
-        <v>2.56</v>
+        <v>3.35</v>
       </c>
       <c r="H2">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="I2">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="L2">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="N2">
+        <v>1.8</v>
+      </c>
+      <c r="O2">
+        <v>2.18</v>
+      </c>
+      <c r="P2">
+        <v>1.22</v>
+      </c>
+      <c r="Q2">
+        <v>5.2</v>
+      </c>
+      <c r="R2">
+        <v>1.06</v>
+      </c>
+      <c r="S2">
+        <v>16</v>
+      </c>
+      <c r="T2">
+        <v>3.25</v>
+      </c>
+      <c r="U2">
+        <v>1.37</v>
+      </c>
+      <c r="V2">
+        <v>1.45</v>
+      </c>
+      <c r="W2">
+        <v>1.43</v>
+      </c>
+      <c r="X2">
+        <v>4.9</v>
+      </c>
+      <c r="Y2">
+        <v>6.2</v>
+      </c>
+      <c r="Z2">
+        <v>17.5</v>
+      </c>
+      <c r="AA2">
+        <v>95</v>
+      </c>
+      <c r="AB2">
+        <v>6.4</v>
+      </c>
+      <c r="AC2">
+        <v>7.2</v>
+      </c>
+      <c r="AD2">
+        <v>22</v>
+      </c>
+      <c r="AE2">
+        <v>120</v>
+      </c>
+      <c r="AF2">
+        <v>19</v>
+      </c>
+      <c r="AG2">
+        <v>21</v>
+      </c>
+      <c r="AH2">
+        <v>65</v>
+      </c>
+      <c r="AI2">
+        <v>290</v>
+      </c>
+      <c r="AJ2">
+        <v>90</v>
+      </c>
+      <c r="AK2">
+        <v>130</v>
+      </c>
+      <c r="AL2">
+        <v>340</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>220</v>
+      </c>
+      <c r="AO2">
+        <v>210</v>
+      </c>
+      <c r="AP2">
+        <v>4.4</v>
+      </c>
+      <c r="AQ2">
+        <v>5.5</v>
+      </c>
+      <c r="AR2">
+        <v>14.5</v>
+      </c>
+      <c r="AS2">
+        <v>50</v>
+      </c>
+      <c r="AT2">
         <v>5.7</v>
       </c>
-      <c r="O2">
-        <v>1.19</v>
-      </c>
-      <c r="P2">
-        <v>2.6</v>
-      </c>
-      <c r="Q2">
-        <v>1.62</v>
-      </c>
-      <c r="R2">
-        <v>1.63</v>
-      </c>
-      <c r="S2">
-        <v>2.48</v>
-      </c>
-      <c r="T2">
-        <v>1.5</v>
-      </c>
-      <c r="U2">
-        <v>2.78</v>
-      </c>
-      <c r="V2">
-        <v>1.51</v>
-      </c>
-      <c r="W2">
-        <v>1.64</v>
-      </c>
-      <c r="X2">
-        <v>23</v>
-      </c>
-      <c r="Y2">
-        <v>18</v>
-      </c>
-      <c r="Z2">
-        <v>24</v>
-      </c>
-      <c r="AA2">
-        <v>55</v>
-      </c>
-      <c r="AB2">
-        <v>16.5</v>
-      </c>
-      <c r="AC2">
-        <v>9</v>
-      </c>
-      <c r="AD2">
-        <v>13</v>
-      </c>
-      <c r="AE2">
-        <v>26</v>
-      </c>
-      <c r="AF2">
-        <v>20</v>
-      </c>
-      <c r="AG2">
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
         <v>12.5</v>
       </c>
-      <c r="AH2">
-        <v>14.5</v>
-      </c>
-      <c r="AI2">
-        <v>34</v>
-      </c>
-      <c r="AJ2">
-        <v>36</v>
-      </c>
-      <c r="AK2">
-        <v>22</v>
-      </c>
-      <c r="AL2">
-        <v>29</v>
-      </c>
-      <c r="AM2">
-        <v>55</v>
-      </c>
-      <c r="AN2">
-        <v>13.5</v>
-      </c>
-      <c r="AO2">
-        <v>17.5</v>
-      </c>
-      <c r="AP2">
-        <v>20</v>
-      </c>
-      <c r="AQ2">
+      <c r="AW2">
+        <v>75</v>
+      </c>
+      <c r="AX2">
         <v>16</v>
       </c>
-      <c r="AR2">
-        <v>22</v>
-      </c>
-      <c r="AS2">
-        <v>40</v>
-      </c>
-      <c r="AT2">
-        <v>14.5</v>
-      </c>
-      <c r="AU2">
-        <v>8.4</v>
-      </c>
-      <c r="AV2">
-        <v>11.5</v>
-      </c>
-      <c r="AW2">
-        <v>23</v>
-      </c>
-      <c r="AX2">
-        <v>17.5</v>
-      </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ2">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BC2">
-        <v>19.5</v>
+        <v>75</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="BE2">
-        <v>44</v>
+        <v>480</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="BG2">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BH2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>106</v>
@@ -1170,28 +1170,28 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="H3">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="I3">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="L3">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <v>6</v>
@@ -1200,196 +1200,196 @@
         <v>1.18</v>
       </c>
       <c r="P3">
-        <v>2.72</v>
+        <v>2.16</v>
       </c>
       <c r="Q3">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="R3">
-        <v>1.69</v>
+        <v>1.33</v>
       </c>
       <c r="S3">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="T3">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="U3">
-        <v>2.74</v>
+        <v>2.02</v>
       </c>
       <c r="V3">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="W3">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
+        <v>6.4</v>
+      </c>
+      <c r="Z3">
+        <v>6</v>
+      </c>
+      <c r="AA3">
+        <v>11</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>8.4</v>
+      </c>
+      <c r="AD3">
+        <v>7.2</v>
+      </c>
+      <c r="AE3">
+        <v>15</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>24</v>
+      </c>
+      <c r="AH3">
+        <v>23</v>
+      </c>
+      <c r="AI3">
+        <v>48</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>150</v>
+      </c>
+      <c r="AL3">
+        <v>140</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
         <v>13</v>
       </c>
-      <c r="Z3">
-        <v>14.5</v>
-      </c>
-      <c r="AA3">
+      <c r="AP3">
+        <v>1000</v>
+      </c>
+      <c r="AQ3">
+        <v>5.8</v>
+      </c>
+      <c r="AR3">
+        <v>5.3</v>
+      </c>
+      <c r="AS3">
+        <v>9.6</v>
+      </c>
+      <c r="AT3">
+        <v>1000</v>
+      </c>
+      <c r="AU3">
+        <v>7.4</v>
+      </c>
+      <c r="AV3">
+        <v>6.6</v>
+      </c>
+      <c r="AW3">
+        <v>13</v>
+      </c>
+      <c r="AX3">
+        <v>1000</v>
+      </c>
+      <c r="AY3">
         <v>22</v>
       </c>
-      <c r="AB3">
-        <v>25</v>
-      </c>
-      <c r="AC3">
-        <v>10</v>
-      </c>
-      <c r="AD3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE3">
-        <v>15.5</v>
-      </c>
-      <c r="AF3">
-        <v>42</v>
-      </c>
-      <c r="AG3">
-        <v>19</v>
-      </c>
-      <c r="AH3">
-        <v>16</v>
-      </c>
-      <c r="AI3">
-        <v>24</v>
-      </c>
-      <c r="AJ3">
-        <v>110</v>
-      </c>
-      <c r="AK3">
-        <v>50</v>
-      </c>
-      <c r="AL3">
-        <v>46</v>
-      </c>
-      <c r="AM3">
-        <v>65</v>
-      </c>
-      <c r="AN3">
-        <v>36</v>
-      </c>
-      <c r="AO3">
-        <v>7.4</v>
-      </c>
-      <c r="AP3">
-        <v>23</v>
-      </c>
-      <c r="AQ3">
-        <v>12</v>
-      </c>
-      <c r="AR3">
-        <v>12.5</v>
-      </c>
-      <c r="AS3">
-        <v>19</v>
-      </c>
-      <c r="AT3">
-        <v>22</v>
-      </c>
-      <c r="AU3">
-        <v>9.4</v>
-      </c>
-      <c r="AV3">
-        <v>9.6</v>
-      </c>
-      <c r="AW3">
-        <v>13.5</v>
-      </c>
-      <c r="AX3">
+      <c r="AZ3">
+        <v>19.5</v>
+      </c>
+      <c r="BA3">
         <v>38</v>
       </c>
-      <c r="AY3">
-        <v>17.5</v>
-      </c>
-      <c r="AZ3">
-        <v>14.5</v>
-      </c>
-      <c r="BA3">
-        <v>20</v>
-      </c>
       <c r="BB3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BC3">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="BD3">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="BE3">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="BF3">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="BG3">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH3">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>106</v>
@@ -1412,226 +1412,226 @@
         <v>101</v>
       </c>
       <c r="F4">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="G4">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="L4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M4">
         <v>1.03</v>
       </c>
       <c r="N4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P4">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="Q4">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="R4">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="S4">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="U4">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W4">
-        <v>2.96</v>
+        <v>3.55</v>
       </c>
       <c r="X4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y4">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AA4">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="AB4">
         <v>12</v>
       </c>
       <c r="AC4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD4">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AF4">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI4">
+        <v>970</v>
+      </c>
+      <c r="AJ4">
+        <v>11.5</v>
+      </c>
+      <c r="AK4">
+        <v>13</v>
+      </c>
+      <c r="AL4">
+        <v>28</v>
+      </c>
+      <c r="AM4">
+        <v>110</v>
+      </c>
+      <c r="AN4">
+        <v>4.6</v>
+      </c>
+      <c r="AO4">
+        <v>160</v>
+      </c>
+      <c r="AP4">
+        <v>26</v>
+      </c>
+      <c r="AQ4">
+        <v>38</v>
+      </c>
+      <c r="AR4">
         <v>80</v>
-      </c>
-      <c r="AJ4">
-        <v>14.5</v>
-      </c>
-      <c r="AK4">
-        <v>14.5</v>
-      </c>
-      <c r="AL4">
-        <v>27</v>
-      </c>
-      <c r="AM4">
-        <v>95</v>
-      </c>
-      <c r="AN4">
-        <v>5.6</v>
-      </c>
-      <c r="AO4">
-        <v>80</v>
-      </c>
-      <c r="AP4">
-        <v>22</v>
-      </c>
-      <c r="AQ4">
-        <v>30</v>
-      </c>
-      <c r="AR4">
-        <v>50</v>
       </c>
       <c r="AS4">
         <v>85</v>
       </c>
       <c r="AT4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU4">
+        <v>12</v>
+      </c>
+      <c r="AV4">
+        <v>30</v>
+      </c>
+      <c r="AW4">
+        <v>95</v>
+      </c>
+      <c r="AX4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY4">
+        <v>9.6</v>
+      </c>
+      <c r="AZ4">
+        <v>21</v>
+      </c>
+      <c r="BA4">
+        <v>65</v>
+      </c>
+      <c r="BB4">
         <v>10.5</v>
       </c>
-      <c r="AV4">
-        <v>24</v>
-      </c>
-      <c r="AW4">
-        <v>55</v>
-      </c>
-      <c r="AX4">
-        <v>9.6</v>
-      </c>
-      <c r="AY4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4">
-        <v>18</v>
-      </c>
-      <c r="BA4">
-        <v>48</v>
-      </c>
-      <c r="BB4">
+      <c r="BC4">
         <v>12.5</v>
       </c>
-      <c r="BC4">
+      <c r="BD4">
+        <v>25</v>
+      </c>
+      <c r="BE4">
+        <v>70</v>
+      </c>
+      <c r="BF4">
+        <v>4.3</v>
+      </c>
+      <c r="BG4">
+        <v>85</v>
+      </c>
+      <c r="BH4">
+        <v>4.9</v>
+      </c>
+      <c r="BI4">
+        <v>4.5</v>
+      </c>
+      <c r="BJ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL4">
+        <v>120</v>
+      </c>
+      <c r="BM4">
         <v>13</v>
       </c>
-      <c r="BD4">
-        <v>22</v>
-      </c>
-      <c r="BE4">
-        <v>55</v>
-      </c>
-      <c r="BF4">
-        <v>5.1</v>
-      </c>
-      <c r="BG4">
-        <v>55</v>
-      </c>
-      <c r="BH4">
-        <v>5.6</v>
-      </c>
-      <c r="BI4">
-        <v>3.75</v>
-      </c>
-      <c r="BJ4">
-        <v>9.6</v>
-      </c>
-      <c r="BK4">
-        <v>7</v>
-      </c>
-      <c r="BL4">
-        <v>110</v>
-      </c>
-      <c r="BM4">
-        <v>7.6</v>
-      </c>
       <c r="BN4">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
         <v>4</v>
       </c>
       <c r="BP4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BQ4">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BR4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS4">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="BT4">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BU4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BV4">
         <v>60</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BX4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY4">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BZ4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="CA4">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="CB4" t="s">
         <v>106</v>
@@ -1660,19 +1660,19 @@
         <v>4.5</v>
       </c>
       <c r="H5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I5">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1690,25 +1690,25 @@
         <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U5">
         <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5">
         <v>8.800000000000001</v>
@@ -1723,7 +1723,7 @@
         <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5">
         <v>11</v>
@@ -1747,25 +1747,25 @@
         <v>120</v>
       </c>
       <c r="AK5">
+        <v>80</v>
+      </c>
+      <c r="AL5">
         <v>70</v>
-      </c>
-      <c r="AL5">
-        <v>90</v>
       </c>
       <c r="AM5">
         <v>150</v>
       </c>
       <c r="AN5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP5">
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5">
         <v>10.5</v>
@@ -1774,7 +1774,7 @@
         <v>21</v>
       </c>
       <c r="AT5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU5">
         <v>7</v>
@@ -1792,82 +1792,82 @@
         <v>15</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BB5">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>38</v>
+        <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BE5">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="BF5">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH5">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="BL5">
-        <v>170</v>
+        <v>640</v>
       </c>
       <c r="BM5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN5">
         <v>8</v>
       </c>
       <c r="BO5">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BP5">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BQ5">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BR5">
         <v>55</v>
       </c>
       <c r="BS5">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BT5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV5">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BW5">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY5">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1896,22 +1896,22 @@
         <v>103</v>
       </c>
       <c r="F6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="J6">
         <v>4.4</v>
       </c>
       <c r="K6">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
         <v>1.28</v>
@@ -1920,7 +1920,7 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O6">
         <v>1.17</v>
@@ -1929,25 +1929,25 @@
         <v>2.68</v>
       </c>
       <c r="Q6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S6">
         <v>2.34</v>
       </c>
       <c r="T6">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="W6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X6">
         <v>34</v>
@@ -1956,16 +1956,16 @@
         <v>14</v>
       </c>
       <c r="Z6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB6">
         <v>28</v>
       </c>
       <c r="AC6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD6">
         <v>13</v>
@@ -1980,13 +1980,13 @@
         <v>22</v>
       </c>
       <c r="AH6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI6">
         <v>26</v>
       </c>
       <c r="AJ6">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK6">
         <v>65</v>
@@ -1995,43 +1995,43 @@
         <v>60</v>
       </c>
       <c r="AM6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AP6">
         <v>23</v>
       </c>
       <c r="AQ6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR6">
         <v>11</v>
       </c>
       <c r="AS6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT6">
-        <v>5.6</v>
+        <v>22</v>
       </c>
       <c r="AU6">
         <v>9.4</v>
       </c>
       <c r="AV6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW6">
         <v>13.5</v>
       </c>
       <c r="AX6">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ6">
         <v>14</v>
@@ -2043,10 +2043,10 @@
         <v>6.2</v>
       </c>
       <c r="BC6">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD6">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE6">
         <v>6</v>
@@ -2055,7 +2055,7 @@
         <v>30</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH6">
         <v>5.4</v>
@@ -2082,13 +2082,13 @@
         <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ6">
         <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS6">
         <v>1.04</v>
@@ -2097,7 +2097,7 @@
         <v>5.5</v>
       </c>
       <c r="BU6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV6">
         <v>12</v>
@@ -2138,16 +2138,16 @@
         <v>104</v>
       </c>
       <c r="F7">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G7">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="H7">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I7">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="J7">
         <v>3.45</v>
@@ -2156,7 +2156,7 @@
         <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2165,46 +2165,46 @@
         <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U7">
         <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W7">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC7">
         <v>7.8</v>
@@ -2213,40 +2213,40 @@
         <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
         <v>19.5</v>
       </c>
       <c r="AI7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ7">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AK7">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AL7">
         <v>55</v>
       </c>
       <c r="AM7">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AN7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
         <v>8.800000000000001</v>
@@ -2255,10 +2255,10 @@
         <v>13</v>
       </c>
       <c r="AS7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU7">
         <v>7</v>
@@ -2270,19 +2270,19 @@
         <v>23</v>
       </c>
       <c r="AX7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB7">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BC7">
         <v>32</v>
@@ -2294,16 +2294,16 @@
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH7">
         <v>3.7</v>
       </c>
       <c r="BI7">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="BJ7">
         <v>12</v>
@@ -2318,40 +2318,40 @@
         <v>6</v>
       </c>
       <c r="BN7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BQ7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR7">
         <v>48</v>
       </c>
       <c r="BS7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU7">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BW7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BX7">
         <v>38</v>
       </c>
       <c r="BY7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BZ7">
         <v>38</v>
@@ -2383,7 +2383,7 @@
         <v>3.9</v>
       </c>
       <c r="G8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H8">
         <v>1.92</v>
@@ -2398,7 +2398,7 @@
         <v>4.4</v>
       </c>
       <c r="L8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M8">
         <v>1.03</v>
@@ -2410,22 +2410,22 @@
         <v>1.15</v>
       </c>
       <c r="P8">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q8">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S8">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T8">
         <v>1.51</v>
       </c>
       <c r="U8">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V8">
         <v>2.06</v>
@@ -2437,7 +2437,7 @@
         <v>32</v>
       </c>
       <c r="Y8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z8">
         <v>16.5</v>
@@ -2455,7 +2455,7 @@
         <v>11</v>
       </c>
       <c r="AE8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF8">
         <v>36</v>
@@ -2482,16 +2482,16 @@
         <v>50</v>
       </c>
       <c r="AN8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AP8">
         <v>28</v>
       </c>
       <c r="AQ8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR8">
         <v>14.5</v>
@@ -2515,7 +2515,7 @@
         <v>32</v>
       </c>
       <c r="AY8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
@@ -2527,13 +2527,13 @@
         <v>60</v>
       </c>
       <c r="BC8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD8">
         <v>32</v>
       </c>
       <c r="BE8">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BF8">
         <v>21</v>
@@ -2542,10 +2542,10 @@
         <v>6.8</v>
       </c>
       <c r="BH8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ8">
         <v>8.6</v>
@@ -2563,13 +2563,13 @@
         <v>8</v>
       </c>
       <c r="BO8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BP8">
         <v>26</v>
       </c>
       <c r="BQ8">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BR8">
         <v>29</v>
@@ -2590,16 +2590,16 @@
         <v>10</v>
       </c>
       <c r="BX8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BY8">
         <v>15</v>
       </c>
       <c r="BZ8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA8">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="s">
         <v>106</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>English National League</t>
-  </si>
-  <si>
     <t>Peruvian Primera Division</t>
   </si>
   <si>
@@ -277,9 +274,6 @@
     <t>2026-09-30</t>
   </si>
   <si>
-    <t>18:45:00</t>
-  </si>
-  <si>
     <t>20:00:00</t>
   </si>
   <si>
@@ -292,12 +286,6 @@
     <t>23:30:00</t>
   </si>
   <si>
-    <t>Tamworth FC</t>
-  </si>
-  <si>
-    <t>Eastleigh</t>
-  </si>
-  <si>
     <t>Cienciano</t>
   </si>
   <si>
@@ -313,12 +301,6 @@
     <t>New York Red Bulls</t>
   </si>
   <si>
-    <t>Sutton Utd</t>
-  </si>
-  <si>
-    <t>Southend</t>
-  </si>
-  <si>
     <t>CD Los Chankas</t>
   </si>
   <si>
@@ -334,7 +316,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-09-30 16:43:55</t>
+    <t>2026-09-30 18:55:38</t>
   </si>
 </sst>
 </file>
@@ -666,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -916,179 +898,179 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="G2">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="H2">
-        <v>3.05</v>
+        <v>23</v>
       </c>
       <c r="I2">
-        <v>3.15</v>
+        <v>36</v>
       </c>
       <c r="J2">
+        <v>1.45</v>
+      </c>
+      <c r="K2">
+        <v>1.48</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1.59</v>
+      </c>
+      <c r="Q2">
         <v>2.68</v>
       </c>
-      <c r="K2">
-        <v>2.7</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>1.26</v>
-      </c>
-      <c r="N2">
-        <v>1.8</v>
-      </c>
-      <c r="O2">
-        <v>2.18</v>
-      </c>
-      <c r="P2">
-        <v>1.22</v>
-      </c>
-      <c r="Q2">
-        <v>5.2</v>
-      </c>
       <c r="R2">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="S2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T2">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.03</v>
       </c>
       <c r="W2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X2">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>1.46</v>
       </c>
       <c r="AD2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>970</v>
       </c>
       <c r="AF2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AH2">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AI2">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AL2">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="AQ2">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="AR2">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AS2">
+        <v>18</v>
+      </c>
+      <c r="AT2">
+        <v>18</v>
+      </c>
+      <c r="AU2">
+        <v>1.35</v>
+      </c>
+      <c r="AV2">
+        <v>14</v>
+      </c>
+      <c r="AW2">
+        <v>110</v>
+      </c>
+      <c r="AX2">
+        <v>18</v>
+      </c>
+      <c r="AY2">
+        <v>3.75</v>
+      </c>
+      <c r="AZ2">
+        <v>65</v>
+      </c>
+      <c r="BA2">
+        <v>85</v>
+      </c>
+      <c r="BB2">
+        <v>18</v>
+      </c>
+      <c r="BC2">
+        <v>26</v>
+      </c>
+      <c r="BD2">
+        <v>170</v>
+      </c>
+      <c r="BE2">
+        <v>80</v>
+      </c>
+      <c r="BF2">
+        <v>190</v>
+      </c>
+      <c r="BG2">
         <v>50</v>
       </c>
-      <c r="AT2">
-        <v>5.7</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>12.5</v>
-      </c>
-      <c r="AW2">
-        <v>75</v>
-      </c>
-      <c r="AX2">
-        <v>16</v>
-      </c>
-      <c r="AY2">
-        <v>19.5</v>
-      </c>
-      <c r="AZ2">
-        <v>46</v>
-      </c>
-      <c r="BA2">
-        <v>60</v>
-      </c>
-      <c r="BB2">
-        <v>60</v>
-      </c>
-      <c r="BC2">
-        <v>75</v>
-      </c>
-      <c r="BD2">
-        <v>70</v>
-      </c>
-      <c r="BE2">
-        <v>480</v>
-      </c>
-      <c r="BF2">
-        <v>110</v>
-      </c>
-      <c r="BG2">
-        <v>14</v>
-      </c>
       <c r="BH2">
         <v>0</v>
       </c>
@@ -1150,123 +1132,123 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="G3">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2.06</v>
+      </c>
+      <c r="J3">
+        <v>2.72</v>
+      </c>
+      <c r="K3">
+        <v>2.86</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1.28</v>
+      </c>
+      <c r="N3">
+        <v>1.73</v>
+      </c>
+      <c r="O3">
+        <v>2.3</v>
+      </c>
+      <c r="P3">
+        <v>1.21</v>
+      </c>
+      <c r="Q3">
+        <v>5.4</v>
+      </c>
+      <c r="R3">
+        <v>1.05</v>
+      </c>
+      <c r="S3">
+        <v>17.5</v>
+      </c>
+      <c r="T3">
+        <v>3.85</v>
+      </c>
+      <c r="U3">
         <v>1.3</v>
       </c>
-      <c r="I3">
-        <v>1.31</v>
-      </c>
-      <c r="J3">
-        <v>5.8</v>
-      </c>
-      <c r="K3">
-        <v>5.9</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>6</v>
-      </c>
-      <c r="O3">
-        <v>1.18</v>
-      </c>
-      <c r="P3">
-        <v>2.16</v>
-      </c>
-      <c r="Q3">
-        <v>1.83</v>
-      </c>
-      <c r="R3">
-        <v>1.33</v>
-      </c>
-      <c r="S3">
-        <v>3.85</v>
-      </c>
-      <c r="T3">
-        <v>1.87</v>
-      </c>
-      <c r="U3">
-        <v>2.02</v>
-      </c>
       <c r="V3">
-        <v>4.2</v>
+        <v>1.96</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X3">
+        <v>4.7</v>
+      </c>
+      <c r="Y3">
+        <v>4.3</v>
+      </c>
+      <c r="Z3">
+        <v>9</v>
+      </c>
+      <c r="AA3">
+        <v>28</v>
+      </c>
+      <c r="AB3">
+        <v>10.5</v>
+      </c>
+      <c r="AC3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>18.5</v>
+      </c>
+      <c r="AE3">
+        <v>70</v>
+      </c>
+      <c r="AF3">
+        <v>55</v>
+      </c>
+      <c r="AG3">
+        <v>46</v>
+      </c>
+      <c r="AH3">
+        <v>90</v>
+      </c>
+      <c r="AI3">
         <v>1000</v>
-      </c>
-      <c r="Y3">
-        <v>6.4</v>
-      </c>
-      <c r="Z3">
-        <v>6</v>
-      </c>
-      <c r="AA3">
-        <v>11</v>
-      </c>
-      <c r="AB3">
-        <v>1000</v>
-      </c>
-      <c r="AC3">
-        <v>8.4</v>
-      </c>
-      <c r="AD3">
-        <v>7.2</v>
-      </c>
-      <c r="AE3">
-        <v>15</v>
-      </c>
-      <c r="AF3">
-        <v>1000</v>
-      </c>
-      <c r="AG3">
-        <v>24</v>
-      </c>
-      <c r="AH3">
-        <v>23</v>
-      </c>
-      <c r="AI3">
-        <v>48</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>1000</v>
@@ -1275,401 +1257,401 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="AP3">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="AR3">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="AT3">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AW3">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="AX3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AY3">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>60</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="BB3">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BC3">
+        <v>260</v>
+      </c>
+      <c r="BD3">
+        <v>360</v>
+      </c>
+      <c r="BE3">
+        <v>400</v>
+      </c>
+      <c r="BF3">
+        <v>390</v>
+      </c>
+      <c r="BG3">
+        <v>48</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
         <v>100</v>
-      </c>
-      <c r="BD3">
-        <v>80</v>
-      </c>
-      <c r="BE3">
-        <v>130</v>
-      </c>
-      <c r="BF3">
-        <v>170</v>
-      </c>
-      <c r="BG3">
-        <v>11.5</v>
-      </c>
-      <c r="BH3">
-        <v>0</v>
-      </c>
-      <c r="BI3">
-        <v>0</v>
-      </c>
-      <c r="BJ3">
-        <v>0</v>
-      </c>
-      <c r="BK3">
-        <v>0</v>
-      </c>
-      <c r="BL3">
-        <v>0</v>
-      </c>
-      <c r="BM3">
-        <v>0</v>
-      </c>
-      <c r="BN3">
-        <v>0</v>
-      </c>
-      <c r="BO3">
-        <v>0</v>
-      </c>
-      <c r="BP3">
-        <v>0</v>
-      </c>
-      <c r="BQ3">
-        <v>0</v>
-      </c>
-      <c r="BR3">
-        <v>0</v>
-      </c>
-      <c r="BS3">
-        <v>0</v>
-      </c>
-      <c r="BT3">
-        <v>0</v>
-      </c>
-      <c r="BU3">
-        <v>0</v>
-      </c>
-      <c r="BV3">
-        <v>0</v>
-      </c>
-      <c r="BW3">
-        <v>0</v>
-      </c>
-      <c r="BX3">
-        <v>0</v>
-      </c>
-      <c r="BY3">
-        <v>0</v>
-      </c>
-      <c r="BZ3">
-        <v>0</v>
-      </c>
-      <c r="CA3">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
         <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F4">
-        <v>1.37</v>
+        <v>4.8</v>
       </c>
       <c r="G4">
-        <v>1.39</v>
+        <v>5.2</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>1.69</v>
       </c>
       <c r="I4">
-        <v>9.800000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="J4">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="L4">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
         <v>1.03</v>
       </c>
       <c r="N4">
+        <v>6</v>
+      </c>
+      <c r="O4">
+        <v>1.18</v>
+      </c>
+      <c r="P4">
+        <v>2.72</v>
+      </c>
+      <c r="Q4">
+        <v>1.53</v>
+      </c>
+      <c r="R4">
+        <v>1.68</v>
+      </c>
+      <c r="S4">
+        <v>2.36</v>
+      </c>
+      <c r="T4">
+        <v>1.61</v>
+      </c>
+      <c r="U4">
+        <v>2.42</v>
+      </c>
+      <c r="V4">
+        <v>2.36</v>
+      </c>
+      <c r="W4">
+        <v>1.23</v>
+      </c>
+      <c r="X4">
+        <v>950</v>
+      </c>
+      <c r="Y4">
+        <v>14</v>
+      </c>
+      <c r="Z4">
+        <v>13.5</v>
+      </c>
+      <c r="AA4">
+        <v>23</v>
+      </c>
+      <c r="AB4">
+        <v>28</v>
+      </c>
+      <c r="AC4">
+        <v>11.5</v>
+      </c>
+      <c r="AD4">
+        <v>11</v>
+      </c>
+      <c r="AE4">
+        <v>16.5</v>
+      </c>
+      <c r="AF4">
+        <v>55</v>
+      </c>
+      <c r="AG4">
+        <v>25</v>
+      </c>
+      <c r="AH4">
+        <v>19</v>
+      </c>
+      <c r="AI4">
+        <v>26</v>
+      </c>
+      <c r="AJ4">
+        <v>120</v>
+      </c>
+      <c r="AK4">
+        <v>65</v>
+      </c>
+      <c r="AL4">
+        <v>60</v>
+      </c>
+      <c r="AM4">
+        <v>75</v>
+      </c>
+      <c r="AN4">
+        <v>42</v>
+      </c>
+      <c r="AO4">
+        <v>7.6</v>
+      </c>
+      <c r="AP4">
+        <v>6.2</v>
+      </c>
+      <c r="AQ4">
+        <v>11</v>
+      </c>
+      <c r="AR4">
+        <v>11</v>
+      </c>
+      <c r="AS4">
+        <v>15.5</v>
+      </c>
+      <c r="AT4">
+        <v>21</v>
+      </c>
+      <c r="AU4">
+        <v>9.4</v>
+      </c>
+      <c r="AV4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW4">
+        <v>13.5</v>
+      </c>
+      <c r="AX4">
         <v>6.4</v>
       </c>
-      <c r="O4">
-        <v>1.17</v>
-      </c>
-      <c r="P4">
-        <v>2.84</v>
-      </c>
-      <c r="Q4">
-        <v>1.51</v>
-      </c>
-      <c r="R4">
-        <v>1.74</v>
-      </c>
-      <c r="S4">
-        <v>2.3</v>
-      </c>
-      <c r="T4">
-        <v>1.81</v>
-      </c>
-      <c r="U4">
-        <v>2.14</v>
-      </c>
-      <c r="V4">
-        <v>1.11</v>
-      </c>
-      <c r="W4">
+      <c r="AY4">
+        <v>17</v>
+      </c>
+      <c r="AZ4">
+        <v>14.5</v>
+      </c>
+      <c r="BA4">
+        <v>21</v>
+      </c>
+      <c r="BB4">
+        <v>6.6</v>
+      </c>
+      <c r="BC4">
+        <v>6.4</v>
+      </c>
+      <c r="BD4">
+        <v>6.2</v>
+      </c>
+      <c r="BE4">
+        <v>6.4</v>
+      </c>
+      <c r="BF4">
+        <v>6</v>
+      </c>
+      <c r="BG4">
+        <v>6</v>
+      </c>
+      <c r="BH4">
+        <v>5.4</v>
+      </c>
+      <c r="BI4">
+        <v>4.1</v>
+      </c>
+      <c r="BJ4">
+        <v>11</v>
+      </c>
+      <c r="BK4">
+        <v>3.4</v>
+      </c>
+      <c r="BL4">
+        <v>80</v>
+      </c>
+      <c r="BM4">
+        <v>4.7</v>
+      </c>
+      <c r="BN4">
+        <v>10.5</v>
+      </c>
+      <c r="BO4">
+        <v>3.35</v>
+      </c>
+      <c r="BP4">
+        <v>40</v>
+      </c>
+      <c r="BQ4">
+        <v>4.4</v>
+      </c>
+      <c r="BR4">
+        <v>42</v>
+      </c>
+      <c r="BS4">
+        <v>4.4</v>
+      </c>
+      <c r="BT4">
+        <v>5.7</v>
+      </c>
+      <c r="BU4">
+        <v>4.2</v>
+      </c>
+      <c r="BV4">
+        <v>12.5</v>
+      </c>
+      <c r="BW4">
         <v>3.55</v>
       </c>
-      <c r="X4">
-        <v>30</v>
-      </c>
-      <c r="Y4">
-        <v>44</v>
-      </c>
-      <c r="Z4">
+      <c r="BX4">
+        <v>23</v>
+      </c>
+      <c r="BY4">
+        <v>4.1</v>
+      </c>
+      <c r="BZ4">
+        <v>14.5</v>
+      </c>
+      <c r="CA4">
+        <v>3.7</v>
+      </c>
+      <c r="CB4" t="s">
         <v>100</v>
-      </c>
-      <c r="AA4">
-        <v>400</v>
-      </c>
-      <c r="AB4">
-        <v>12</v>
-      </c>
-      <c r="AC4">
-        <v>13.5</v>
-      </c>
-      <c r="AD4">
-        <v>36</v>
-      </c>
-      <c r="AE4">
-        <v>160</v>
-      </c>
-      <c r="AF4">
-        <v>9.6</v>
-      </c>
-      <c r="AG4">
-        <v>10.5</v>
-      </c>
-      <c r="AH4">
-        <v>24</v>
-      </c>
-      <c r="AI4">
-        <v>970</v>
-      </c>
-      <c r="AJ4">
-        <v>11.5</v>
-      </c>
-      <c r="AK4">
-        <v>13</v>
-      </c>
-      <c r="AL4">
-        <v>28</v>
-      </c>
-      <c r="AM4">
-        <v>110</v>
-      </c>
-      <c r="AN4">
-        <v>4.6</v>
-      </c>
-      <c r="AO4">
-        <v>160</v>
-      </c>
-      <c r="AP4">
-        <v>26</v>
-      </c>
-      <c r="AQ4">
-        <v>38</v>
-      </c>
-      <c r="AR4">
-        <v>80</v>
-      </c>
-      <c r="AS4">
-        <v>85</v>
-      </c>
-      <c r="AT4">
-        <v>10.5</v>
-      </c>
-      <c r="AU4">
-        <v>12</v>
-      </c>
-      <c r="AV4">
-        <v>30</v>
-      </c>
-      <c r="AW4">
-        <v>95</v>
-      </c>
-      <c r="AX4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY4">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4">
-        <v>21</v>
-      </c>
-      <c r="BA4">
-        <v>65</v>
-      </c>
-      <c r="BB4">
-        <v>10.5</v>
-      </c>
-      <c r="BC4">
-        <v>12.5</v>
-      </c>
-      <c r="BD4">
-        <v>25</v>
-      </c>
-      <c r="BE4">
-        <v>70</v>
-      </c>
-      <c r="BF4">
-        <v>4.3</v>
-      </c>
-      <c r="BG4">
-        <v>85</v>
-      </c>
-      <c r="BH4">
-        <v>4.9</v>
-      </c>
-      <c r="BI4">
-        <v>4.5</v>
-      </c>
-      <c r="BJ4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL4">
-        <v>120</v>
-      </c>
-      <c r="BM4">
-        <v>13</v>
-      </c>
-      <c r="BN4">
-        <v>4.3</v>
-      </c>
-      <c r="BO4">
-        <v>4</v>
-      </c>
-      <c r="BP4">
-        <v>8</v>
-      </c>
-      <c r="BQ4">
-        <v>6.8</v>
-      </c>
-      <c r="BR4">
-        <v>19</v>
-      </c>
-      <c r="BS4">
-        <v>15.5</v>
-      </c>
-      <c r="BT4">
-        <v>13.5</v>
-      </c>
-      <c r="BU4">
-        <v>10</v>
-      </c>
-      <c r="BV4">
-        <v>60</v>
-      </c>
-      <c r="BW4">
-        <v>12</v>
-      </c>
-      <c r="BX4">
-        <v>55</v>
-      </c>
-      <c r="BY4">
-        <v>12</v>
-      </c>
-      <c r="BZ4">
-        <v>10</v>
-      </c>
-      <c r="CA4">
-        <v>8.6</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F5">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="G5">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="H5">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="I5">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L5">
         <v>1.44</v>
@@ -1678,931 +1660,447 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
         <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="W5">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="X5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
         <v>8.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AB5">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE5">
         <v>24</v>
       </c>
       <c r="AF5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AG5">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AH5">
+        <v>21</v>
+      </c>
+      <c r="AI5">
+        <v>44</v>
+      </c>
+      <c r="AJ5">
+        <v>75</v>
+      </c>
+      <c r="AK5">
+        <v>50</v>
+      </c>
+      <c r="AL5">
+        <v>60</v>
+      </c>
+      <c r="AM5">
+        <v>120</v>
+      </c>
+      <c r="AN5">
+        <v>55</v>
+      </c>
+      <c r="AO5">
         <v>19.5</v>
       </c>
-      <c r="AI5">
-        <v>42</v>
-      </c>
-      <c r="AJ5">
-        <v>120</v>
-      </c>
-      <c r="AK5">
-        <v>80</v>
-      </c>
-      <c r="AL5">
-        <v>70</v>
-      </c>
-      <c r="AM5">
-        <v>150</v>
-      </c>
-      <c r="AN5">
-        <v>75</v>
-      </c>
-      <c r="AO5">
-        <v>18</v>
-      </c>
       <c r="AP5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>9.6</v>
       </c>
       <c r="AW5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX5">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AY5">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BB5">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="BC5">
-        <v>19.5</v>
+        <v>40</v>
       </c>
       <c r="BD5">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE5">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BG5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BH5">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
-        <v>640</v>
+        <v>160</v>
       </c>
       <c r="BM5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BN5">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BP5">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BQ5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS5">
         <v>6.6</v>
       </c>
       <c r="BT5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BY5">
         <v>6.6</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F6">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="G6">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="I6">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M6">
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="O6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P6">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="R6">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="S6">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="T6">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.98</v>
       </c>
       <c r="V6">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="W6">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="X6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y6">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB6">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE6">
         <v>16.5</v>
       </c>
       <c r="AF6">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AG6">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AH6">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI6">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AJ6">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AK6">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AM6">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AN6">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AO6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP6">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AQ6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AR6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AS6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AT6">
         <v>22</v>
       </c>
       <c r="AU6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW6">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AX6">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AY6">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AZ6">
+        <v>13</v>
+      </c>
+      <c r="BA6">
+        <v>20</v>
+      </c>
+      <c r="BB6">
+        <v>60</v>
+      </c>
+      <c r="BC6">
+        <v>32</v>
+      </c>
+      <c r="BD6">
+        <v>32</v>
+      </c>
+      <c r="BE6">
+        <v>38</v>
+      </c>
+      <c r="BF6">
+        <v>20</v>
+      </c>
+      <c r="BG6">
+        <v>6.6</v>
+      </c>
+      <c r="BH6">
+        <v>4.9</v>
+      </c>
+      <c r="BI6">
+        <v>4.5</v>
+      </c>
+      <c r="BJ6">
+        <v>8.6</v>
+      </c>
+      <c r="BK6">
+        <v>7.6</v>
+      </c>
+      <c r="BL6">
+        <v>65</v>
+      </c>
+      <c r="BM6">
         <v>14</v>
       </c>
-      <c r="BA6">
-        <v>21</v>
-      </c>
-      <c r="BB6">
-        <v>6.2</v>
-      </c>
-      <c r="BC6">
-        <v>6.6</v>
-      </c>
-      <c r="BD6">
-        <v>6.4</v>
-      </c>
-      <c r="BE6">
-        <v>6</v>
-      </c>
-      <c r="BF6">
-        <v>30</v>
-      </c>
-      <c r="BG6">
-        <v>5.8</v>
-      </c>
-      <c r="BH6">
-        <v>5.4</v>
-      </c>
-      <c r="BI6">
-        <v>3.75</v>
-      </c>
-      <c r="BJ6">
+      <c r="BN6">
+        <v>7.8</v>
+      </c>
+      <c r="BO6">
+        <v>7.2</v>
+      </c>
+      <c r="BP6">
+        <v>26</v>
+      </c>
+      <c r="BQ6">
         <v>11</v>
       </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
-      <c r="BL6">
-        <v>90</v>
-      </c>
-      <c r="BM6">
-        <v>1.04</v>
-      </c>
-      <c r="BN6">
-        <v>11</v>
-      </c>
-      <c r="BO6">
-        <v>1.04</v>
-      </c>
-      <c r="BP6">
-        <v>40</v>
-      </c>
-      <c r="BQ6">
-        <v>1.04</v>
-      </c>
       <c r="BR6">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT6">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BU6">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
         <v>12</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX6">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BZ6">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:80">
-      <c r="A7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7">
-        <v>3.3</v>
-      </c>
-      <c r="G7">
-        <v>3.45</v>
-      </c>
-      <c r="H7">
-        <v>2.36</v>
-      </c>
-      <c r="I7">
-        <v>2.42</v>
-      </c>
-      <c r="J7">
-        <v>3.45</v>
-      </c>
-      <c r="K7">
-        <v>3.55</v>
-      </c>
-      <c r="L7">
-        <v>1.44</v>
-      </c>
-      <c r="M7">
-        <v>1.08</v>
-      </c>
-      <c r="N7">
-        <v>3.5</v>
-      </c>
-      <c r="O7">
-        <v>1.38</v>
-      </c>
-      <c r="P7">
-        <v>1.84</v>
-      </c>
-      <c r="Q7">
-        <v>2.14</v>
-      </c>
-      <c r="R7">
-        <v>1.32</v>
-      </c>
-      <c r="S7">
-        <v>3.9</v>
-      </c>
-      <c r="T7">
-        <v>1.88</v>
-      </c>
-      <c r="U7">
-        <v>2.08</v>
-      </c>
-      <c r="V7">
-        <v>1.7</v>
-      </c>
-      <c r="W7">
-        <v>1.4</v>
-      </c>
-      <c r="X7">
-        <v>12.5</v>
-      </c>
-      <c r="Y7">
-        <v>9.6</v>
-      </c>
-      <c r="Z7">
-        <v>14.5</v>
-      </c>
-      <c r="AA7">
-        <v>34</v>
-      </c>
-      <c r="AB7">
-        <v>12.5</v>
-      </c>
-      <c r="AC7">
-        <v>7.8</v>
-      </c>
-      <c r="AD7">
-        <v>11.5</v>
-      </c>
-      <c r="AE7">
-        <v>27</v>
-      </c>
-      <c r="AF7">
-        <v>24</v>
-      </c>
-      <c r="AG7">
-        <v>14.5</v>
-      </c>
-      <c r="AH7">
-        <v>19.5</v>
-      </c>
-      <c r="AI7">
-        <v>44</v>
-      </c>
-      <c r="AJ7">
-        <v>65</v>
-      </c>
-      <c r="AK7">
-        <v>42</v>
-      </c>
-      <c r="AL7">
-        <v>55</v>
-      </c>
-      <c r="AM7">
-        <v>110</v>
-      </c>
-      <c r="AN7">
-        <v>46</v>
-      </c>
-      <c r="AO7">
-        <v>23</v>
-      </c>
-      <c r="AP7">
-        <v>11</v>
-      </c>
-      <c r="AQ7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR7">
-        <v>13</v>
-      </c>
-      <c r="AS7">
-        <v>28</v>
-      </c>
-      <c r="AT7">
-        <v>11</v>
-      </c>
-      <c r="AU7">
-        <v>7</v>
-      </c>
-      <c r="AV7">
-        <v>10.5</v>
-      </c>
-      <c r="AW7">
-        <v>23</v>
-      </c>
-      <c r="AX7">
-        <v>20</v>
-      </c>
-      <c r="AY7">
-        <v>13</v>
-      </c>
-      <c r="AZ7">
-        <v>17</v>
-      </c>
-      <c r="BA7">
-        <v>38</v>
-      </c>
-      <c r="BB7">
-        <v>48</v>
-      </c>
-      <c r="BC7">
-        <v>32</v>
-      </c>
-      <c r="BD7">
-        <v>38</v>
-      </c>
-      <c r="BE7">
-        <v>50</v>
-      </c>
-      <c r="BF7">
-        <v>34</v>
-      </c>
-      <c r="BG7">
-        <v>20</v>
-      </c>
-      <c r="BH7">
-        <v>3.7</v>
-      </c>
-      <c r="BI7">
-        <v>2.96</v>
-      </c>
-      <c r="BJ7">
-        <v>12</v>
-      </c>
-      <c r="BK7">
-        <v>7.4</v>
-      </c>
-      <c r="BL7">
-        <v>160</v>
-      </c>
-      <c r="BM7">
-        <v>6</v>
-      </c>
-      <c r="BN7">
-        <v>6.8</v>
-      </c>
-      <c r="BO7">
-        <v>5.8</v>
-      </c>
-      <c r="BP7">
-        <v>36</v>
-      </c>
-      <c r="BQ7">
-        <v>5.5</v>
-      </c>
-      <c r="BR7">
-        <v>48</v>
-      </c>
-      <c r="BS7">
-        <v>5.6</v>
-      </c>
-      <c r="BT7">
-        <v>5.4</v>
-      </c>
-      <c r="BU7">
-        <v>4.6</v>
-      </c>
-      <c r="BV7">
-        <v>21</v>
-      </c>
-      <c r="BW7">
-        <v>4.9</v>
-      </c>
-      <c r="BX7">
-        <v>38</v>
-      </c>
-      <c r="BY7">
-        <v>5.4</v>
-      </c>
-      <c r="BZ7">
-        <v>38</v>
-      </c>
-      <c r="CA7">
-        <v>5.4</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:80">
-      <c r="A8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8">
-        <v>3.9</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>1.92</v>
-      </c>
-      <c r="I8">
-        <v>1.93</v>
-      </c>
-      <c r="J8">
-        <v>4.3</v>
-      </c>
-      <c r="K8">
-        <v>4.4</v>
-      </c>
-      <c r="L8">
-        <v>1.26</v>
-      </c>
-      <c r="M8">
-        <v>1.03</v>
-      </c>
-      <c r="N8">
-        <v>6.8</v>
-      </c>
-      <c r="O8">
-        <v>1.15</v>
-      </c>
-      <c r="P8">
-        <v>3</v>
-      </c>
-      <c r="Q8">
-        <v>1.48</v>
-      </c>
-      <c r="R8">
-        <v>1.81</v>
-      </c>
-      <c r="S8">
-        <v>2.2</v>
-      </c>
-      <c r="T8">
-        <v>1.51</v>
-      </c>
-      <c r="U8">
-        <v>2.88</v>
-      </c>
-      <c r="V8">
-        <v>2.06</v>
-      </c>
-      <c r="W8">
-        <v>1.33</v>
-      </c>
-      <c r="X8">
-        <v>32</v>
-      </c>
-      <c r="Y8">
-        <v>16.5</v>
-      </c>
-      <c r="Z8">
-        <v>16.5</v>
-      </c>
-      <c r="AA8">
-        <v>23</v>
-      </c>
-      <c r="AB8">
-        <v>25</v>
-      </c>
-      <c r="AC8">
-        <v>11</v>
-      </c>
-      <c r="AD8">
-        <v>11</v>
-      </c>
-      <c r="AE8">
-        <v>16.5</v>
-      </c>
-      <c r="AF8">
-        <v>36</v>
-      </c>
-      <c r="AG8">
-        <v>16.5</v>
-      </c>
-      <c r="AH8">
-        <v>14.5</v>
-      </c>
-      <c r="AI8">
-        <v>23</v>
-      </c>
-      <c r="AJ8">
-        <v>75</v>
-      </c>
-      <c r="AK8">
-        <v>38</v>
-      </c>
-      <c r="AL8">
-        <v>36</v>
-      </c>
-      <c r="AM8">
-        <v>50</v>
-      </c>
-      <c r="AN8">
-        <v>23</v>
-      </c>
-      <c r="AO8">
-        <v>7.4</v>
-      </c>
-      <c r="AP8">
-        <v>28</v>
-      </c>
-      <c r="AQ8">
-        <v>15</v>
-      </c>
-      <c r="AR8">
-        <v>14.5</v>
-      </c>
-      <c r="AS8">
-        <v>20</v>
-      </c>
-      <c r="AT8">
-        <v>22</v>
-      </c>
-      <c r="AU8">
-        <v>10</v>
-      </c>
-      <c r="AV8">
-        <v>10</v>
-      </c>
-      <c r="AW8">
-        <v>15.5</v>
-      </c>
-      <c r="AX8">
-        <v>32</v>
-      </c>
-      <c r="AY8">
-        <v>15.5</v>
-      </c>
-      <c r="AZ8">
-        <v>13.5</v>
-      </c>
-      <c r="BA8">
-        <v>21</v>
-      </c>
-      <c r="BB8">
-        <v>60</v>
-      </c>
-      <c r="BC8">
-        <v>32</v>
-      </c>
-      <c r="BD8">
-        <v>32</v>
-      </c>
-      <c r="BE8">
-        <v>42</v>
-      </c>
-      <c r="BF8">
-        <v>21</v>
-      </c>
-      <c r="BG8">
-        <v>6.8</v>
-      </c>
-      <c r="BH8">
-        <v>5</v>
-      </c>
-      <c r="BI8">
-        <v>4.5</v>
-      </c>
-      <c r="BJ8">
-        <v>8.6</v>
-      </c>
-      <c r="BK8">
-        <v>7.6</v>
-      </c>
-      <c r="BL8">
-        <v>70</v>
-      </c>
-      <c r="BM8">
-        <v>12.5</v>
-      </c>
-      <c r="BN8">
-        <v>8</v>
-      </c>
-      <c r="BO8">
-        <v>7</v>
-      </c>
-      <c r="BP8">
-        <v>26</v>
-      </c>
-      <c r="BQ8">
-        <v>10.5</v>
-      </c>
-      <c r="BR8">
-        <v>29</v>
-      </c>
-      <c r="BS8">
-        <v>10</v>
-      </c>
-      <c r="BT8">
-        <v>5.2</v>
-      </c>
-      <c r="BU8">
-        <v>4.8</v>
-      </c>
-      <c r="BV8">
-        <v>12</v>
-      </c>
-      <c r="BW8">
-        <v>10</v>
-      </c>
-      <c r="BX8">
-        <v>19</v>
-      </c>
-      <c r="BY8">
-        <v>15</v>
-      </c>
-      <c r="BZ8">
-        <v>12.5</v>
-      </c>
-      <c r="CA8">
-        <v>7.2</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
